--- a/.github/datafiles/Communications Calendar 2026.xlsx
+++ b/.github/datafiles/Communications Calendar 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jewishvoice-my.sharepoint.com/personal/creativemarketing_jewishvoice_org/Documents/CM Shared Folders/Calendars/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2EC8C37-904C-47D3-B3BB-56B795DE4869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF1547F1-9751-4A8D-9FDF-3DEE0D8C6A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{32BB45BA-020D-466F-91C6-73191094497B}"/>
   </bookViews>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9600" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9604" uniqueCount="378">
   <si>
     <t>Description</t>
   </si>
@@ -832,6 +832,9 @@
   </si>
   <si>
     <t>Independence Day (US) - 7/4/26</t>
+  </si>
+  <si>
+    <t>Tentative... Outreach Recap Email</t>
   </si>
   <si>
     <t>July Newsletter</t>
@@ -1611,6 +1614,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1621,9 +1627,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1973,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD25C92C-1A37-4466-8D09-37A65C4BD4ED}">
-  <dimension ref="A1:XEY402"/>
+  <dimension ref="A1:XEY403"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="48.42578125" style="1" customWidth="1"/>
@@ -2034,29 +2037,29 @@
       <c r="J2" s="35"/>
     </row>
     <row r="3" spans="1:10" s="5" customFormat="1" ht="19.5" hidden="1">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
       <c r="H3" s="33"/>
       <c r="I3" s="33"/>
       <c r="J3" s="33"/>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
       <c r="H4" s="36"/>
       <c r="I4" s="36"/>
       <c r="J4" s="36"/>
@@ -2288,15 +2291,15 @@
       <c r="J15" s="37"/>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
       <c r="H16" s="36"/>
       <c r="I16" s="36"/>
       <c r="J16" s="36"/>
@@ -2474,15 +2477,15 @@
       <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A25" s="76" t="s">
+      <c r="A25" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="76"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
       <c r="H25" s="38"/>
       <c r="I25" s="38"/>
       <c r="J25" s="38"/>
@@ -2610,29 +2613,29 @@
       <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:10" s="5" customFormat="1" ht="19.5" hidden="1">
-      <c r="A33" s="78" t="s">
+      <c r="A33" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="78"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="79"/>
+      <c r="G33" s="79"/>
       <c r="H33" s="34"/>
       <c r="I33" s="34"/>
       <c r="J33" s="34"/>
     </row>
     <row r="34" spans="1:10" s="5" customFormat="1" ht="19.5" hidden="1">
-      <c r="A34" s="79" t="s">
+      <c r="A34" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="79"/>
+      <c r="B34" s="75"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="75"/>
       <c r="H34" s="33"/>
       <c r="I34" s="33"/>
       <c r="J34" s="33"/>
@@ -2660,15 +2663,15 @@
       <c r="J35" s="37"/>
     </row>
     <row r="36" spans="1:10" hidden="1">
-      <c r="A36" s="77" t="s">
+      <c r="A36" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
+      <c r="B36" s="78"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="78"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="78"/>
       <c r="H36" s="36"/>
       <c r="I36" s="36"/>
       <c r="J36" s="36"/>
@@ -2692,15 +2695,15 @@
       <c r="F37" s="6"/>
     </row>
     <row r="38" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A38" s="75" t="s">
+      <c r="A38" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="75"/>
-      <c r="C38" s="75"/>
-      <c r="D38" s="75"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
+      <c r="B38" s="76"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
       <c r="H38" s="39"/>
       <c r="I38" s="39"/>
       <c r="J38" s="39"/>
@@ -2883,29 +2886,29 @@
       <c r="J47" s="37"/>
     </row>
     <row r="48" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A48" s="77" t="s">
+      <c r="A48" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="77"/>
-      <c r="C48" s="77"/>
-      <c r="D48" s="77"/>
-      <c r="E48" s="77"/>
-      <c r="F48" s="77"/>
-      <c r="G48" s="77"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78"/>
+      <c r="G48" s="78"/>
       <c r="H48" s="36"/>
       <c r="I48" s="36"/>
       <c r="J48" s="36"/>
     </row>
     <row r="49" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A49" s="77" t="s">
+      <c r="A49" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="77"/>
-      <c r="C49" s="77"/>
-      <c r="D49" s="77"/>
-      <c r="E49" s="77"/>
-      <c r="F49" s="77"/>
-      <c r="G49" s="77"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="78"/>
+      <c r="D49" s="78"/>
+      <c r="E49" s="78"/>
+      <c r="F49" s="78"/>
+      <c r="G49" s="78"/>
       <c r="H49" s="36"/>
       <c r="I49" s="36"/>
       <c r="J49" s="36"/>
@@ -2929,15 +2932,15 @@
       <c r="F50" s="6"/>
     </row>
     <row r="51" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A51" s="75" t="s">
+      <c r="A51" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="75"/>
-      <c r="C51" s="75"/>
-      <c r="D51" s="75"/>
-      <c r="E51" s="75"/>
-      <c r="F51" s="75"/>
-      <c r="G51" s="75"/>
+      <c r="B51" s="76"/>
+      <c r="C51" s="76"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="76"/>
+      <c r="F51" s="76"/>
+      <c r="G51" s="76"/>
       <c r="H51" s="39"/>
       <c r="I51" s="39"/>
       <c r="J51" s="39"/>
@@ -2978,15 +2981,15 @@
       <c r="F53" s="6"/>
     </row>
     <row r="54" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A54" s="76" t="s">
+      <c r="A54" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="76"/>
-      <c r="C54" s="76"/>
-      <c r="D54" s="76"/>
-      <c r="E54" s="76"/>
-      <c r="F54" s="76"/>
-      <c r="G54" s="76"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="77"/>
+      <c r="E54" s="77"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="77"/>
       <c r="H54" s="38"/>
       <c r="I54" s="38"/>
       <c r="J54" s="38"/>
@@ -3344,29 +3347,29 @@
       <c r="F71" s="6"/>
     </row>
     <row r="72" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A72" s="78" t="s">
+      <c r="A72" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="B72" s="78"/>
-      <c r="C72" s="78"/>
-      <c r="D72" s="78"/>
-      <c r="E72" s="78"/>
-      <c r="F72" s="78"/>
-      <c r="G72" s="78"/>
+      <c r="B72" s="79"/>
+      <c r="C72" s="79"/>
+      <c r="D72" s="79"/>
+      <c r="E72" s="79"/>
+      <c r="F72" s="79"/>
+      <c r="G72" s="79"/>
       <c r="H72" s="34"/>
       <c r="I72" s="34"/>
       <c r="J72" s="34"/>
     </row>
     <row r="73" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A73" s="79" t="s">
+      <c r="A73" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="B73" s="79"/>
-      <c r="C73" s="79"/>
-      <c r="D73" s="79"/>
-      <c r="E73" s="79"/>
-      <c r="F73" s="79"/>
-      <c r="G73" s="79"/>
+      <c r="B73" s="75"/>
+      <c r="C73" s="75"/>
+      <c r="D73" s="75"/>
+      <c r="E73" s="75"/>
+      <c r="F73" s="75"/>
+      <c r="G73" s="75"/>
       <c r="H73" s="33"/>
       <c r="I73" s="33"/>
       <c r="J73" s="33"/>
@@ -3548,15 +3551,15 @@
       <c r="J80" s="37"/>
     </row>
     <row r="81" spans="1:10" s="1" customFormat="1">
-      <c r="A81" s="76" t="s">
+      <c r="A81" s="77" t="s">
         <v>101</v>
       </c>
-      <c r="B81" s="76"/>
-      <c r="C81" s="76"/>
-      <c r="D81" s="76"/>
-      <c r="E81" s="76"/>
-      <c r="F81" s="76"/>
-      <c r="G81" s="76"/>
+      <c r="B81" s="77"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="77"/>
+      <c r="E81" s="77"/>
+      <c r="F81" s="77"/>
+      <c r="G81" s="77"/>
       <c r="H81" s="38"/>
       <c r="I81" s="38"/>
       <c r="J81" s="38"/>
@@ -3624,15 +3627,15 @@
       <c r="J84" s="37"/>
     </row>
     <row r="85" spans="1:10" s="1" customFormat="1">
-      <c r="A85" s="75" t="s">
+      <c r="A85" s="76" t="s">
         <v>103</v>
       </c>
-      <c r="B85" s="75"/>
-      <c r="C85" s="75"/>
-      <c r="D85" s="75"/>
-      <c r="E85" s="75"/>
-      <c r="F85" s="75"/>
-      <c r="G85" s="75"/>
+      <c r="B85" s="76"/>
+      <c r="C85" s="76"/>
+      <c r="D85" s="76"/>
+      <c r="E85" s="76"/>
+      <c r="F85" s="76"/>
+      <c r="G85" s="76"/>
       <c r="H85" s="39"/>
       <c r="I85" s="39"/>
       <c r="J85" s="39"/>
@@ -3827,15 +3830,15 @@
       </c>
     </row>
     <row r="95" spans="1:10" s="1" customFormat="1">
-      <c r="A95" s="77" t="s">
+      <c r="A95" s="78" t="s">
         <v>116</v>
       </c>
-      <c r="B95" s="77"/>
-      <c r="C95" s="77"/>
-      <c r="D95" s="77"/>
-      <c r="E95" s="77"/>
-      <c r="F95" s="77"/>
-      <c r="G95" s="77"/>
+      <c r="B95" s="78"/>
+      <c r="C95" s="78"/>
+      <c r="D95" s="78"/>
+      <c r="E95" s="78"/>
+      <c r="F95" s="78"/>
+      <c r="G95" s="78"/>
       <c r="H95" s="36"/>
       <c r="I95" s="36"/>
       <c r="J95" s="36"/>
@@ -3883,15 +3886,15 @@
       <c r="F97" s="6"/>
     </row>
     <row r="98" spans="1:10" s="1" customFormat="1">
-      <c r="A98" s="76" t="s">
+      <c r="A98" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="B98" s="76"/>
-      <c r="C98" s="76"/>
-      <c r="D98" s="76"/>
-      <c r="E98" s="76"/>
-      <c r="F98" s="76"/>
-      <c r="G98" s="76"/>
+      <c r="B98" s="77"/>
+      <c r="C98" s="77"/>
+      <c r="D98" s="77"/>
+      <c r="E98" s="77"/>
+      <c r="F98" s="77"/>
+      <c r="G98" s="77"/>
       <c r="H98" s="38"/>
       <c r="I98" s="38"/>
       <c r="J98" s="38"/>
@@ -4089,15 +4092,15 @@
       <c r="J107" s="54"/>
     </row>
     <row r="108" spans="1:10" s="7" customFormat="1">
-      <c r="A108" s="77" t="s">
+      <c r="A108" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="B108" s="77"/>
-      <c r="C108" s="77"/>
-      <c r="D108" s="77"/>
-      <c r="E108" s="77"/>
-      <c r="F108" s="77"/>
-      <c r="G108" s="77"/>
+      <c r="B108" s="78"/>
+      <c r="C108" s="78"/>
+      <c r="D108" s="78"/>
+      <c r="E108" s="78"/>
+      <c r="F108" s="78"/>
+      <c r="G108" s="78"/>
       <c r="H108" s="36"/>
       <c r="I108" s="36"/>
       <c r="J108" s="36"/>
@@ -4167,29 +4170,29 @@
       <c r="F111" s="6"/>
     </row>
     <row r="112" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A112" s="78" t="s">
+      <c r="A112" s="79" t="s">
         <v>130</v>
       </c>
-      <c r="B112" s="78"/>
-      <c r="C112" s="78"/>
-      <c r="D112" s="78"/>
-      <c r="E112" s="78"/>
-      <c r="F112" s="78"/>
-      <c r="G112" s="78"/>
+      <c r="B112" s="79"/>
+      <c r="C112" s="79"/>
+      <c r="D112" s="79"/>
+      <c r="E112" s="79"/>
+      <c r="F112" s="79"/>
+      <c r="G112" s="79"/>
       <c r="H112" s="34"/>
       <c r="I112" s="34"/>
       <c r="J112" s="34"/>
     </row>
     <row r="113" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A113" s="79" t="s">
+      <c r="A113" s="75" t="s">
         <v>131</v>
       </c>
-      <c r="B113" s="79"/>
-      <c r="C113" s="79"/>
-      <c r="D113" s="79"/>
-      <c r="E113" s="79"/>
-      <c r="F113" s="79"/>
-      <c r="G113" s="79"/>
+      <c r="B113" s="75"/>
+      <c r="C113" s="75"/>
+      <c r="D113" s="75"/>
+      <c r="E113" s="75"/>
+      <c r="F113" s="75"/>
+      <c r="G113" s="75"/>
       <c r="H113" s="33"/>
       <c r="I113" s="33"/>
       <c r="J113" s="33"/>
@@ -4339,15 +4342,15 @@
       <c r="F119" s="6"/>
     </row>
     <row r="120" spans="1:10" s="1" customFormat="1">
-      <c r="A120" s="76" t="s">
+      <c r="A120" s="77" t="s">
         <v>145</v>
       </c>
-      <c r="B120" s="76"/>
-      <c r="C120" s="76"/>
-      <c r="D120" s="76"/>
-      <c r="E120" s="76"/>
-      <c r="F120" s="76"/>
-      <c r="G120" s="76"/>
+      <c r="B120" s="77"/>
+      <c r="C120" s="77"/>
+      <c r="D120" s="77"/>
+      <c r="E120" s="77"/>
+      <c r="F120" s="77"/>
+      <c r="G120" s="77"/>
       <c r="H120" s="38"/>
       <c r="I120" s="38"/>
       <c r="J120" s="38"/>
@@ -4377,29 +4380,29 @@
       <c r="J121" s="37"/>
     </row>
     <row r="122" spans="1:10" s="1" customFormat="1">
-      <c r="A122" s="77" t="s">
+      <c r="A122" s="78" t="s">
         <v>146</v>
       </c>
-      <c r="B122" s="77"/>
-      <c r="C122" s="77"/>
-      <c r="D122" s="77"/>
-      <c r="E122" s="77"/>
-      <c r="F122" s="77"/>
-      <c r="G122" s="77"/>
+      <c r="B122" s="78"/>
+      <c r="C122" s="78"/>
+      <c r="D122" s="78"/>
+      <c r="E122" s="78"/>
+      <c r="F122" s="78"/>
+      <c r="G122" s="78"/>
       <c r="H122" s="36"/>
       <c r="I122" s="36"/>
       <c r="J122" s="36"/>
     </row>
     <row r="123" spans="1:10" s="1" customFormat="1">
-      <c r="A123" s="76" t="s">
+      <c r="A123" s="77" t="s">
         <v>147</v>
       </c>
-      <c r="B123" s="76"/>
-      <c r="C123" s="76"/>
-      <c r="D123" s="76"/>
-      <c r="E123" s="76"/>
-      <c r="F123" s="76"/>
-      <c r="G123" s="76"/>
+      <c r="B123" s="77"/>
+      <c r="C123" s="77"/>
+      <c r="D123" s="77"/>
+      <c r="E123" s="77"/>
+      <c r="F123" s="77"/>
+      <c r="G123" s="77"/>
       <c r="H123" s="38"/>
       <c r="I123" s="38"/>
       <c r="J123" s="38"/>
@@ -4425,29 +4428,29 @@
       <c r="J124" s="56"/>
     </row>
     <row r="125" spans="1:10" s="1" customFormat="1">
-      <c r="A125" s="77" t="s">
+      <c r="A125" s="78" t="s">
         <v>150</v>
       </c>
-      <c r="B125" s="77"/>
-      <c r="C125" s="77"/>
-      <c r="D125" s="77"/>
-      <c r="E125" s="77"/>
-      <c r="F125" s="77"/>
-      <c r="G125" s="77"/>
+      <c r="B125" s="78"/>
+      <c r="C125" s="78"/>
+      <c r="D125" s="78"/>
+      <c r="E125" s="78"/>
+      <c r="F125" s="78"/>
+      <c r="G125" s="78"/>
       <c r="H125" s="36"/>
       <c r="I125" s="36"/>
       <c r="J125" s="36"/>
     </row>
     <row r="126" spans="1:10" s="1" customFormat="1">
-      <c r="A126" s="77" t="s">
+      <c r="A126" s="78" t="s">
         <v>151</v>
       </c>
-      <c r="B126" s="77"/>
-      <c r="C126" s="77"/>
-      <c r="D126" s="77"/>
-      <c r="E126" s="77"/>
-      <c r="F126" s="77"/>
-      <c r="G126" s="77"/>
+      <c r="B126" s="78"/>
+      <c r="C126" s="78"/>
+      <c r="D126" s="78"/>
+      <c r="E126" s="78"/>
+      <c r="F126" s="78"/>
+      <c r="G126" s="78"/>
       <c r="H126" s="36"/>
       <c r="I126" s="36"/>
       <c r="J126" s="36"/>
@@ -4513,15 +4516,15 @@
       <c r="J129" s="37"/>
     </row>
     <row r="130" spans="1:10" s="1" customFormat="1">
-      <c r="A130" s="75" t="s">
+      <c r="A130" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="B130" s="75"/>
-      <c r="C130" s="75"/>
-      <c r="D130" s="75"/>
-      <c r="E130" s="75"/>
-      <c r="F130" s="75"/>
-      <c r="G130" s="75"/>
+      <c r="B130" s="76"/>
+      <c r="C130" s="76"/>
+      <c r="D130" s="76"/>
+      <c r="E130" s="76"/>
+      <c r="F130" s="76"/>
+      <c r="G130" s="76"/>
       <c r="H130" s="39"/>
       <c r="I130" s="39"/>
       <c r="J130" s="39"/>
@@ -4623,29 +4626,29 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="1" customFormat="1">
-      <c r="A136" s="75" t="s">
+      <c r="A136" s="76" t="s">
         <v>157</v>
       </c>
-      <c r="B136" s="75"/>
-      <c r="C136" s="75"/>
-      <c r="D136" s="75"/>
-      <c r="E136" s="75"/>
-      <c r="F136" s="75"/>
-      <c r="G136" s="75"/>
+      <c r="B136" s="76"/>
+      <c r="C136" s="76"/>
+      <c r="D136" s="76"/>
+      <c r="E136" s="76"/>
+      <c r="F136" s="76"/>
+      <c r="G136" s="76"/>
       <c r="H136" s="39"/>
       <c r="I136" s="39"/>
       <c r="J136" s="39"/>
     </row>
     <row r="137" spans="1:10" s="1" customFormat="1">
-      <c r="A137" s="76" t="s">
+      <c r="A137" s="77" t="s">
         <v>158</v>
       </c>
-      <c r="B137" s="76"/>
-      <c r="C137" s="76"/>
-      <c r="D137" s="76"/>
-      <c r="E137" s="76"/>
-      <c r="F137" s="76"/>
-      <c r="G137" s="76"/>
+      <c r="B137" s="77"/>
+      <c r="C137" s="77"/>
+      <c r="D137" s="77"/>
+      <c r="E137" s="77"/>
+      <c r="F137" s="77"/>
+      <c r="G137" s="77"/>
       <c r="H137" s="38"/>
       <c r="I137" s="38"/>
       <c r="J137" s="38"/>
@@ -4745,15 +4748,15 @@
       <c r="J141" s="23"/>
     </row>
     <row r="142" spans="1:10" s="1" customFormat="1">
-      <c r="A142" s="76" t="s">
+      <c r="A142" s="77" t="s">
         <v>163</v>
       </c>
-      <c r="B142" s="76"/>
-      <c r="C142" s="76"/>
-      <c r="D142" s="76"/>
-      <c r="E142" s="76"/>
-      <c r="F142" s="76"/>
-      <c r="G142" s="76"/>
+      <c r="B142" s="77"/>
+      <c r="C142" s="77"/>
+      <c r="D142" s="77"/>
+      <c r="E142" s="77"/>
+      <c r="F142" s="77"/>
+      <c r="G142" s="77"/>
       <c r="H142" s="38"/>
       <c r="I142" s="38"/>
       <c r="J142" s="38"/>
@@ -4822,29 +4825,29 @@
       </c>
     </row>
     <row r="146" spans="1:16379" s="1" customFormat="1">
-      <c r="A146" s="76" t="s">
+      <c r="A146" s="77" t="s">
         <v>168</v>
       </c>
-      <c r="B146" s="76"/>
-      <c r="C146" s="76"/>
-      <c r="D146" s="76"/>
-      <c r="E146" s="76"/>
-      <c r="F146" s="76"/>
-      <c r="G146" s="76"/>
+      <c r="B146" s="77"/>
+      <c r="C146" s="77"/>
+      <c r="D146" s="77"/>
+      <c r="E146" s="77"/>
+      <c r="F146" s="77"/>
+      <c r="G146" s="77"/>
       <c r="H146" s="38"/>
       <c r="I146" s="38"/>
       <c r="J146" s="38"/>
     </row>
     <row r="147" spans="1:16379" s="1" customFormat="1">
-      <c r="A147" s="76" t="s">
+      <c r="A147" s="77" t="s">
         <v>169</v>
       </c>
-      <c r="B147" s="76"/>
-      <c r="C147" s="76"/>
-      <c r="D147" s="76"/>
-      <c r="E147" s="76"/>
-      <c r="F147" s="76"/>
-      <c r="G147" s="76"/>
+      <c r="B147" s="77"/>
+      <c r="C147" s="77"/>
+      <c r="D147" s="77"/>
+      <c r="E147" s="77"/>
+      <c r="F147" s="77"/>
+      <c r="G147" s="77"/>
       <c r="H147" s="38"/>
       <c r="I147" s="38"/>
       <c r="J147" s="38"/>
@@ -52103,57 +52106,57 @@
       <c r="J158" s="61"/>
     </row>
     <row r="159" spans="1:16379" s="1" customFormat="1" ht="19.5">
-      <c r="A159" s="78" t="s">
+      <c r="A159" s="79" t="s">
         <v>179</v>
       </c>
-      <c r="B159" s="78"/>
-      <c r="C159" s="78"/>
-      <c r="D159" s="78"/>
-      <c r="E159" s="78"/>
-      <c r="F159" s="78"/>
-      <c r="G159" s="78"/>
+      <c r="B159" s="79"/>
+      <c r="C159" s="79"/>
+      <c r="D159" s="79"/>
+      <c r="E159" s="79"/>
+      <c r="F159" s="79"/>
+      <c r="G159" s="79"/>
       <c r="H159" s="34"/>
       <c r="I159" s="34"/>
       <c r="J159" s="34"/>
     </row>
     <row r="160" spans="1:16379" s="5" customFormat="1" ht="19.5">
-      <c r="A160" s="79" t="s">
+      <c r="A160" s="75" t="s">
         <v>131</v>
       </c>
-      <c r="B160" s="79"/>
-      <c r="C160" s="79"/>
-      <c r="D160" s="79"/>
-      <c r="E160" s="79"/>
-      <c r="F160" s="79"/>
-      <c r="G160" s="79"/>
+      <c r="B160" s="75"/>
+      <c r="C160" s="75"/>
+      <c r="D160" s="75"/>
+      <c r="E160" s="75"/>
+      <c r="F160" s="75"/>
+      <c r="G160" s="75"/>
       <c r="H160" s="33"/>
       <c r="I160" s="33"/>
       <c r="J160" s="33"/>
     </row>
     <row r="161" spans="1:10" s="1" customFormat="1">
-      <c r="A161" s="75" t="s">
+      <c r="A161" s="76" t="s">
         <v>180</v>
       </c>
-      <c r="B161" s="75"/>
-      <c r="C161" s="75"/>
-      <c r="D161" s="75"/>
-      <c r="E161" s="75"/>
-      <c r="F161" s="75"/>
-      <c r="G161" s="75"/>
+      <c r="B161" s="76"/>
+      <c r="C161" s="76"/>
+      <c r="D161" s="76"/>
+      <c r="E161" s="76"/>
+      <c r="F161" s="76"/>
+      <c r="G161" s="76"/>
       <c r="H161" s="39"/>
       <c r="I161" s="39"/>
       <c r="J161" s="39"/>
     </row>
     <row r="162" spans="1:10" s="1" customFormat="1">
-      <c r="A162" s="77" t="s">
+      <c r="A162" s="78" t="s">
         <v>181</v>
       </c>
-      <c r="B162" s="77"/>
-      <c r="C162" s="77"/>
-      <c r="D162" s="77"/>
-      <c r="E162" s="77"/>
-      <c r="F162" s="77"/>
-      <c r="G162" s="77"/>
+      <c r="B162" s="78"/>
+      <c r="C162" s="78"/>
+      <c r="D162" s="78"/>
+      <c r="E162" s="78"/>
+      <c r="F162" s="78"/>
+      <c r="G162" s="78"/>
       <c r="H162" s="36"/>
       <c r="I162" s="36"/>
       <c r="J162" s="36"/>
@@ -52309,15 +52312,15 @@
       <c r="F169" s="6"/>
     </row>
     <row r="170" spans="1:10" s="1" customFormat="1">
-      <c r="A170" s="77" t="s">
+      <c r="A170" s="78" t="s">
         <v>191</v>
       </c>
-      <c r="B170" s="77"/>
-      <c r="C170" s="77"/>
-      <c r="D170" s="77"/>
-      <c r="E170" s="77"/>
-      <c r="F170" s="77"/>
-      <c r="G170" s="77"/>
+      <c r="B170" s="78"/>
+      <c r="C170" s="78"/>
+      <c r="D170" s="78"/>
+      <c r="E170" s="78"/>
+      <c r="F170" s="78"/>
+      <c r="G170" s="78"/>
       <c r="H170" s="36"/>
       <c r="I170" s="36"/>
       <c r="J170" s="36"/>
@@ -52455,43 +52458,43 @@
       <c r="F177" s="6"/>
     </row>
     <row r="178" spans="1:10" s="1" customFormat="1">
-      <c r="A178" s="76" t="s">
+      <c r="A178" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="B178" s="76"/>
-      <c r="C178" s="76"/>
-      <c r="D178" s="76"/>
-      <c r="E178" s="76"/>
-      <c r="F178" s="76"/>
-      <c r="G178" s="76"/>
+      <c r="B178" s="77"/>
+      <c r="C178" s="77"/>
+      <c r="D178" s="77"/>
+      <c r="E178" s="77"/>
+      <c r="F178" s="77"/>
+      <c r="G178" s="77"/>
       <c r="H178" s="38"/>
       <c r="I178" s="38"/>
       <c r="J178" s="38"/>
     </row>
     <row r="179" spans="1:10" s="1" customFormat="1">
-      <c r="A179" s="76" t="s">
+      <c r="A179" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="B179" s="76"/>
-      <c r="C179" s="76"/>
-      <c r="D179" s="76"/>
-      <c r="E179" s="76"/>
-      <c r="F179" s="76"/>
-      <c r="G179" s="76"/>
+      <c r="B179" s="77"/>
+      <c r="C179" s="77"/>
+      <c r="D179" s="77"/>
+      <c r="E179" s="77"/>
+      <c r="F179" s="77"/>
+      <c r="G179" s="77"/>
       <c r="H179" s="38"/>
       <c r="I179" s="38"/>
       <c r="J179" s="38"/>
     </row>
     <row r="180" spans="1:10" s="1" customFormat="1">
-      <c r="A180" s="77" t="s">
+      <c r="A180" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="B180" s="77"/>
-      <c r="C180" s="77"/>
-      <c r="D180" s="77"/>
-      <c r="E180" s="77"/>
-      <c r="F180" s="77"/>
-      <c r="G180" s="77"/>
+      <c r="B180" s="78"/>
+      <c r="C180" s="78"/>
+      <c r="D180" s="78"/>
+      <c r="E180" s="78"/>
+      <c r="F180" s="78"/>
+      <c r="G180" s="78"/>
       <c r="H180" s="36"/>
       <c r="I180" s="36"/>
       <c r="J180" s="36"/>
@@ -52686,57 +52689,57 @@
       <c r="F189" s="6"/>
     </row>
     <row r="190" spans="1:10" s="1" customFormat="1">
-      <c r="A190" s="75" t="s">
+      <c r="A190" s="76" t="s">
         <v>213</v>
       </c>
-      <c r="B190" s="75"/>
-      <c r="C190" s="75"/>
-      <c r="D190" s="75"/>
-      <c r="E190" s="75"/>
-      <c r="F190" s="75"/>
-      <c r="G190" s="75"/>
+      <c r="B190" s="76"/>
+      <c r="C190" s="76"/>
+      <c r="D190" s="76"/>
+      <c r="E190" s="76"/>
+      <c r="F190" s="76"/>
+      <c r="G190" s="76"/>
       <c r="H190" s="39"/>
       <c r="I190" s="39"/>
       <c r="J190" s="39"/>
     </row>
     <row r="191" spans="1:10" s="1" customFormat="1">
-      <c r="A191" s="76" t="s">
+      <c r="A191" s="77" t="s">
         <v>214</v>
       </c>
-      <c r="B191" s="76"/>
-      <c r="C191" s="76"/>
-      <c r="D191" s="76"/>
-      <c r="E191" s="76"/>
-      <c r="F191" s="76"/>
-      <c r="G191" s="76"/>
+      <c r="B191" s="77"/>
+      <c r="C191" s="77"/>
+      <c r="D191" s="77"/>
+      <c r="E191" s="77"/>
+      <c r="F191" s="77"/>
+      <c r="G191" s="77"/>
       <c r="H191" s="38"/>
       <c r="I191" s="38"/>
       <c r="J191" s="38"/>
     </row>
     <row r="192" spans="1:10" s="1" customFormat="1">
-      <c r="A192" s="76" t="s">
+      <c r="A192" s="77" t="s">
         <v>215</v>
       </c>
-      <c r="B192" s="76"/>
-      <c r="C192" s="76"/>
-      <c r="D192" s="76"/>
-      <c r="E192" s="76"/>
-      <c r="F192" s="76"/>
-      <c r="G192" s="76"/>
+      <c r="B192" s="77"/>
+      <c r="C192" s="77"/>
+      <c r="D192" s="77"/>
+      <c r="E192" s="77"/>
+      <c r="F192" s="77"/>
+      <c r="G192" s="77"/>
       <c r="H192" s="38"/>
       <c r="I192" s="38"/>
       <c r="J192" s="38"/>
     </row>
     <row r="193" spans="1:10" s="1" customFormat="1">
-      <c r="A193" s="77" t="s">
+      <c r="A193" s="78" t="s">
         <v>216</v>
       </c>
-      <c r="B193" s="77"/>
-      <c r="C193" s="77"/>
-      <c r="D193" s="77"/>
-      <c r="E193" s="77"/>
-      <c r="F193" s="77"/>
-      <c r="G193" s="77"/>
+      <c r="B193" s="78"/>
+      <c r="C193" s="78"/>
+      <c r="D193" s="78"/>
+      <c r="E193" s="78"/>
+      <c r="F193" s="78"/>
+      <c r="G193" s="78"/>
       <c r="H193" s="36"/>
       <c r="I193" s="36"/>
       <c r="J193" s="36"/>
@@ -52856,43 +52859,43 @@
       <c r="F199" s="6"/>
     </row>
     <row r="200" spans="1:10" s="5" customFormat="1" ht="20.25">
-      <c r="A200" s="75" t="s">
+      <c r="A200" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="B200" s="75"/>
-      <c r="C200" s="75"/>
-      <c r="D200" s="75"/>
-      <c r="E200" s="75"/>
-      <c r="F200" s="75"/>
-      <c r="G200" s="75"/>
+      <c r="B200" s="76"/>
+      <c r="C200" s="76"/>
+      <c r="D200" s="76"/>
+      <c r="E200" s="76"/>
+      <c r="F200" s="76"/>
+      <c r="G200" s="76"/>
       <c r="H200" s="39"/>
       <c r="I200" s="39"/>
       <c r="J200" s="39"/>
     </row>
     <row r="201" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A201" s="78" t="s">
+      <c r="A201" s="79" t="s">
         <v>223</v>
       </c>
-      <c r="B201" s="78"/>
-      <c r="C201" s="78"/>
-      <c r="D201" s="78"/>
-      <c r="E201" s="78"/>
-      <c r="F201" s="78"/>
-      <c r="G201" s="78"/>
+      <c r="B201" s="79"/>
+      <c r="C201" s="79"/>
+      <c r="D201" s="79"/>
+      <c r="E201" s="79"/>
+      <c r="F201" s="79"/>
+      <c r="G201" s="79"/>
       <c r="H201" s="34"/>
       <c r="I201" s="34"/>
       <c r="J201" s="34"/>
     </row>
     <row r="202" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A202" s="79" t="s">
+      <c r="A202" s="75" t="s">
         <v>131</v>
       </c>
-      <c r="B202" s="79"/>
-      <c r="C202" s="79"/>
-      <c r="D202" s="79"/>
-      <c r="E202" s="79"/>
-      <c r="F202" s="79"/>
-      <c r="G202" s="79"/>
+      <c r="B202" s="75"/>
+      <c r="C202" s="75"/>
+      <c r="D202" s="75"/>
+      <c r="E202" s="75"/>
+      <c r="F202" s="75"/>
+      <c r="G202" s="75"/>
       <c r="H202" s="33"/>
       <c r="I202" s="33"/>
       <c r="J202" s="33"/>
@@ -53076,15 +53079,15 @@
       <c r="F211" s="6"/>
     </row>
     <row r="212" spans="1:10" s="1" customFormat="1">
-      <c r="A212" s="75" t="s">
+      <c r="A212" s="76" t="s">
         <v>229</v>
       </c>
-      <c r="B212" s="75"/>
-      <c r="C212" s="75"/>
-      <c r="D212" s="75"/>
-      <c r="E212" s="75"/>
-      <c r="F212" s="75"/>
-      <c r="G212" s="75"/>
+      <c r="B212" s="76"/>
+      <c r="C212" s="76"/>
+      <c r="D212" s="76"/>
+      <c r="E212" s="76"/>
+      <c r="F212" s="76"/>
+      <c r="G212" s="76"/>
       <c r="H212" s="39"/>
       <c r="I212" s="39"/>
       <c r="J212" s="39"/>
@@ -53148,15 +53151,15 @@
       <c r="F215" s="6"/>
     </row>
     <row r="216" spans="1:10" s="1" customFormat="1">
-      <c r="A216" s="77" t="s">
+      <c r="A216" s="78" t="s">
         <v>231</v>
       </c>
-      <c r="B216" s="77"/>
-      <c r="C216" s="77"/>
-      <c r="D216" s="77"/>
-      <c r="E216" s="77"/>
-      <c r="F216" s="77"/>
-      <c r="G216" s="77"/>
+      <c r="B216" s="78"/>
+      <c r="C216" s="78"/>
+      <c r="D216" s="78"/>
+      <c r="E216" s="78"/>
+      <c r="F216" s="78"/>
+      <c r="G216" s="78"/>
       <c r="H216" s="36"/>
       <c r="I216" s="36"/>
       <c r="J216" s="36"/>
@@ -53224,15 +53227,15 @@
       <c r="F219" s="6"/>
     </row>
     <row r="220" spans="1:10" s="1" customFormat="1">
-      <c r="A220" s="76" t="s">
+      <c r="A220" s="77" t="s">
         <v>236</v>
       </c>
-      <c r="B220" s="76"/>
-      <c r="C220" s="76"/>
-      <c r="D220" s="76"/>
-      <c r="E220" s="76"/>
-      <c r="F220" s="76"/>
-      <c r="G220" s="76"/>
+      <c r="B220" s="77"/>
+      <c r="C220" s="77"/>
+      <c r="D220" s="77"/>
+      <c r="E220" s="77"/>
+      <c r="F220" s="77"/>
+      <c r="G220" s="77"/>
       <c r="H220" s="38"/>
       <c r="I220" s="38"/>
       <c r="J220" s="38"/>
@@ -53314,29 +53317,29 @@
       <c r="F224" s="6"/>
     </row>
     <row r="225" spans="1:10" s="1" customFormat="1">
-      <c r="A225" s="77" t="s">
+      <c r="A225" s="78" t="s">
         <v>238</v>
       </c>
-      <c r="B225" s="77"/>
-      <c r="C225" s="77"/>
-      <c r="D225" s="77"/>
-      <c r="E225" s="77"/>
-      <c r="F225" s="77"/>
-      <c r="G225" s="77"/>
+      <c r="B225" s="78"/>
+      <c r="C225" s="78"/>
+      <c r="D225" s="78"/>
+      <c r="E225" s="78"/>
+      <c r="F225" s="78"/>
+      <c r="G225" s="78"/>
       <c r="H225" s="36"/>
       <c r="I225" s="36"/>
       <c r="J225" s="36"/>
     </row>
     <row r="226" spans="1:10" s="1" customFormat="1">
-      <c r="A226" s="77" t="s">
+      <c r="A226" s="78" t="s">
         <v>239</v>
       </c>
-      <c r="B226" s="77"/>
-      <c r="C226" s="77"/>
-      <c r="D226" s="77"/>
-      <c r="E226" s="77"/>
-      <c r="F226" s="77"/>
-      <c r="G226" s="77"/>
+      <c r="B226" s="78"/>
+      <c r="C226" s="78"/>
+      <c r="D226" s="78"/>
+      <c r="E226" s="78"/>
+      <c r="F226" s="78"/>
+      <c r="G226" s="78"/>
       <c r="H226" s="36"/>
       <c r="I226" s="36"/>
       <c r="J226" s="36"/>
@@ -53436,15 +53439,15 @@
       <c r="F231" s="6"/>
     </row>
     <row r="232" spans="1:10" s="7" customFormat="1">
-      <c r="A232" s="75" t="s">
+      <c r="A232" s="76" t="s">
         <v>241</v>
       </c>
-      <c r="B232" s="75"/>
-      <c r="C232" s="75"/>
-      <c r="D232" s="75"/>
-      <c r="E232" s="75"/>
-      <c r="F232" s="75"/>
-      <c r="G232" s="75"/>
+      <c r="B232" s="76"/>
+      <c r="C232" s="76"/>
+      <c r="D232" s="76"/>
+      <c r="E232" s="76"/>
+      <c r="F232" s="76"/>
+      <c r="G232" s="76"/>
       <c r="H232" s="39"/>
       <c r="I232" s="39"/>
       <c r="J232" s="39"/>
@@ -53490,43 +53493,43 @@
       <c r="F234" s="6"/>
     </row>
     <row r="235" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A235" s="78" t="s">
+      <c r="A235" s="79" t="s">
         <v>243</v>
       </c>
-      <c r="B235" s="78"/>
-      <c r="C235" s="78"/>
-      <c r="D235" s="78"/>
-      <c r="E235" s="78"/>
-      <c r="F235" s="78"/>
-      <c r="G235" s="78"/>
+      <c r="B235" s="79"/>
+      <c r="C235" s="79"/>
+      <c r="D235" s="79"/>
+      <c r="E235" s="79"/>
+      <c r="F235" s="79"/>
+      <c r="G235" s="79"/>
       <c r="H235" s="34"/>
       <c r="I235" s="34"/>
       <c r="J235" s="34"/>
     </row>
     <row r="236" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A236" s="79" t="s">
+      <c r="A236" s="75" t="s">
         <v>131</v>
       </c>
-      <c r="B236" s="79"/>
-      <c r="C236" s="79"/>
-      <c r="D236" s="79"/>
-      <c r="E236" s="79"/>
-      <c r="F236" s="79"/>
-      <c r="G236" s="79"/>
+      <c r="B236" s="75"/>
+      <c r="C236" s="75"/>
+      <c r="D236" s="75"/>
+      <c r="E236" s="75"/>
+      <c r="F236" s="75"/>
+      <c r="G236" s="75"/>
       <c r="H236" s="33"/>
       <c r="I236" s="33"/>
       <c r="J236" s="33"/>
     </row>
     <row r="237" spans="1:10" s="1" customFormat="1">
-      <c r="A237" s="77" t="s">
+      <c r="A237" s="78" t="s">
         <v>244</v>
       </c>
-      <c r="B237" s="77"/>
-      <c r="C237" s="77"/>
-      <c r="D237" s="77"/>
-      <c r="E237" s="77"/>
-      <c r="F237" s="77"/>
-      <c r="G237" s="77"/>
+      <c r="B237" s="78"/>
+      <c r="C237" s="78"/>
+      <c r="D237" s="78"/>
+      <c r="E237" s="78"/>
+      <c r="F237" s="78"/>
+      <c r="G237" s="78"/>
       <c r="H237" s="36"/>
       <c r="I237" s="36"/>
       <c r="J237" s="36"/>
@@ -53586,15 +53589,15 @@
       <c r="F240" s="6"/>
     </row>
     <row r="241" spans="1:10" s="1" customFormat="1">
-      <c r="A241" s="77" t="s">
+      <c r="A241" s="78" t="s">
         <v>245</v>
       </c>
-      <c r="B241" s="77"/>
-      <c r="C241" s="77"/>
-      <c r="D241" s="77"/>
-      <c r="E241" s="77"/>
-      <c r="F241" s="77"/>
-      <c r="G241" s="77"/>
+      <c r="B241" s="78"/>
+      <c r="C241" s="78"/>
+      <c r="D241" s="78"/>
+      <c r="E241" s="78"/>
+      <c r="F241" s="78"/>
+      <c r="G241" s="78"/>
       <c r="H241" s="36"/>
       <c r="I241" s="36"/>
       <c r="J241" s="36"/>
@@ -53619,115 +53622,115 @@
     </row>
     <row r="243" spans="1:10" s="1" customFormat="1">
       <c r="A243" s="1" t="s">
-        <v>22</v>
+        <v>246</v>
       </c>
       <c r="B243" s="13">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F243" s="6"/>
     </row>
     <row r="244" spans="1:10" s="1" customFormat="1">
-      <c r="A244" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B244" s="11">
-        <v>46212</v>
+      <c r="A244" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B244" s="13">
+        <v>46211</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E244" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F244" s="6"/>
     </row>
     <row r="245" spans="1:10" s="1" customFormat="1">
-      <c r="A245" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="B245" s="24">
-        <v>46213</v>
-      </c>
-      <c r="C245" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D245" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E245" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F245" s="25"/>
-      <c r="G245" s="23"/>
-      <c r="H245" s="37"/>
-      <c r="I245" s="37"/>
-      <c r="J245" s="37"/>
+      <c r="A245" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B245" s="11">
+        <v>46212</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E245" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F245" s="6"/>
     </row>
     <row r="246" spans="1:10" s="1" customFormat="1">
-      <c r="A246" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B246" s="13">
-        <v>46216</v>
-      </c>
-      <c r="C246" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E246" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F246" s="6"/>
+      <c r="A246" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="B246" s="24">
+        <v>46213</v>
+      </c>
+      <c r="C246" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D246" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E246" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F246" s="25"/>
+      <c r="G246" s="23"/>
+      <c r="H246" s="37"/>
+      <c r="I246" s="37"/>
+      <c r="J246" s="37"/>
     </row>
     <row r="247" spans="1:10" s="1" customFormat="1">
-      <c r="A247" s="76" t="s">
-        <v>247</v>
-      </c>
-      <c r="B247" s="76"/>
-      <c r="C247" s="76"/>
-      <c r="D247" s="76"/>
-      <c r="E247" s="76"/>
-      <c r="F247" s="76"/>
-      <c r="G247" s="76"/>
-      <c r="H247" s="38"/>
-      <c r="I247" s="38"/>
-      <c r="J247" s="38"/>
+      <c r="A247" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B247" s="13">
+        <v>46216</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F247" s="6"/>
     </row>
     <row r="248" spans="1:10" s="1" customFormat="1">
-      <c r="A248" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B248" s="13">
-        <v>46218</v>
-      </c>
-      <c r="C248" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E248" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F248" s="6"/>
+      <c r="A248" s="77" t="s">
+        <v>248</v>
+      </c>
+      <c r="B248" s="77"/>
+      <c r="C248" s="77"/>
+      <c r="D248" s="77"/>
+      <c r="E248" s="77"/>
+      <c r="F248" s="77"/>
+      <c r="G248" s="77"/>
+      <c r="H248" s="38"/>
+      <c r="I248" s="38"/>
+      <c r="J248" s="38"/>
     </row>
     <row r="249" spans="1:10" s="1" customFormat="1">
-      <c r="A249" s="9" t="s">
-        <v>28</v>
+      <c r="A249" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B249" s="13">
         <v>46218</v>
@@ -53736,22 +53739,22 @@
         <v>14</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E249" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F249" s="6"/>
     </row>
     <row r="250" spans="1:10" s="1" customFormat="1">
-      <c r="A250" s="10" t="s">
-        <v>24</v>
+      <c r="A250" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B250" s="13">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>15</v>
@@ -53762,57 +53765,57 @@
       <c r="F250" s="6"/>
     </row>
     <row r="251" spans="1:10" s="1" customFormat="1">
-      <c r="A251" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="B251" s="24">
-        <v>46223</v>
-      </c>
-      <c r="C251" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D251" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E251" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F251" s="25"/>
-      <c r="G251" s="23"/>
-      <c r="H251" s="37"/>
-      <c r="I251" s="37"/>
-      <c r="J251" s="37"/>
+      <c r="A251" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B251" s="13">
+        <v>46219</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E251" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F251" s="6"/>
     </row>
     <row r="252" spans="1:10" s="1" customFormat="1">
-      <c r="A252" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B252" s="13">
+      <c r="A252" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="B252" s="24">
         <v>46223</v>
       </c>
-      <c r="C252" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E252" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F252" s="6"/>
+      <c r="C252" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D252" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E252" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F252" s="25"/>
+      <c r="G252" s="23"/>
+      <c r="H252" s="37"/>
+      <c r="I252" s="37"/>
+      <c r="J252" s="37"/>
     </row>
     <row r="253" spans="1:10" s="1" customFormat="1">
       <c r="A253" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B253" s="13">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="C253" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>16</v>
@@ -53820,112 +53823,108 @@
       <c r="F253" s="6"/>
     </row>
     <row r="254" spans="1:10" s="1" customFormat="1">
-      <c r="A254" s="76" t="s">
-        <v>249</v>
-      </c>
-      <c r="B254" s="76"/>
-      <c r="C254" s="76"/>
-      <c r="D254" s="76"/>
-      <c r="E254" s="76"/>
-      <c r="F254" s="76"/>
-      <c r="G254" s="76"/>
-      <c r="H254" s="38"/>
-      <c r="I254" s="38"/>
-      <c r="J254" s="38"/>
+      <c r="A254" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B254" s="13">
+        <v>46225</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F254" s="6"/>
     </row>
     <row r="255" spans="1:10" s="1" customFormat="1">
-      <c r="A255" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B255" s="11">
-        <v>46226</v>
-      </c>
-      <c r="C255" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E255" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F255" s="6"/>
+      <c r="A255" s="77" t="s">
+        <v>250</v>
+      </c>
+      <c r="B255" s="77"/>
+      <c r="C255" s="77"/>
+      <c r="D255" s="77"/>
+      <c r="E255" s="77"/>
+      <c r="F255" s="77"/>
+      <c r="G255" s="77"/>
+      <c r="H255" s="38"/>
+      <c r="I255" s="38"/>
+      <c r="J255" s="38"/>
     </row>
     <row r="256" spans="1:10" s="1" customFormat="1">
-      <c r="A256" s="75" t="s">
-        <v>250</v>
-      </c>
-      <c r="B256" s="75"/>
-      <c r="C256" s="75"/>
-      <c r="D256" s="75"/>
-      <c r="E256" s="75"/>
-      <c r="F256" s="75"/>
-      <c r="G256" s="75"/>
-      <c r="H256" s="39"/>
-      <c r="I256" s="39"/>
-      <c r="J256" s="39"/>
+      <c r="A256" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B256" s="11">
+        <v>46226</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E256" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F256" s="6"/>
     </row>
     <row r="257" spans="1:10" s="1" customFormat="1">
-      <c r="A257" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B257" s="13">
-        <v>46230</v>
-      </c>
-      <c r="C257" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E257" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F257" s="6"/>
+      <c r="A257" s="76" t="s">
+        <v>251</v>
+      </c>
+      <c r="B257" s="76"/>
+      <c r="C257" s="76"/>
+      <c r="D257" s="76"/>
+      <c r="E257" s="76"/>
+      <c r="F257" s="76"/>
+      <c r="G257" s="76"/>
+      <c r="H257" s="39"/>
+      <c r="I257" s="39"/>
+      <c r="J257" s="39"/>
     </row>
     <row r="258" spans="1:10" s="1" customFormat="1">
       <c r="A258" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B258" s="13">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F258" s="6"/>
     </row>
-    <row r="259" spans="1:10" s="7" customFormat="1">
+    <row r="259" spans="1:10" s="1" customFormat="1">
       <c r="A259" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B259" s="13">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F259" s="6"/>
-      <c r="G259" s="1"/>
-      <c r="H259" s="40"/>
-      <c r="I259" s="40"/>
-      <c r="J259" s="40"/>
     </row>
     <row r="260" spans="1:10" s="7" customFormat="1">
-      <c r="A260" s="9" t="s">
-        <v>28</v>
+      <c r="A260" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B260" s="13">
         <v>46232</v>
@@ -53934,10 +53933,10 @@
         <v>14</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E260" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F260" s="6"/>
       <c r="G260" s="1"/>
@@ -53945,15 +53944,15 @@
       <c r="I260" s="40"/>
       <c r="J260" s="40"/>
     </row>
-    <row r="261" spans="1:10" s="5" customFormat="1" ht="20.25">
-      <c r="A261" s="10" t="s">
-        <v>24</v>
+    <row r="261" spans="1:10" s="7" customFormat="1">
+      <c r="A261" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B261" s="13">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>15</v>
@@ -53961,39 +53960,47 @@
       <c r="E261" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F261" s="65"/>
-      <c r="G261" s="7"/>
-      <c r="H261" s="42"/>
-      <c r="I261" s="42"/>
-      <c r="J261" s="42"/>
+      <c r="F261" s="6"/>
+      <c r="G261" s="1"/>
+      <c r="H261" s="40"/>
+      <c r="I261" s="40"/>
+      <c r="J261" s="40"/>
     </row>
-    <row r="262" spans="1:10" s="1" customFormat="1">
-      <c r="A262" s="9"/>
-      <c r="B262" s="13"/>
-      <c r="C262" s="8"/>
-      <c r="F262" s="6"/>
+    <row r="262" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A262" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B262" s="13">
+        <v>46233</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E262" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F262" s="65"/>
       <c r="G262" s="7"/>
       <c r="H262" s="42"/>
       <c r="I262" s="42"/>
       <c r="J262" s="42"/>
     </row>
-    <row r="263" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A263" s="78" t="s">
-        <v>251</v>
-      </c>
-      <c r="B263" s="78"/>
-      <c r="C263" s="78"/>
-      <c r="D263" s="78"/>
-      <c r="E263" s="78"/>
-      <c r="F263" s="78"/>
-      <c r="G263" s="78"/>
-      <c r="H263" s="34"/>
-      <c r="I263" s="34"/>
-      <c r="J263" s="34"/>
+    <row r="263" spans="1:10" s="1" customFormat="1">
+      <c r="A263" s="9"/>
+      <c r="B263" s="13"/>
+      <c r="C263" s="8"/>
+      <c r="F263" s="6"/>
+      <c r="G263" s="7"/>
+      <c r="H263" s="42"/>
+      <c r="I263" s="42"/>
+      <c r="J263" s="42"/>
     </row>
-    <row r="264" spans="1:10" s="5" customFormat="1" ht="19.5">
+    <row r="264" spans="1:10" s="1" customFormat="1" ht="19.5">
       <c r="A264" s="79" t="s">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="B264" s="79"/>
       <c r="C264" s="79"/>
@@ -54001,13 +54008,13 @@
       <c r="E264" s="79"/>
       <c r="F264" s="79"/>
       <c r="G264" s="79"/>
-      <c r="H264" s="33"/>
-      <c r="I264" s="33"/>
-      <c r="J264" s="33"/>
+      <c r="H264" s="34"/>
+      <c r="I264" s="34"/>
+      <c r="J264" s="34"/>
     </row>
-    <row r="265" spans="1:10" s="1" customFormat="1">
+    <row r="265" spans="1:10" s="5" customFormat="1" ht="19.5">
       <c r="A265" s="75" t="s">
-        <v>252</v>
+        <v>131</v>
       </c>
       <c r="B265" s="75"/>
       <c r="C265" s="75"/>
@@ -54015,70 +54022,66 @@
       <c r="E265" s="75"/>
       <c r="F265" s="75"/>
       <c r="G265" s="75"/>
-      <c r="H265" s="39"/>
-      <c r="I265" s="39"/>
-      <c r="J265" s="39"/>
+      <c r="H265" s="33"/>
+      <c r="I265" s="33"/>
+      <c r="J265" s="33"/>
     </row>
     <row r="266" spans="1:10" s="1" customFormat="1">
-      <c r="A266" s="77" t="s">
+      <c r="A266" s="76" t="s">
         <v>253</v>
       </c>
-      <c r="B266" s="77"/>
-      <c r="C266" s="77"/>
-      <c r="D266" s="77"/>
-      <c r="E266" s="77"/>
-      <c r="F266" s="77"/>
-      <c r="G266" s="77"/>
-      <c r="H266" s="36"/>
-      <c r="I266" s="36"/>
-      <c r="J266" s="36"/>
+      <c r="B266" s="76"/>
+      <c r="C266" s="76"/>
+      <c r="D266" s="76"/>
+      <c r="E266" s="76"/>
+      <c r="F266" s="76"/>
+      <c r="G266" s="76"/>
+      <c r="H266" s="39"/>
+      <c r="I266" s="39"/>
+      <c r="J266" s="39"/>
     </row>
     <row r="267" spans="1:10" s="1" customFormat="1">
-      <c r="A267" s="23" t="s">
+      <c r="A267" s="78" t="s">
         <v>254</v>
       </c>
-      <c r="B267" s="24">
-        <v>46235</v>
-      </c>
-      <c r="C267" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D267" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E267" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F267" s="26"/>
-      <c r="G267" s="26"/>
-      <c r="H267" s="41"/>
-      <c r="I267" s="41"/>
-      <c r="J267" s="41"/>
+      <c r="B267" s="78"/>
+      <c r="C267" s="78"/>
+      <c r="D267" s="78"/>
+      <c r="E267" s="78"/>
+      <c r="F267" s="78"/>
+      <c r="G267" s="78"/>
+      <c r="H267" s="36"/>
+      <c r="I267" s="36"/>
+      <c r="J267" s="36"/>
     </row>
     <row r="268" spans="1:10" s="1" customFormat="1">
-      <c r="A268" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B268" s="13">
-        <v>46237</v>
-      </c>
-      <c r="C268" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E268" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F268" s="6"/>
+      <c r="A268" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B268" s="24">
+        <v>46235</v>
+      </c>
+      <c r="C268" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D268" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E268" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F268" s="26"/>
+      <c r="G268" s="26"/>
+      <c r="H268" s="41"/>
+      <c r="I268" s="41"/>
+      <c r="J268" s="41"/>
     </row>
     <row r="269" spans="1:10" s="1" customFormat="1">
       <c r="A269" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B269" s="13">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="C269" s="6" t="s">
         <v>14</v>
@@ -54086,20 +54089,20 @@
       <c r="D269" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E269" s="7" t="s">
-        <v>26</v>
+      <c r="E269" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F269" s="6"/>
     </row>
     <row r="270" spans="1:10" s="1" customFormat="1">
-      <c r="A270" s="9" t="s">
-        <v>24</v>
+      <c r="A270" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B270" s="13">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>15</v>
@@ -54110,29 +54113,29 @@
       <c r="F270" s="6"/>
     </row>
     <row r="271" spans="1:10" s="1" customFormat="1">
-      <c r="A271" s="1" t="s">
-        <v>13</v>
+      <c r="A271" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="B271" s="13">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E271" s="1" t="s">
-        <v>16</v>
+      <c r="E271" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F271" s="6"/>
     </row>
     <row r="272" spans="1:10" s="1" customFormat="1">
       <c r="A272" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B272" s="13">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="C272" s="6" t="s">
         <v>14</v>
@@ -54140,14 +54143,14 @@
       <c r="D272" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E272" s="7" t="s">
-        <v>26</v>
+      <c r="E272" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F272" s="6"/>
     </row>
     <row r="273" spans="1:10" s="1" customFormat="1">
-      <c r="A273" s="9" t="s">
-        <v>28</v>
+      <c r="A273" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B273" s="13">
         <v>46246</v>
@@ -54164,14 +54167,14 @@
       <c r="F273" s="6"/>
     </row>
     <row r="274" spans="1:10" s="1" customFormat="1">
-      <c r="A274" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B274" s="11">
-        <v>46247</v>
+      <c r="A274" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B274" s="13">
+        <v>46246</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>15</v>
@@ -54182,65 +54185,65 @@
       <c r="F274" s="6"/>
     </row>
     <row r="275" spans="1:10" s="1" customFormat="1">
-      <c r="A275" s="76" t="s">
-        <v>255</v>
-      </c>
-      <c r="B275" s="76"/>
-      <c r="C275" s="76"/>
-      <c r="D275" s="76"/>
-      <c r="E275" s="76"/>
-      <c r="F275" s="76"/>
-      <c r="G275" s="76"/>
-      <c r="H275" s="38"/>
-      <c r="I275" s="38"/>
-      <c r="J275" s="38"/>
+      <c r="A275" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B275" s="11">
+        <v>46247</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E275" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F275" s="6"/>
     </row>
     <row r="276" spans="1:10" s="1" customFormat="1">
-      <c r="A276" s="23" t="s">
+      <c r="A276" s="77" t="s">
         <v>256</v>
       </c>
-      <c r="B276" s="24">
-        <v>46249</v>
-      </c>
-      <c r="C276" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D276" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E276" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F276" s="26"/>
-      <c r="G276" s="26"/>
-      <c r="H276" s="41"/>
-      <c r="I276" s="41"/>
-      <c r="J276" s="41"/>
+      <c r="B276" s="77"/>
+      <c r="C276" s="77"/>
+      <c r="D276" s="77"/>
+      <c r="E276" s="77"/>
+      <c r="F276" s="77"/>
+      <c r="G276" s="77"/>
+      <c r="H276" s="38"/>
+      <c r="I276" s="38"/>
+      <c r="J276" s="38"/>
     </row>
     <row r="277" spans="1:10" s="1" customFormat="1">
-      <c r="A277" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B277" s="13">
-        <v>46251</v>
-      </c>
-      <c r="C277" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E277" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F277" s="6"/>
+      <c r="A277" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="B277" s="24">
+        <v>46249</v>
+      </c>
+      <c r="C277" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D277" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E277" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F277" s="26"/>
+      <c r="G277" s="26"/>
+      <c r="H277" s="41"/>
+      <c r="I277" s="41"/>
+      <c r="J277" s="41"/>
     </row>
     <row r="278" spans="1:10" s="1" customFormat="1">
       <c r="A278" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B278" s="13">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="C278" s="6" t="s">
         <v>14</v>
@@ -54248,20 +54251,20 @@
       <c r="D278" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E278" s="7" t="s">
-        <v>26</v>
+      <c r="E278" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F278" s="6"/>
     </row>
     <row r="279" spans="1:10" s="1" customFormat="1">
-      <c r="A279" s="9" t="s">
-        <v>24</v>
+      <c r="A279" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B279" s="13">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>15</v>
@@ -54272,62 +54275,62 @@
       <c r="F279" s="6"/>
     </row>
     <row r="280" spans="1:10" s="1" customFormat="1">
-      <c r="A280" s="1" t="s">
-        <v>13</v>
+      <c r="A280" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="B280" s="13">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E280" s="1" t="s">
-        <v>16</v>
+      <c r="E280" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F280" s="6"/>
     </row>
     <row r="281" spans="1:10" s="1" customFormat="1">
       <c r="A281" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B281" s="13">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F281" s="6"/>
     </row>
     <row r="282" spans="1:10" s="1" customFormat="1">
       <c r="A282" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B282" s="13">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E282" s="7" t="s">
-        <v>26</v>
+      <c r="E282" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F282" s="6"/>
     </row>
     <row r="283" spans="1:10" s="1" customFormat="1">
-      <c r="A283" s="9" t="s">
-        <v>28</v>
+      <c r="A283" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B283" s="13">
         <v>46260</v>
@@ -54344,26 +54347,22 @@
       <c r="F283" s="6"/>
     </row>
     <row r="284" spans="1:10" s="1" customFormat="1">
-      <c r="A284" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="B284" s="24">
-        <v>46261</v>
-      </c>
-      <c r="C284" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D284" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E284" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="F284" s="25"/>
-      <c r="G284" s="23"/>
-      <c r="H284" s="37"/>
-      <c r="I284" s="37"/>
-      <c r="J284" s="37"/>
+      <c r="A284" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B284" s="13">
+        <v>46260</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E284" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F284" s="6"/>
     </row>
     <row r="285" spans="1:10" s="1" customFormat="1">
       <c r="A285" s="23" t="s">
@@ -54379,7 +54378,7 @@
         <v>19</v>
       </c>
       <c r="E285" s="23" t="s">
-        <v>259</v>
+        <v>172</v>
       </c>
       <c r="F285" s="25"/>
       <c r="G285" s="23"/>
@@ -54388,88 +54387,96 @@
       <c r="J285" s="37"/>
     </row>
     <row r="286" spans="1:10" s="1" customFormat="1">
-      <c r="A286" s="10" t="s">
+      <c r="A286" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="B286" s="24">
+        <v>46261</v>
+      </c>
+      <c r="C286" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D286" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E286" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="F286" s="25"/>
+      <c r="G286" s="23"/>
+      <c r="H286" s="37"/>
+      <c r="I286" s="37"/>
+      <c r="J286" s="37"/>
+    </row>
+    <row r="287" spans="1:10" s="1" customFormat="1">
+      <c r="A287" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B286" s="11">
+      <c r="B287" s="11">
         <v>46261</v>
       </c>
-      <c r="C286" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E286" s="7" t="s">
+      <c r="C287" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E287" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F286" s="6"/>
+      <c r="F287" s="6"/>
     </row>
-    <row r="287" spans="1:10" s="7" customFormat="1">
-      <c r="A287" s="77" t="s">
-        <v>260</v>
-      </c>
-      <c r="B287" s="77"/>
-      <c r="C287" s="77"/>
-      <c r="D287" s="77"/>
-      <c r="E287" s="77"/>
-      <c r="F287" s="77"/>
-      <c r="G287" s="77"/>
-      <c r="H287" s="36"/>
-      <c r="I287" s="36"/>
-      <c r="J287" s="36"/>
+    <row r="288" spans="1:10" s="7" customFormat="1">
+      <c r="A288" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="B288" s="78"/>
+      <c r="C288" s="78"/>
+      <c r="D288" s="78"/>
+      <c r="E288" s="78"/>
+      <c r="F288" s="78"/>
+      <c r="G288" s="78"/>
+      <c r="H288" s="36"/>
+      <c r="I288" s="36"/>
+      <c r="J288" s="36"/>
     </row>
-    <row r="288" spans="1:10" s="5" customFormat="1" ht="20.25">
-      <c r="A288" s="1" t="s">
+    <row r="289" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A289" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B288" s="13">
+      <c r="B289" s="13">
         <v>46265</v>
       </c>
-      <c r="C288" s="6" t="s">
+      <c r="C289" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D288" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E288" s="1" t="s">
+      <c r="D289" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E289" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F288" s="6"/>
-      <c r="G288" s="1"/>
-      <c r="H288" s="40"/>
-      <c r="I288" s="40"/>
-      <c r="J288" s="40"/>
+      <c r="F289" s="6"/>
+      <c r="G289" s="1"/>
+      <c r="H289" s="40"/>
+      <c r="I289" s="40"/>
+      <c r="J289" s="40"/>
     </row>
-    <row r="289" spans="1:10" s="1" customFormat="1">
-      <c r="A289" s="16"/>
-      <c r="B289" s="12"/>
-      <c r="C289" s="12"/>
-      <c r="D289" s="7"/>
-      <c r="E289" s="7"/>
-      <c r="F289" s="65"/>
-      <c r="G289" s="7"/>
-      <c r="H289" s="42"/>
-      <c r="I289" s="42"/>
-      <c r="J289" s="42"/>
+    <row r="290" spans="1:10" s="1" customFormat="1">
+      <c r="A290" s="16"/>
+      <c r="B290" s="12"/>
+      <c r="C290" s="12"/>
+      <c r="D290" s="7"/>
+      <c r="E290" s="7"/>
+      <c r="F290" s="65"/>
+      <c r="G290" s="7"/>
+      <c r="H290" s="42"/>
+      <c r="I290" s="42"/>
+      <c r="J290" s="42"/>
     </row>
-    <row r="290" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A290" s="78" t="s">
-        <v>261</v>
-      </c>
-      <c r="B290" s="78"/>
-      <c r="C290" s="78"/>
-      <c r="D290" s="78"/>
-      <c r="E290" s="78"/>
-      <c r="F290" s="78"/>
-      <c r="G290" s="78"/>
-      <c r="H290" s="34"/>
-      <c r="I290" s="34"/>
-      <c r="J290" s="34"/>
-    </row>
-    <row r="291" spans="1:10" s="5" customFormat="1" ht="19.5">
+    <row r="291" spans="1:10" s="1" customFormat="1" ht="19.5">
       <c r="A291" s="79" t="s">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="B291" s="79"/>
       <c r="C291" s="79"/>
@@ -54477,37 +54484,33 @@
       <c r="E291" s="79"/>
       <c r="F291" s="79"/>
       <c r="G291" s="79"/>
-      <c r="H291" s="33"/>
-      <c r="I291" s="33"/>
-      <c r="J291" s="33"/>
+      <c r="H291" s="34"/>
+      <c r="I291" s="34"/>
+      <c r="J291" s="34"/>
     </row>
-    <row r="292" spans="1:10" s="1" customFormat="1">
-      <c r="A292" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B292" s="13">
-        <v>46267</v>
-      </c>
-      <c r="C292" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E292" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F292" s="6"/>
+    <row r="292" spans="1:10" s="5" customFormat="1" ht="19.5">
+      <c r="A292" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B292" s="75"/>
+      <c r="C292" s="75"/>
+      <c r="D292" s="75"/>
+      <c r="E292" s="75"/>
+      <c r="F292" s="75"/>
+      <c r="G292" s="75"/>
+      <c r="H292" s="33"/>
+      <c r="I292" s="33"/>
+      <c r="J292" s="33"/>
     </row>
     <row r="293" spans="1:10" s="1" customFormat="1">
-      <c r="A293" s="9" t="s">
-        <v>24</v>
+      <c r="A293" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B293" s="13">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>15</v>
@@ -54518,86 +54521,86 @@
       <c r="F293" s="6"/>
     </row>
     <row r="294" spans="1:10" s="1" customFormat="1">
-      <c r="A294" s="77" t="s">
-        <v>262</v>
-      </c>
-      <c r="B294" s="77"/>
-      <c r="C294" s="77"/>
-      <c r="D294" s="77"/>
-      <c r="E294" s="77"/>
-      <c r="F294" s="77"/>
-      <c r="G294" s="77"/>
-      <c r="H294" s="36"/>
-      <c r="I294" s="36"/>
-      <c r="J294" s="36"/>
+      <c r="A294" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B294" s="13">
+        <v>46268</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E294" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F294" s="6"/>
     </row>
     <row r="295" spans="1:10" s="1" customFormat="1">
-      <c r="A295" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B295" s="13">
-        <v>46272</v>
-      </c>
-      <c r="C295" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E295" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F295" s="6"/>
+      <c r="A295" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="B295" s="78"/>
+      <c r="C295" s="78"/>
+      <c r="D295" s="78"/>
+      <c r="E295" s="78"/>
+      <c r="F295" s="78"/>
+      <c r="G295" s="78"/>
+      <c r="H295" s="36"/>
+      <c r="I295" s="36"/>
+      <c r="J295" s="36"/>
     </row>
     <row r="296" spans="1:10" s="1" customFormat="1">
-      <c r="A296" s="75" t="s">
-        <v>263</v>
-      </c>
-      <c r="B296" s="75"/>
-      <c r="C296" s="75"/>
-      <c r="D296" s="75"/>
-      <c r="E296" s="75"/>
-      <c r="F296" s="75"/>
-      <c r="G296" s="75"/>
-      <c r="H296" s="39"/>
-      <c r="I296" s="39"/>
-      <c r="J296" s="39"/>
+      <c r="A296" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B296" s="13">
+        <v>46272</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F296" s="6"/>
     </row>
     <row r="297" spans="1:10" s="1" customFormat="1">
-      <c r="A297" s="75" t="s">
+      <c r="A297" s="76" t="s">
         <v>264</v>
       </c>
-      <c r="B297" s="75"/>
-      <c r="C297" s="75"/>
-      <c r="D297" s="75"/>
-      <c r="E297" s="75"/>
-      <c r="F297" s="75"/>
-      <c r="G297" s="75"/>
+      <c r="B297" s="76"/>
+      <c r="C297" s="76"/>
+      <c r="D297" s="76"/>
+      <c r="E297" s="76"/>
+      <c r="F297" s="76"/>
+      <c r="G297" s="76"/>
       <c r="H297" s="39"/>
       <c r="I297" s="39"/>
       <c r="J297" s="39"/>
     </row>
     <row r="298" spans="1:10" s="1" customFormat="1">
-      <c r="A298" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B298" s="13">
-        <v>46274</v>
-      </c>
-      <c r="C298" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E298" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F298" s="6"/>
+      <c r="A298" s="76" t="s">
+        <v>265</v>
+      </c>
+      <c r="B298" s="76"/>
+      <c r="C298" s="76"/>
+      <c r="D298" s="76"/>
+      <c r="E298" s="76"/>
+      <c r="F298" s="76"/>
+      <c r="G298" s="76"/>
+      <c r="H298" s="39"/>
+      <c r="I298" s="39"/>
+      <c r="J298" s="39"/>
     </row>
     <row r="299" spans="1:10" s="1" customFormat="1">
-      <c r="A299" s="9" t="s">
-        <v>28</v>
+      <c r="A299" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B299" s="13">
         <v>46274</v>
@@ -54614,14 +54617,14 @@
       <c r="F299" s="6"/>
     </row>
     <row r="300" spans="1:10" s="1" customFormat="1">
-      <c r="A300" s="10" t="s">
-        <v>24</v>
+      <c r="A300" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B300" s="13">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>15</v>
@@ -54632,86 +54635,86 @@
       <c r="F300" s="6"/>
     </row>
     <row r="301" spans="1:10" s="1" customFormat="1">
-      <c r="A301" s="76" t="s">
-        <v>265</v>
-      </c>
-      <c r="B301" s="76"/>
-      <c r="C301" s="76"/>
-      <c r="D301" s="76"/>
-      <c r="E301" s="76"/>
-      <c r="F301" s="76"/>
-      <c r="G301" s="76"/>
-      <c r="H301" s="38"/>
-      <c r="I301" s="38"/>
-      <c r="J301" s="38"/>
+      <c r="A301" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B301" s="13">
+        <v>46275</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E301" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F301" s="6"/>
     </row>
     <row r="302" spans="1:10" s="1" customFormat="1">
-      <c r="A302" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B302" s="13">
-        <v>46279</v>
-      </c>
-      <c r="C302" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E302" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F302" s="6"/>
+      <c r="A302" s="77" t="s">
+        <v>266</v>
+      </c>
+      <c r="B302" s="77"/>
+      <c r="C302" s="77"/>
+      <c r="D302" s="77"/>
+      <c r="E302" s="77"/>
+      <c r="F302" s="77"/>
+      <c r="G302" s="77"/>
+      <c r="H302" s="38"/>
+      <c r="I302" s="38"/>
+      <c r="J302" s="38"/>
     </row>
     <row r="303" spans="1:10" s="1" customFormat="1">
-      <c r="A303" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="B303" s="24">
-        <v>46280</v>
-      </c>
-      <c r="C303" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D303" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E303" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F303" s="25"/>
-      <c r="G303" s="23"/>
-      <c r="H303" s="37"/>
-      <c r="I303" s="37"/>
-      <c r="J303" s="37"/>
+      <c r="A303" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B303" s="13">
+        <v>46279</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F303" s="6"/>
     </row>
     <row r="304" spans="1:10" s="1" customFormat="1">
-      <c r="A304" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B304" s="13">
-        <v>46281</v>
-      </c>
-      <c r="C304" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E304" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F304" s="6"/>
+      <c r="A304" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="B304" s="24">
+        <v>46280</v>
+      </c>
+      <c r="C304" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D304" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E304" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F304" s="25"/>
+      <c r="G304" s="23"/>
+      <c r="H304" s="37"/>
+      <c r="I304" s="37"/>
+      <c r="J304" s="37"/>
     </row>
     <row r="305" spans="1:10" s="1" customFormat="1">
-      <c r="A305" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B305" s="11">
-        <v>46282</v>
+      <c r="A305" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B305" s="13">
+        <v>46281</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>15</v>
@@ -54722,43 +54725,43 @@
       <c r="F305" s="6"/>
     </row>
     <row r="306" spans="1:10" s="1" customFormat="1">
-      <c r="A306" s="76" t="s">
-        <v>267</v>
-      </c>
-      <c r="B306" s="76"/>
-      <c r="C306" s="76"/>
-      <c r="D306" s="76"/>
-      <c r="E306" s="76"/>
-      <c r="F306" s="76"/>
-      <c r="G306" s="76"/>
-      <c r="H306" s="38"/>
-      <c r="I306" s="38"/>
-      <c r="J306" s="38"/>
+      <c r="A306" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B306" s="11">
+        <v>46282</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E306" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F306" s="6"/>
     </row>
     <row r="307" spans="1:10" s="1" customFormat="1">
-      <c r="A307" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B307" s="13">
-        <v>46286</v>
-      </c>
-      <c r="C307" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E307" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F307" s="6"/>
+      <c r="A307" s="77" t="s">
+        <v>268</v>
+      </c>
+      <c r="B307" s="77"/>
+      <c r="C307" s="77"/>
+      <c r="D307" s="77"/>
+      <c r="E307" s="77"/>
+      <c r="F307" s="77"/>
+      <c r="G307" s="77"/>
+      <c r="H307" s="38"/>
+      <c r="I307" s="38"/>
+      <c r="J307" s="38"/>
     </row>
     <row r="308" spans="1:10" s="1" customFormat="1">
       <c r="A308" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B308" s="13">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="C308" s="6" t="s">
         <v>14</v>
@@ -54766,14 +54769,14 @@
       <c r="D308" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E308" s="7" t="s">
-        <v>26</v>
+      <c r="E308" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F308" s="6"/>
     </row>
     <row r="309" spans="1:10" s="1" customFormat="1">
-      <c r="A309" s="9" t="s">
-        <v>28</v>
+      <c r="A309" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B309" s="13">
         <v>46288</v>
@@ -54790,14 +54793,14 @@
       <c r="F309" s="6"/>
     </row>
     <row r="310" spans="1:10" s="1" customFormat="1">
-      <c r="A310" s="10" t="s">
-        <v>24</v>
+      <c r="A310" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B310" s="13">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>15</v>
@@ -54808,78 +54811,74 @@
       <c r="F310" s="6"/>
     </row>
     <row r="311" spans="1:10" s="1" customFormat="1">
-      <c r="A311" s="76" t="s">
-        <v>268</v>
-      </c>
-      <c r="B311" s="76"/>
-      <c r="C311" s="76"/>
-      <c r="D311" s="76"/>
-      <c r="E311" s="76"/>
-      <c r="F311" s="76"/>
-      <c r="G311" s="76"/>
-      <c r="H311" s="38"/>
-      <c r="I311" s="38"/>
-      <c r="J311" s="38"/>
+      <c r="A311" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B311" s="13">
+        <v>46289</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E311" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F311" s="6"/>
     </row>
     <row r="312" spans="1:10" s="1" customFormat="1">
-      <c r="A312" s="23" t="s">
+      <c r="A312" s="77" t="s">
         <v>269</v>
       </c>
-      <c r="B312" s="24">
+      <c r="B312" s="77"/>
+      <c r="C312" s="77"/>
+      <c r="D312" s="77"/>
+      <c r="E312" s="77"/>
+      <c r="F312" s="77"/>
+      <c r="G312" s="77"/>
+      <c r="H312" s="38"/>
+      <c r="I312" s="38"/>
+      <c r="J312" s="38"/>
+    </row>
+    <row r="313" spans="1:10" s="1" customFormat="1">
+      <c r="A313" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="B313" s="24">
         <v>46291</v>
       </c>
-      <c r="C312" s="25" t="s">
+      <c r="C313" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D312" s="23" t="s">
+      <c r="D313" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="E312" s="23" t="s">
+      <c r="E313" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="F312" s="26"/>
-      <c r="G312" s="26"/>
-      <c r="H312" s="41"/>
-      <c r="I312" s="41"/>
-      <c r="J312" s="41"/>
-    </row>
-    <row r="313" spans="1:10" s="7" customFormat="1">
-      <c r="A313" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B313" s="13">
-        <v>46293</v>
-      </c>
-      <c r="C313" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E313" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F313" s="6"/>
-      <c r="G313" s="1"/>
-      <c r="H313" s="40"/>
-      <c r="I313" s="40"/>
-      <c r="J313" s="40"/>
+      <c r="F313" s="26"/>
+      <c r="G313" s="26"/>
+      <c r="H313" s="41"/>
+      <c r="I313" s="41"/>
+      <c r="J313" s="41"/>
     </row>
     <row r="314" spans="1:10" s="7" customFormat="1">
       <c r="A314" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B314" s="13">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F314" s="6"/>
       <c r="G314" s="1"/>
@@ -54887,21 +54886,21 @@
       <c r="I314" s="40"/>
       <c r="J314" s="40"/>
     </row>
-    <row r="315" spans="1:10" s="5" customFormat="1" ht="20.25">
+    <row r="315" spans="1:10" s="7" customFormat="1">
       <c r="A315" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B315" s="13">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E315" s="7" t="s">
-        <v>26</v>
+      <c r="E315" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F315" s="6"/>
       <c r="G315" s="1"/>
@@ -54909,35 +54908,43 @@
       <c r="I315" s="40"/>
       <c r="J315" s="40"/>
     </row>
-    <row r="316" spans="1:10" s="1" customFormat="1">
-      <c r="A316" s="16"/>
-      <c r="B316" s="12"/>
-      <c r="C316" s="12"/>
-      <c r="D316" s="7"/>
-      <c r="E316" s="7"/>
-      <c r="F316" s="65"/>
-      <c r="G316" s="7"/>
-      <c r="H316" s="42"/>
-      <c r="I316" s="42"/>
-      <c r="J316" s="42"/>
+    <row r="316" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A316" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B316" s="13">
+        <v>46295</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E316" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F316" s="6"/>
+      <c r="G316" s="1"/>
+      <c r="H316" s="40"/>
+      <c r="I316" s="40"/>
+      <c r="J316" s="40"/>
     </row>
-    <row r="317" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A317" s="78" t="s">
-        <v>270</v>
-      </c>
-      <c r="B317" s="78"/>
-      <c r="C317" s="78"/>
-      <c r="D317" s="78"/>
-      <c r="E317" s="78"/>
-      <c r="F317" s="78"/>
-      <c r="G317" s="78"/>
-      <c r="H317" s="34"/>
-      <c r="I317" s="34"/>
-      <c r="J317" s="34"/>
+    <row r="317" spans="1:10" s="1" customFormat="1">
+      <c r="A317" s="16"/>
+      <c r="B317" s="12"/>
+      <c r="C317" s="12"/>
+      <c r="D317" s="7"/>
+      <c r="E317" s="7"/>
+      <c r="F317" s="65"/>
+      <c r="G317" s="7"/>
+      <c r="H317" s="42"/>
+      <c r="I317" s="42"/>
+      <c r="J317" s="42"/>
     </row>
-    <row r="318" spans="1:10" s="5" customFormat="1" ht="19.5">
+    <row r="318" spans="1:10" s="1" customFormat="1" ht="19.5">
       <c r="A318" s="79" t="s">
-        <v>131</v>
+        <v>271</v>
       </c>
       <c r="B318" s="79"/>
       <c r="C318" s="79"/>
@@ -54945,123 +54952,119 @@
       <c r="E318" s="79"/>
       <c r="F318" s="79"/>
       <c r="G318" s="79"/>
-      <c r="H318" s="33"/>
-      <c r="I318" s="33"/>
-      <c r="J318" s="33"/>
+      <c r="H318" s="34"/>
+      <c r="I318" s="34"/>
+      <c r="J318" s="34"/>
     </row>
-    <row r="319" spans="1:10" s="1" customFormat="1">
-      <c r="A319" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B319" s="11">
-        <v>46296</v>
-      </c>
-      <c r="C319" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E319" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F319" s="6"/>
+    <row r="319" spans="1:10" s="5" customFormat="1" ht="19.5">
+      <c r="A319" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B319" s="75"/>
+      <c r="C319" s="75"/>
+      <c r="D319" s="75"/>
+      <c r="E319" s="75"/>
+      <c r="F319" s="75"/>
+      <c r="G319" s="75"/>
+      <c r="H319" s="33"/>
+      <c r="I319" s="33"/>
+      <c r="J319" s="33"/>
     </row>
     <row r="320" spans="1:10" s="1" customFormat="1">
-      <c r="A320" s="76" t="s">
-        <v>271</v>
-      </c>
-      <c r="B320" s="76"/>
-      <c r="C320" s="76"/>
-      <c r="D320" s="76"/>
-      <c r="E320" s="76"/>
-      <c r="F320" s="76"/>
-      <c r="G320" s="76"/>
-      <c r="H320" s="38"/>
-      <c r="I320" s="38"/>
-      <c r="J320" s="38"/>
+      <c r="A320" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B320" s="11">
+        <v>46296</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E320" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F320" s="6"/>
     </row>
     <row r="321" spans="1:10" s="1" customFormat="1">
-      <c r="A321" s="76" t="s">
+      <c r="A321" s="77" t="s">
         <v>272</v>
       </c>
-      <c r="B321" s="76"/>
-      <c r="C321" s="76"/>
-      <c r="D321" s="76"/>
-      <c r="E321" s="76"/>
-      <c r="F321" s="76"/>
-      <c r="G321" s="76"/>
+      <c r="B321" s="77"/>
+      <c r="C321" s="77"/>
+      <c r="D321" s="77"/>
+      <c r="E321" s="77"/>
+      <c r="F321" s="77"/>
+      <c r="G321" s="77"/>
       <c r="H321" s="38"/>
       <c r="I321" s="38"/>
       <c r="J321" s="38"/>
     </row>
     <row r="322" spans="1:10" s="1" customFormat="1">
-      <c r="A322" s="76" t="s">
+      <c r="A322" s="77" t="s">
         <v>273</v>
       </c>
-      <c r="B322" s="76"/>
-      <c r="C322" s="76"/>
-      <c r="D322" s="76"/>
-      <c r="E322" s="76"/>
-      <c r="F322" s="76"/>
-      <c r="G322" s="76"/>
+      <c r="B322" s="77"/>
+      <c r="C322" s="77"/>
+      <c r="D322" s="77"/>
+      <c r="E322" s="77"/>
+      <c r="F322" s="77"/>
+      <c r="G322" s="77"/>
       <c r="H322" s="38"/>
       <c r="I322" s="38"/>
       <c r="J322" s="38"/>
     </row>
     <row r="323" spans="1:10" s="1" customFormat="1">
-      <c r="A323" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B323" s="13">
-        <v>46300</v>
-      </c>
-      <c r="C323" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D323" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E323" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F323" s="6"/>
+      <c r="A323" s="77" t="s">
+        <v>274</v>
+      </c>
+      <c r="B323" s="77"/>
+      <c r="C323" s="77"/>
+      <c r="D323" s="77"/>
+      <c r="E323" s="77"/>
+      <c r="F323" s="77"/>
+      <c r="G323" s="77"/>
+      <c r="H323" s="38"/>
+      <c r="I323" s="38"/>
+      <c r="J323" s="38"/>
     </row>
     <row r="324" spans="1:10" s="1" customFormat="1">
-      <c r="A324" s="75" t="s">
-        <v>274</v>
-      </c>
-      <c r="B324" s="75"/>
-      <c r="C324" s="75"/>
-      <c r="D324" s="75"/>
-      <c r="E324" s="75"/>
-      <c r="F324" s="75"/>
-      <c r="G324" s="75"/>
-      <c r="H324" s="39"/>
-      <c r="I324" s="39"/>
-      <c r="J324" s="39"/>
+      <c r="A324" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B324" s="13">
+        <v>46300</v>
+      </c>
+      <c r="C324" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E324" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F324" s="6"/>
     </row>
     <row r="325" spans="1:10" s="1" customFormat="1">
-      <c r="A325" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B325" s="13">
-        <v>46302</v>
-      </c>
-      <c r="C325" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E325" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F325" s="6"/>
+      <c r="A325" s="76" t="s">
+        <v>275</v>
+      </c>
+      <c r="B325" s="76"/>
+      <c r="C325" s="76"/>
+      <c r="D325" s="76"/>
+      <c r="E325" s="76"/>
+      <c r="F325" s="76"/>
+      <c r="G325" s="76"/>
+      <c r="H325" s="39"/>
+      <c r="I325" s="39"/>
+      <c r="J325" s="39"/>
     </row>
     <row r="326" spans="1:10" s="1" customFormat="1">
-      <c r="A326" s="9" t="s">
-        <v>28</v>
+      <c r="A326" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B326" s="13">
         <v>46302</v>
@@ -55078,14 +55081,14 @@
       <c r="F326" s="6"/>
     </row>
     <row r="327" spans="1:10" s="1" customFormat="1">
-      <c r="A327" s="10" t="s">
-        <v>24</v>
+      <c r="A327" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B327" s="13">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>15</v>
@@ -55096,100 +55099,100 @@
       <c r="F327" s="6"/>
     </row>
     <row r="328" spans="1:10" s="1" customFormat="1">
-      <c r="A328" s="77" t="s">
-        <v>275</v>
-      </c>
-      <c r="B328" s="77"/>
-      <c r="C328" s="77"/>
-      <c r="D328" s="77"/>
-      <c r="E328" s="77"/>
-      <c r="F328" s="77"/>
-      <c r="G328" s="77"/>
-      <c r="H328" s="36"/>
-      <c r="I328" s="36"/>
-      <c r="J328" s="36"/>
+      <c r="A328" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B328" s="13">
+        <v>46303</v>
+      </c>
+      <c r="C328" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E328" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F328" s="6"/>
     </row>
     <row r="329" spans="1:10" s="1" customFormat="1">
-      <c r="A329" s="23" t="s">
+      <c r="A329" s="78" t="s">
         <v>276</v>
       </c>
-      <c r="B329" s="24">
-        <v>46305</v>
-      </c>
-      <c r="C329" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D329" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E329" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F329" s="26"/>
-      <c r="G329" s="26"/>
-      <c r="H329" s="41"/>
-      <c r="I329" s="41"/>
-      <c r="J329" s="41"/>
+      <c r="B329" s="78"/>
+      <c r="C329" s="78"/>
+      <c r="D329" s="78"/>
+      <c r="E329" s="78"/>
+      <c r="F329" s="78"/>
+      <c r="G329" s="78"/>
+      <c r="H329" s="36"/>
+      <c r="I329" s="36"/>
+      <c r="J329" s="36"/>
     </row>
     <row r="330" spans="1:10" s="1" customFormat="1">
-      <c r="A330" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B330" s="13">
-        <v>46307</v>
-      </c>
-      <c r="C330" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E330" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F330" s="6"/>
+      <c r="A330" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="B330" s="24">
+        <v>46305</v>
+      </c>
+      <c r="C330" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D330" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E330" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F330" s="26"/>
+      <c r="G330" s="26"/>
+      <c r="H330" s="41"/>
+      <c r="I330" s="41"/>
+      <c r="J330" s="41"/>
     </row>
     <row r="331" spans="1:10" s="1" customFormat="1">
-      <c r="A331" s="75" t="s">
-        <v>277</v>
-      </c>
-      <c r="B331" s="75"/>
-      <c r="C331" s="75"/>
-      <c r="D331" s="75"/>
-      <c r="E331" s="75"/>
-      <c r="F331" s="75"/>
-      <c r="G331" s="75"/>
-      <c r="H331" s="39"/>
-      <c r="I331" s="39"/>
-      <c r="J331" s="39"/>
+      <c r="A331" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B331" s="13">
+        <v>46307</v>
+      </c>
+      <c r="C331" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E331" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F331" s="6"/>
     </row>
     <row r="332" spans="1:10" s="1" customFormat="1">
-      <c r="A332" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B332" s="13">
-        <v>46309</v>
-      </c>
-      <c r="C332" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E332" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F332" s="6"/>
+      <c r="A332" s="76" t="s">
+        <v>278</v>
+      </c>
+      <c r="B332" s="76"/>
+      <c r="C332" s="76"/>
+      <c r="D332" s="76"/>
+      <c r="E332" s="76"/>
+      <c r="F332" s="76"/>
+      <c r="G332" s="76"/>
+      <c r="H332" s="39"/>
+      <c r="I332" s="39"/>
+      <c r="J332" s="39"/>
     </row>
     <row r="333" spans="1:10" s="1" customFormat="1">
-      <c r="A333" s="9" t="s">
-        <v>24</v>
+      <c r="A333" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B333" s="13">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>15</v>
@@ -55200,80 +55203,80 @@
       <c r="F333" s="6"/>
     </row>
     <row r="334" spans="1:10" s="1" customFormat="1">
-      <c r="A334" s="75" t="s">
-        <v>278</v>
-      </c>
-      <c r="B334" s="75"/>
-      <c r="C334" s="75"/>
-      <c r="D334" s="75"/>
-      <c r="E334" s="75"/>
-      <c r="F334" s="75"/>
-      <c r="G334" s="75"/>
-      <c r="H334" s="39"/>
-      <c r="I334" s="39"/>
-      <c r="J334" s="39"/>
+      <c r="A334" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B334" s="13">
+        <v>46310</v>
+      </c>
+      <c r="C334" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E334" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F334" s="6"/>
     </row>
     <row r="335" spans="1:10" s="1" customFormat="1">
-      <c r="A335" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B335" s="13">
-        <v>46314</v>
-      </c>
-      <c r="C335" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E335" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F335" s="6"/>
+      <c r="A335" s="76" t="s">
+        <v>279</v>
+      </c>
+      <c r="B335" s="76"/>
+      <c r="C335" s="76"/>
+      <c r="D335" s="76"/>
+      <c r="E335" s="76"/>
+      <c r="F335" s="76"/>
+      <c r="G335" s="76"/>
+      <c r="H335" s="39"/>
+      <c r="I335" s="39"/>
+      <c r="J335" s="39"/>
     </row>
     <row r="336" spans="1:10" s="1" customFormat="1">
-      <c r="A336" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="B336" s="24">
-        <v>46315</v>
-      </c>
-      <c r="C336" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D336" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E336" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F336" s="25"/>
-      <c r="G336" s="23"/>
-      <c r="H336" s="37"/>
-      <c r="I336" s="37"/>
-      <c r="J336" s="37"/>
+      <c r="A336" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B336" s="13">
+        <v>46314</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E336" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F336" s="6"/>
     </row>
     <row r="337" spans="1:10" s="1" customFormat="1">
-      <c r="A337" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B337" s="13">
-        <v>46316</v>
-      </c>
-      <c r="C337" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E337" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F337" s="6"/>
+      <c r="A337" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="B337" s="24">
+        <v>46315</v>
+      </c>
+      <c r="C337" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D337" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E337" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F337" s="25"/>
+      <c r="G337" s="23"/>
+      <c r="H337" s="37"/>
+      <c r="I337" s="37"/>
+      <c r="J337" s="37"/>
     </row>
     <row r="338" spans="1:10" s="1" customFormat="1">
-      <c r="A338" s="9" t="s">
-        <v>28</v>
+      <c r="A338" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B338" s="13">
         <v>46316</v>
@@ -55290,14 +55293,14 @@
       <c r="F338" s="6"/>
     </row>
     <row r="339" spans="1:10" s="1" customFormat="1">
-      <c r="A339" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B339" s="11">
-        <v>46317</v>
+      <c r="A339" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B339" s="13">
+        <v>46316</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>15</v>
@@ -55308,56 +55311,52 @@
       <c r="F339" s="6"/>
     </row>
     <row r="340" spans="1:10" s="1" customFormat="1">
-      <c r="A340" s="75" t="s">
-        <v>280</v>
-      </c>
-      <c r="B340" s="75"/>
-      <c r="C340" s="75"/>
-      <c r="D340" s="75"/>
-      <c r="E340" s="75"/>
-      <c r="F340" s="75"/>
-      <c r="G340" s="75"/>
-      <c r="H340" s="39"/>
-      <c r="I340" s="39"/>
-      <c r="J340" s="39"/>
+      <c r="A340" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B340" s="11">
+        <v>46317</v>
+      </c>
+      <c r="C340" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E340" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F340" s="6"/>
     </row>
-    <row r="341" spans="1:10" s="7" customFormat="1">
-      <c r="A341" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B341" s="13">
-        <v>46321</v>
-      </c>
-      <c r="C341" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E341" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F341" s="6"/>
-      <c r="G341" s="1"/>
-      <c r="H341" s="40"/>
-      <c r="I341" s="40"/>
-      <c r="J341" s="40"/>
+    <row r="341" spans="1:10" s="1" customFormat="1">
+      <c r="A341" s="76" t="s">
+        <v>281</v>
+      </c>
+      <c r="B341" s="76"/>
+      <c r="C341" s="76"/>
+      <c r="D341" s="76"/>
+      <c r="E341" s="76"/>
+      <c r="F341" s="76"/>
+      <c r="G341" s="76"/>
+      <c r="H341" s="39"/>
+      <c r="I341" s="39"/>
+      <c r="J341" s="39"/>
     </row>
     <row r="342" spans="1:10" s="7" customFormat="1">
       <c r="A342" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B342" s="13">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F342" s="6"/>
       <c r="G342" s="1"/>
@@ -55367,19 +55366,19 @@
     </row>
     <row r="343" spans="1:10" s="7" customFormat="1">
       <c r="A343" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B343" s="13">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E343" s="7" t="s">
-        <v>26</v>
+      <c r="E343" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F343" s="6"/>
       <c r="G343" s="1"/>
@@ -55388,14 +55387,14 @@
       <c r="J343" s="40"/>
     </row>
     <row r="344" spans="1:10" s="7" customFormat="1">
-      <c r="A344" s="9" t="s">
-        <v>24</v>
+      <c r="A344" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B344" s="13">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>15</v>
@@ -55403,49 +55402,57 @@
       <c r="E344" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F344" s="65"/>
+      <c r="F344" s="6"/>
+      <c r="G344" s="1"/>
+      <c r="H344" s="40"/>
+      <c r="I344" s="40"/>
+      <c r="J344" s="40"/>
     </row>
-    <row r="345" spans="1:10" s="5" customFormat="1" ht="20.25">
-      <c r="A345" s="75" t="s">
-        <v>281</v>
-      </c>
-      <c r="B345" s="75"/>
-      <c r="C345" s="75"/>
-      <c r="D345" s="75"/>
-      <c r="E345" s="75"/>
-      <c r="F345" s="75"/>
-      <c r="G345" s="75"/>
-      <c r="H345" s="39"/>
-      <c r="I345" s="39"/>
-      <c r="J345" s="39"/>
+    <row r="345" spans="1:10" s="7" customFormat="1">
+      <c r="A345" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B345" s="13">
+        <v>46324</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E345" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F345" s="65"/>
     </row>
-    <row r="346" spans="1:10" s="1" customFormat="1">
-      <c r="A346" s="9"/>
-      <c r="B346" s="13"/>
-      <c r="C346" s="8"/>
-      <c r="F346" s="6"/>
-      <c r="G346" s="7"/>
-      <c r="H346" s="42"/>
-      <c r="I346" s="42"/>
-      <c r="J346" s="42"/>
+    <row r="346" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A346" s="76" t="s">
+        <v>282</v>
+      </c>
+      <c r="B346" s="76"/>
+      <c r="C346" s="76"/>
+      <c r="D346" s="76"/>
+      <c r="E346" s="76"/>
+      <c r="F346" s="76"/>
+      <c r="G346" s="76"/>
+      <c r="H346" s="39"/>
+      <c r="I346" s="39"/>
+      <c r="J346" s="39"/>
     </row>
-    <row r="347" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A347" s="78" t="s">
-        <v>282</v>
-      </c>
-      <c r="B347" s="78"/>
-      <c r="C347" s="78"/>
-      <c r="D347" s="78"/>
-      <c r="E347" s="78"/>
-      <c r="F347" s="78"/>
-      <c r="G347" s="78"/>
-      <c r="H347" s="34"/>
-      <c r="I347" s="34"/>
-      <c r="J347" s="34"/>
+    <row r="347" spans="1:10" s="1" customFormat="1">
+      <c r="A347" s="9"/>
+      <c r="B347" s="13"/>
+      <c r="C347" s="8"/>
+      <c r="F347" s="6"/>
+      <c r="G347" s="7"/>
+      <c r="H347" s="42"/>
+      <c r="I347" s="42"/>
+      <c r="J347" s="42"/>
     </row>
-    <row r="348" spans="1:10" s="5" customFormat="1" ht="19.5">
+    <row r="348" spans="1:10" s="1" customFormat="1" ht="19.5">
       <c r="A348" s="79" t="s">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="B348" s="79"/>
       <c r="C348" s="79"/>
@@ -55453,56 +55460,52 @@
       <c r="E348" s="79"/>
       <c r="F348" s="79"/>
       <c r="G348" s="79"/>
-      <c r="H348" s="33"/>
-      <c r="I348" s="33"/>
-      <c r="J348" s="33"/>
+      <c r="H348" s="34"/>
+      <c r="I348" s="34"/>
+      <c r="J348" s="34"/>
     </row>
-    <row r="349" spans="1:10" s="1" customFormat="1">
-      <c r="A349" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="B349" s="24">
-        <v>46327</v>
-      </c>
-      <c r="C349" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D349" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E349" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="F349" s="25"/>
-      <c r="G349" s="23"/>
-      <c r="H349" s="37"/>
-      <c r="I349" s="37"/>
-      <c r="J349" s="37"/>
+    <row r="349" spans="1:10" s="5" customFormat="1" ht="19.5">
+      <c r="A349" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B349" s="75"/>
+      <c r="C349" s="75"/>
+      <c r="D349" s="75"/>
+      <c r="E349" s="75"/>
+      <c r="F349" s="75"/>
+      <c r="G349" s="75"/>
+      <c r="H349" s="33"/>
+      <c r="I349" s="33"/>
+      <c r="J349" s="33"/>
     </row>
     <row r="350" spans="1:10" s="1" customFormat="1">
-      <c r="A350" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B350" s="13">
-        <v>46328</v>
-      </c>
-      <c r="C350" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E350" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F350" s="6"/>
+      <c r="A350" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="B350" s="24">
+        <v>46327</v>
+      </c>
+      <c r="C350" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D350" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E350" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="F350" s="25"/>
+      <c r="G350" s="23"/>
+      <c r="H350" s="37"/>
+      <c r="I350" s="37"/>
+      <c r="J350" s="37"/>
     </row>
     <row r="351" spans="1:10" s="1" customFormat="1">
       <c r="A351" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B351" s="13">
-        <v>46330</v>
+        <v>46328</v>
       </c>
       <c r="C351" s="6" t="s">
         <v>14</v>
@@ -55510,14 +55513,14 @@
       <c r="D351" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E351" s="7" t="s">
-        <v>26</v>
+      <c r="E351" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F351" s="6"/>
     </row>
     <row r="352" spans="1:10" s="1" customFormat="1">
-      <c r="A352" s="9" t="s">
-        <v>28</v>
+      <c r="A352" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B352" s="13">
         <v>46330</v>
@@ -55534,14 +55537,14 @@
       <c r="F352" s="6"/>
     </row>
     <row r="353" spans="1:10" s="1" customFormat="1">
-      <c r="A353" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B353" s="11">
-        <v>46331</v>
+      <c r="A353" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B353" s="13">
+        <v>46330</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>15</v>
@@ -55552,100 +55555,100 @@
       <c r="F353" s="6"/>
     </row>
     <row r="354" spans="1:10" s="1" customFormat="1">
-      <c r="A354" s="76" t="s">
-        <v>285</v>
-      </c>
-      <c r="B354" s="76"/>
-      <c r="C354" s="76"/>
-      <c r="D354" s="76"/>
-      <c r="E354" s="76"/>
-      <c r="F354" s="76"/>
-      <c r="G354" s="76"/>
-      <c r="H354" s="38"/>
-      <c r="I354" s="38"/>
-      <c r="J354" s="38"/>
+      <c r="A354" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B354" s="11">
+        <v>46331</v>
+      </c>
+      <c r="C354" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E354" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F354" s="6"/>
     </row>
     <row r="355" spans="1:10" s="1" customFormat="1">
-      <c r="A355" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B355" s="13">
-        <v>46335</v>
-      </c>
-      <c r="C355" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E355" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F355" s="6"/>
+      <c r="A355" s="77" t="s">
+        <v>286</v>
+      </c>
+      <c r="B355" s="77"/>
+      <c r="C355" s="77"/>
+      <c r="D355" s="77"/>
+      <c r="E355" s="77"/>
+      <c r="F355" s="77"/>
+      <c r="G355" s="77"/>
+      <c r="H355" s="38"/>
+      <c r="I355" s="38"/>
+      <c r="J355" s="38"/>
     </row>
     <row r="356" spans="1:10" s="1" customFormat="1">
-      <c r="A356" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="B356" s="24">
-        <v>46336</v>
-      </c>
-      <c r="C356" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D356" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E356" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="F356" s="25"/>
-      <c r="G356" s="23"/>
-      <c r="H356" s="37"/>
-      <c r="I356" s="37"/>
-      <c r="J356" s="37"/>
+      <c r="A356" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B356" s="13">
+        <v>46335</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F356" s="6"/>
     </row>
     <row r="357" spans="1:10" s="1" customFormat="1">
-      <c r="A357" s="77" t="s">
+      <c r="A357" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="B357" s="24">
+        <v>46336</v>
+      </c>
+      <c r="C357" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D357" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E357" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="B357" s="77"/>
-      <c r="C357" s="77"/>
-      <c r="D357" s="77"/>
-      <c r="E357" s="77"/>
-      <c r="F357" s="77"/>
-      <c r="G357" s="77"/>
-      <c r="H357" s="36"/>
-      <c r="I357" s="36"/>
-      <c r="J357" s="36"/>
+      <c r="F357" s="25"/>
+      <c r="G357" s="23"/>
+      <c r="H357" s="37"/>
+      <c r="I357" s="37"/>
+      <c r="J357" s="37"/>
     </row>
     <row r="358" spans="1:10" s="1" customFormat="1">
-      <c r="A358" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B358" s="13">
-        <v>46337</v>
-      </c>
-      <c r="C358" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D358" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E358" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F358" s="6"/>
+      <c r="A358" s="78" t="s">
+        <v>289</v>
+      </c>
+      <c r="B358" s="78"/>
+      <c r="C358" s="78"/>
+      <c r="D358" s="78"/>
+      <c r="E358" s="78"/>
+      <c r="F358" s="78"/>
+      <c r="G358" s="78"/>
+      <c r="H358" s="36"/>
+      <c r="I358" s="36"/>
+      <c r="J358" s="36"/>
     </row>
     <row r="359" spans="1:10" s="1" customFormat="1">
-      <c r="A359" s="9" t="s">
-        <v>24</v>
+      <c r="A359" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B359" s="13">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>15</v>
@@ -55656,29 +55659,29 @@
       <c r="F359" s="6"/>
     </row>
     <row r="360" spans="1:10" s="1" customFormat="1">
-      <c r="A360" s="1" t="s">
-        <v>13</v>
+      <c r="A360" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="B360" s="13">
-        <v>46342</v>
+        <v>46338</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E360" s="1" t="s">
-        <v>16</v>
+      <c r="E360" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F360" s="6"/>
     </row>
     <row r="361" spans="1:10" s="1" customFormat="1">
       <c r="A361" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B361" s="13">
-        <v>46344</v>
+        <v>46342</v>
       </c>
       <c r="C361" s="6" t="s">
         <v>14</v>
@@ -55686,14 +55689,14 @@
       <c r="D361" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E361" s="7" t="s">
-        <v>26</v>
+      <c r="E361" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F361" s="6"/>
     </row>
     <row r="362" spans="1:10" s="1" customFormat="1">
-      <c r="A362" s="9" t="s">
-        <v>28</v>
+      <c r="A362" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B362" s="13">
         <v>46344</v>
@@ -55710,14 +55713,14 @@
       <c r="F362" s="6"/>
     </row>
     <row r="363" spans="1:10" s="1" customFormat="1">
-      <c r="A363" s="10" t="s">
-        <v>24</v>
+      <c r="A363" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B363" s="13">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>15</v>
@@ -55728,192 +55731,196 @@
       <c r="F363" s="6"/>
     </row>
     <row r="364" spans="1:10" s="1" customFormat="1">
-      <c r="A364" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="B364" s="24">
-        <v>46346</v>
-      </c>
-      <c r="C364" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D364" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E364" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="F364" s="25"/>
-      <c r="G364" s="23"/>
-      <c r="H364" s="37"/>
-      <c r="I364" s="37"/>
-      <c r="J364" s="37"/>
+      <c r="A364" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B364" s="13">
+        <v>46345</v>
+      </c>
+      <c r="C364" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E364" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F364" s="6"/>
     </row>
     <row r="365" spans="1:10" s="1" customFormat="1">
-      <c r="A365" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B365" s="13">
-        <v>46349</v>
-      </c>
-      <c r="C365" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D365" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E365" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F365" s="6"/>
+      <c r="A365" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="B365" s="24">
+        <v>46346</v>
+      </c>
+      <c r="C365" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D365" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E365" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="F365" s="25"/>
+      <c r="G365" s="23"/>
+      <c r="H365" s="37"/>
+      <c r="I365" s="37"/>
+      <c r="J365" s="37"/>
     </row>
     <row r="366" spans="1:10" s="1" customFormat="1">
-      <c r="A366" s="75" t="s">
-        <v>291</v>
-      </c>
-      <c r="B366" s="75"/>
-      <c r="C366" s="75"/>
-      <c r="D366" s="75"/>
-      <c r="E366" s="75"/>
-      <c r="F366" s="75"/>
-      <c r="G366" s="75"/>
-      <c r="H366" s="39"/>
-      <c r="I366" s="39"/>
-      <c r="J366" s="39"/>
+      <c r="A366" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B366" s="13">
+        <v>46349</v>
+      </c>
+      <c r="C366" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E366" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F366" s="6"/>
     </row>
     <row r="367" spans="1:10" s="1" customFormat="1">
-      <c r="A367" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B367" s="13">
-        <v>46350</v>
-      </c>
-      <c r="C367" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D367" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E367" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F367" s="6"/>
+      <c r="A367" s="76" t="s">
+        <v>292</v>
+      </c>
+      <c r="B367" s="76"/>
+      <c r="C367" s="76"/>
+      <c r="D367" s="76"/>
+      <c r="E367" s="76"/>
+      <c r="F367" s="76"/>
+      <c r="G367" s="76"/>
+      <c r="H367" s="39"/>
+      <c r="I367" s="39"/>
+      <c r="J367" s="39"/>
     </row>
     <row r="368" spans="1:10" s="1" customFormat="1">
       <c r="A368" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B368" s="13">
-        <v>46351</v>
+        <v>46350</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D368" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E368" s="7" t="s">
-        <v>26</v>
+      <c r="E368" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F368" s="6"/>
     </row>
     <row r="369" spans="1:10" s="1" customFormat="1">
-      <c r="A369" s="77" t="s">
-        <v>292</v>
-      </c>
-      <c r="B369" s="77"/>
-      <c r="C369" s="77"/>
-      <c r="D369" s="77"/>
-      <c r="E369" s="77"/>
-      <c r="F369" s="77"/>
-      <c r="G369" s="77"/>
-      <c r="H369" s="36"/>
-      <c r="I369" s="36"/>
-      <c r="J369" s="36"/>
+      <c r="A369" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B369" s="13">
+        <v>46351</v>
+      </c>
+      <c r="C369" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E369" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F369" s="6"/>
     </row>
     <row r="370" spans="1:10" s="1" customFormat="1">
-      <c r="A370" s="9" t="s">
+      <c r="A370" s="78" t="s">
+        <v>293</v>
+      </c>
+      <c r="B370" s="78"/>
+      <c r="C370" s="78"/>
+      <c r="D370" s="78"/>
+      <c r="E370" s="78"/>
+      <c r="F370" s="78"/>
+      <c r="G370" s="78"/>
+      <c r="H370" s="36"/>
+      <c r="I370" s="36"/>
+      <c r="J370" s="36"/>
+    </row>
+    <row r="371" spans="1:10" s="1" customFormat="1">
+      <c r="A371" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B370" s="11">
+      <c r="B371" s="11">
         <v>46352</v>
       </c>
-      <c r="C370" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D370" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E370" s="7" t="s">
+      <c r="C371" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E371" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F370" s="6"/>
+      <c r="F371" s="6"/>
     </row>
-    <row r="371" spans="1:10" s="7" customFormat="1">
-      <c r="A371" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="B371" s="75"/>
-      <c r="C371" s="75"/>
-      <c r="D371" s="75"/>
-      <c r="E371" s="75"/>
-      <c r="F371" s="75"/>
-      <c r="G371" s="75"/>
-      <c r="H371" s="39"/>
-      <c r="I371" s="39"/>
-      <c r="J371" s="39"/>
+    <row r="372" spans="1:10" s="7" customFormat="1">
+      <c r="A372" s="76" t="s">
+        <v>294</v>
+      </c>
+      <c r="B372" s="76"/>
+      <c r="C372" s="76"/>
+      <c r="D372" s="76"/>
+      <c r="E372" s="76"/>
+      <c r="F372" s="76"/>
+      <c r="G372" s="76"/>
+      <c r="H372" s="39"/>
+      <c r="I372" s="39"/>
+      <c r="J372" s="39"/>
     </row>
-    <row r="372" spans="1:10" s="5" customFormat="1" ht="20.25">
-      <c r="A372" s="1" t="s">
+    <row r="373" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A373" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B372" s="13">
+      <c r="B373" s="13">
         <v>46356</v>
       </c>
-      <c r="C372" s="6" t="s">
+      <c r="C373" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D372" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E372" s="1" t="s">
+      <c r="D373" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E373" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F372" s="6"/>
-      <c r="G372" s="1"/>
-      <c r="H372" s="40"/>
-      <c r="I372" s="40"/>
-      <c r="J372" s="40"/>
+      <c r="F373" s="6"/>
+      <c r="G373" s="1"/>
+      <c r="H373" s="40"/>
+      <c r="I373" s="40"/>
+      <c r="J373" s="40"/>
     </row>
-    <row r="373" spans="1:10" s="1" customFormat="1">
-      <c r="A373" s="7"/>
-      <c r="B373" s="7"/>
-      <c r="C373" s="7"/>
-      <c r="D373" s="7"/>
-      <c r="E373" s="7"/>
-      <c r="F373" s="65"/>
-      <c r="G373" s="7"/>
-      <c r="H373" s="42"/>
-      <c r="I373" s="42"/>
-      <c r="J373" s="42"/>
+    <row r="374" spans="1:10" s="1" customFormat="1">
+      <c r="A374" s="7"/>
+      <c r="B374" s="7"/>
+      <c r="C374" s="7"/>
+      <c r="D374" s="7"/>
+      <c r="E374" s="7"/>
+      <c r="F374" s="65"/>
+      <c r="G374" s="7"/>
+      <c r="H374" s="42"/>
+      <c r="I374" s="42"/>
+      <c r="J374" s="42"/>
     </row>
-    <row r="374" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A374" s="78" t="s">
-        <v>294</v>
-      </c>
-      <c r="B374" s="78"/>
-      <c r="C374" s="78"/>
-      <c r="D374" s="78"/>
-      <c r="E374" s="78"/>
-      <c r="F374" s="78"/>
-      <c r="G374" s="78"/>
-      <c r="H374" s="34"/>
-      <c r="I374" s="34"/>
-      <c r="J374" s="34"/>
-    </row>
-    <row r="375" spans="1:10" s="5" customFormat="1" ht="19.5">
+    <row r="375" spans="1:10" s="1" customFormat="1" ht="19.5">
       <c r="A375" s="79" t="s">
-        <v>131</v>
+        <v>295</v>
       </c>
       <c r="B375" s="79"/>
       <c r="C375" s="79"/>
@@ -55921,53 +55928,49 @@
       <c r="E375" s="79"/>
       <c r="F375" s="79"/>
       <c r="G375" s="79"/>
-      <c r="H375" s="33"/>
-      <c r="I375" s="33"/>
-      <c r="J375" s="33"/>
+      <c r="H375" s="34"/>
+      <c r="I375" s="34"/>
+      <c r="J375" s="34"/>
     </row>
-    <row r="376" spans="1:10" s="1" customFormat="1">
-      <c r="A376" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="B376" s="24">
-        <v>46357</v>
-      </c>
-      <c r="C376" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D376" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E376" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="F376" s="25"/>
-      <c r="G376" s="23"/>
-      <c r="H376" s="37"/>
-      <c r="I376" s="37"/>
-      <c r="J376" s="37"/>
+    <row r="376" spans="1:10" s="5" customFormat="1" ht="19.5">
+      <c r="A376" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B376" s="75"/>
+      <c r="C376" s="75"/>
+      <c r="D376" s="75"/>
+      <c r="E376" s="75"/>
+      <c r="F376" s="75"/>
+      <c r="G376" s="75"/>
+      <c r="H376" s="33"/>
+      <c r="I376" s="33"/>
+      <c r="J376" s="33"/>
     </row>
     <row r="377" spans="1:10" s="1" customFormat="1">
-      <c r="A377" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B377" s="13">
-        <v>46358</v>
-      </c>
-      <c r="C377" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D377" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E377" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F377" s="6"/>
+      <c r="A377" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="B377" s="24">
+        <v>46357</v>
+      </c>
+      <c r="C377" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D377" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E377" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="F377" s="25"/>
+      <c r="G377" s="23"/>
+      <c r="H377" s="37"/>
+      <c r="I377" s="37"/>
+      <c r="J377" s="37"/>
     </row>
     <row r="378" spans="1:10" s="1" customFormat="1">
-      <c r="A378" s="9" t="s">
-        <v>28</v>
+      <c r="A378" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B378" s="13">
         <v>46358</v>
@@ -55984,14 +55987,14 @@
       <c r="F378" s="6"/>
     </row>
     <row r="379" spans="1:10" s="1" customFormat="1">
-      <c r="A379" s="10" t="s">
-        <v>24</v>
+      <c r="A379" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B379" s="13">
-        <v>46359</v>
+        <v>46358</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D379" s="1" t="s">
         <v>15</v>
@@ -56002,43 +56005,43 @@
       <c r="F379" s="6"/>
     </row>
     <row r="380" spans="1:10" s="1" customFormat="1">
-      <c r="A380" s="76" t="s">
-        <v>297</v>
-      </c>
-      <c r="B380" s="76"/>
-      <c r="C380" s="76"/>
-      <c r="D380" s="76"/>
-      <c r="E380" s="76"/>
-      <c r="F380" s="76"/>
-      <c r="G380" s="76"/>
-      <c r="H380" s="38"/>
-      <c r="I380" s="38"/>
-      <c r="J380" s="38"/>
+      <c r="A380" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B380" s="13">
+        <v>46359</v>
+      </c>
+      <c r="C380" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E380" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F380" s="6"/>
     </row>
     <row r="381" spans="1:10" s="1" customFormat="1">
-      <c r="A381" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B381" s="13">
-        <v>46363</v>
-      </c>
-      <c r="C381" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D381" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E381" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F381" s="6"/>
+      <c r="A381" s="77" t="s">
+        <v>298</v>
+      </c>
+      <c r="B381" s="77"/>
+      <c r="C381" s="77"/>
+      <c r="D381" s="77"/>
+      <c r="E381" s="77"/>
+      <c r="F381" s="77"/>
+      <c r="G381" s="77"/>
+      <c r="H381" s="38"/>
+      <c r="I381" s="38"/>
+      <c r="J381" s="38"/>
     </row>
     <row r="382" spans="1:10" s="1" customFormat="1">
       <c r="A382" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B382" s="13">
-        <v>46365</v>
+        <v>46363</v>
       </c>
       <c r="C382" s="6" t="s">
         <v>14</v>
@@ -56046,20 +56049,20 @@
       <c r="D382" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E382" s="7" t="s">
-        <v>26</v>
+      <c r="E382" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F382" s="6"/>
     </row>
     <row r="383" spans="1:10" s="1" customFormat="1">
-      <c r="A383" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B383" s="11">
-        <v>46366</v>
+      <c r="A383" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B383" s="13">
+        <v>46365</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D383" s="1" t="s">
         <v>15</v>
@@ -56070,80 +56073,80 @@
       <c r="F383" s="6"/>
     </row>
     <row r="384" spans="1:10" s="1" customFormat="1">
-      <c r="A384" s="76" t="s">
-        <v>298</v>
-      </c>
-      <c r="B384" s="76"/>
-      <c r="C384" s="76"/>
-      <c r="D384" s="76"/>
-      <c r="E384" s="76"/>
-      <c r="F384" s="76"/>
-      <c r="G384" s="76"/>
-      <c r="H384" s="38"/>
-      <c r="I384" s="38"/>
-      <c r="J384" s="38"/>
+      <c r="A384" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B384" s="11">
+        <v>46366</v>
+      </c>
+      <c r="C384" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D384" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E384" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F384" s="6"/>
     </row>
     <row r="385" spans="1:10" s="1" customFormat="1">
-      <c r="A385" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B385" s="13">
-        <v>46370</v>
-      </c>
-      <c r="C385" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D385" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E385" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F385" s="6"/>
+      <c r="A385" s="77" t="s">
+        <v>299</v>
+      </c>
+      <c r="B385" s="77"/>
+      <c r="C385" s="77"/>
+      <c r="D385" s="77"/>
+      <c r="E385" s="77"/>
+      <c r="F385" s="77"/>
+      <c r="G385" s="77"/>
+      <c r="H385" s="38"/>
+      <c r="I385" s="38"/>
+      <c r="J385" s="38"/>
     </row>
     <row r="386" spans="1:10" s="1" customFormat="1">
-      <c r="A386" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="B386" s="24">
-        <v>46371</v>
-      </c>
-      <c r="C386" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D386" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E386" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="F386" s="25"/>
-      <c r="G386" s="23"/>
-      <c r="H386" s="37"/>
-      <c r="I386" s="37"/>
-      <c r="J386" s="37"/>
+      <c r="A386" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B386" s="13">
+        <v>46370</v>
+      </c>
+      <c r="C386" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E386" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F386" s="6"/>
     </row>
     <row r="387" spans="1:10" s="1" customFormat="1">
-      <c r="A387" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B387" s="13">
-        <v>46372</v>
-      </c>
-      <c r="C387" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D387" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E387" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F387" s="6"/>
+      <c r="A387" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="B387" s="24">
+        <v>46371</v>
+      </c>
+      <c r="C387" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D387" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E387" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="F387" s="25"/>
+      <c r="G387" s="23"/>
+      <c r="H387" s="37"/>
+      <c r="I387" s="37"/>
+      <c r="J387" s="37"/>
     </row>
     <row r="388" spans="1:10" s="1" customFormat="1">
-      <c r="A388" s="9" t="s">
-        <v>28</v>
+      <c r="A388" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B388" s="13">
         <v>46372</v>
@@ -56160,14 +56163,14 @@
       <c r="F388" s="6"/>
     </row>
     <row r="389" spans="1:10" s="1" customFormat="1">
-      <c r="A389" s="10" t="s">
-        <v>24</v>
+      <c r="A389" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B389" s="13">
-        <v>46373</v>
+        <v>46372</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D389" s="1" t="s">
         <v>15</v>
@@ -56178,29 +56181,29 @@
       <c r="F389" s="6"/>
     </row>
     <row r="390" spans="1:10" s="1" customFormat="1">
-      <c r="A390" s="1" t="s">
-        <v>13</v>
+      <c r="A390" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="B390" s="13">
-        <v>46377</v>
+        <v>46373</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E390" s="1" t="s">
-        <v>16</v>
+      <c r="E390" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F390" s="6"/>
     </row>
     <row r="391" spans="1:10" s="1" customFormat="1">
       <c r="A391" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B391" s="13">
-        <v>46379</v>
+        <v>46377</v>
       </c>
       <c r="C391" s="6" t="s">
         <v>14</v>
@@ -56208,56 +56211,60 @@
       <c r="D391" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E391" s="7" t="s">
-        <v>26</v>
+      <c r="E391" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F391" s="6"/>
     </row>
     <row r="392" spans="1:10" s="1" customFormat="1">
-      <c r="A392" s="76" t="s">
-        <v>301</v>
-      </c>
-      <c r="B392" s="76"/>
-      <c r="C392" s="76"/>
-      <c r="D392" s="76"/>
-      <c r="E392" s="76"/>
-      <c r="F392" s="76"/>
-      <c r="G392" s="76"/>
-      <c r="H392" s="38"/>
-      <c r="I392" s="38"/>
-      <c r="J392" s="38"/>
+      <c r="A392" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B392" s="13">
+        <v>46379</v>
+      </c>
+      <c r="C392" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E392" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F392" s="6"/>
     </row>
     <row r="393" spans="1:10" s="1" customFormat="1">
-      <c r="A393" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B393" s="13">
-        <v>46380</v>
-      </c>
-      <c r="C393" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D393" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E393" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F393" s="6"/>
+      <c r="A393" s="77" t="s">
+        <v>302</v>
+      </c>
+      <c r="B393" s="77"/>
+      <c r="C393" s="77"/>
+      <c r="D393" s="77"/>
+      <c r="E393" s="77"/>
+      <c r="F393" s="77"/>
+      <c r="G393" s="77"/>
+      <c r="H393" s="38"/>
+      <c r="I393" s="38"/>
+      <c r="J393" s="38"/>
     </row>
     <row r="394" spans="1:10" s="1" customFormat="1">
-      <c r="A394" s="76" t="s">
-        <v>302</v>
-      </c>
-      <c r="B394" s="76"/>
-      <c r="C394" s="76"/>
-      <c r="D394" s="76"/>
-      <c r="E394" s="76"/>
-      <c r="F394" s="76"/>
-      <c r="G394" s="76"/>
-      <c r="H394" s="38"/>
-      <c r="I394" s="38"/>
-      <c r="J394" s="38"/>
+      <c r="A394" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B394" s="13">
+        <v>46380</v>
+      </c>
+      <c r="C394" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E394" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F394" s="6"/>
     </row>
     <row r="395" spans="1:10" s="1" customFormat="1">
       <c r="A395" s="77" t="s">
@@ -56269,67 +56276,63 @@
       <c r="E395" s="77"/>
       <c r="F395" s="77"/>
       <c r="G395" s="77"/>
-      <c r="H395" s="36"/>
-      <c r="I395" s="36"/>
-      <c r="J395" s="36"/>
+      <c r="H395" s="38"/>
+      <c r="I395" s="38"/>
+      <c r="J395" s="38"/>
     </row>
     <row r="396" spans="1:10" s="1" customFormat="1">
-      <c r="A396" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B396" s="13">
-        <v>46384</v>
-      </c>
-      <c r="C396" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D396" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E396" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F396" s="6"/>
+      <c r="A396" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="B396" s="78"/>
+      <c r="C396" s="78"/>
+      <c r="D396" s="78"/>
+      <c r="E396" s="78"/>
+      <c r="F396" s="78"/>
+      <c r="G396" s="78"/>
+      <c r="H396" s="36"/>
+      <c r="I396" s="36"/>
+      <c r="J396" s="36"/>
     </row>
     <row r="397" spans="1:10" s="1" customFormat="1">
       <c r="A397" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B397" s="13">
-        <v>46385</v>
+        <v>46384</v>
       </c>
       <c r="C397" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D397" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F397" s="6"/>
     </row>
     <row r="398" spans="1:10" s="1" customFormat="1">
       <c r="A398" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B398" s="13">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="C398" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D398" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E398" s="7" t="s">
-        <v>26</v>
+      <c r="E398" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F398" s="6"/>
     </row>
     <row r="399" spans="1:10" s="1" customFormat="1">
-      <c r="A399" s="9" t="s">
-        <v>28</v>
+      <c r="A399" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B399" s="13">
         <v>46386</v>
@@ -56345,104 +56348,112 @@
       </c>
       <c r="F399" s="6"/>
     </row>
-    <row r="400" spans="1:10" s="7" customFormat="1">
-      <c r="A400" s="77" t="s">
-        <v>304</v>
-      </c>
-      <c r="B400" s="77"/>
-      <c r="C400" s="77"/>
-      <c r="D400" s="77"/>
-      <c r="E400" s="77"/>
-      <c r="F400" s="77"/>
-      <c r="G400" s="77"/>
-      <c r="H400" s="36"/>
-      <c r="I400" s="36"/>
-      <c r="J400" s="36"/>
+    <row r="400" spans="1:10" s="1" customFormat="1">
+      <c r="A400" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B400" s="13">
+        <v>46386</v>
+      </c>
+      <c r="C400" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E400" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F400" s="6"/>
     </row>
-    <row r="401" spans="1:10">
-      <c r="A401" s="75" t="s">
+    <row r="401" spans="1:10" s="7" customFormat="1">
+      <c r="A401" s="78" t="s">
         <v>305</v>
       </c>
-      <c r="B401" s="75"/>
-      <c r="C401" s="75"/>
-      <c r="D401" s="75"/>
-      <c r="E401" s="75"/>
-      <c r="F401" s="75"/>
-      <c r="G401" s="75"/>
-      <c r="H401" s="39"/>
-      <c r="I401" s="39"/>
-      <c r="J401" s="39"/>
+      <c r="B401" s="78"/>
+      <c r="C401" s="78"/>
+      <c r="D401" s="78"/>
+      <c r="E401" s="78"/>
+      <c r="F401" s="78"/>
+      <c r="G401" s="78"/>
+      <c r="H401" s="36"/>
+      <c r="I401" s="36"/>
+      <c r="J401" s="36"/>
     </row>
     <row r="402" spans="1:10">
-      <c r="A402" s="10" t="s">
+      <c r="A402" s="76" t="s">
+        <v>306</v>
+      </c>
+      <c r="B402" s="76"/>
+      <c r="C402" s="76"/>
+      <c r="D402" s="76"/>
+      <c r="E402" s="76"/>
+      <c r="F402" s="76"/>
+      <c r="G402" s="76"/>
+      <c r="H402" s="39"/>
+      <c r="I402" s="39"/>
+      <c r="J402" s="39"/>
+    </row>
+    <row r="403" spans="1:10">
+      <c r="A403" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B402" s="11">
+      <c r="B403" s="11">
         <v>46387</v>
       </c>
-      <c r="C402" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D402" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E402" s="7" t="s">
+      <c r="C403" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E403" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F402" s="65"/>
-      <c r="G402" s="7"/>
-      <c r="H402" s="42"/>
-      <c r="I402" s="42"/>
-      <c r="J402" s="42"/>
+      <c r="F403" s="65"/>
+      <c r="G403" s="7"/>
+      <c r="H403" s="42"/>
+      <c r="I403" s="42"/>
+      <c r="J403" s="42"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{CD25C92C-1A37-4466-8D09-37A65C4BD4ED}"/>
   <mergeCells count="102">
-    <mergeCell ref="A160:G160"/>
-    <mergeCell ref="A202:G202"/>
-    <mergeCell ref="A324:G324"/>
-    <mergeCell ref="A345:G345"/>
-    <mergeCell ref="A366:G366"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A95:G95"/>
-    <mergeCell ref="A98:G98"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A113:G113"/>
-    <mergeCell ref="A226:G226"/>
-    <mergeCell ref="A237:G237"/>
-    <mergeCell ref="A241:G241"/>
-    <mergeCell ref="A235:G235"/>
-    <mergeCell ref="A256:G256"/>
-    <mergeCell ref="A232:G232"/>
-    <mergeCell ref="A247:G247"/>
-    <mergeCell ref="A401:G401"/>
-    <mergeCell ref="A354:G354"/>
-    <mergeCell ref="A347:G347"/>
-    <mergeCell ref="A374:G374"/>
-    <mergeCell ref="A400:G400"/>
+    <mergeCell ref="A161:G161"/>
+    <mergeCell ref="A190:G190"/>
+    <mergeCell ref="A191:G191"/>
+    <mergeCell ref="A192:G192"/>
+    <mergeCell ref="A193:G193"/>
+    <mergeCell ref="A216:G216"/>
+    <mergeCell ref="A201:G201"/>
+    <mergeCell ref="A200:G200"/>
+    <mergeCell ref="A212:G212"/>
+    <mergeCell ref="A162:G162"/>
+    <mergeCell ref="A170:G170"/>
+    <mergeCell ref="A178:G178"/>
+    <mergeCell ref="A179:G179"/>
+    <mergeCell ref="A180:G180"/>
+    <mergeCell ref="A312:G312"/>
     <mergeCell ref="A321:G321"/>
-    <mergeCell ref="A322:G322"/>
-    <mergeCell ref="A328:G328"/>
-    <mergeCell ref="A357:G357"/>
-    <mergeCell ref="A369:G369"/>
-    <mergeCell ref="A334:G334"/>
-    <mergeCell ref="A340:G340"/>
-    <mergeCell ref="A331:G331"/>
-    <mergeCell ref="A380:G380"/>
-    <mergeCell ref="A384:G384"/>
-    <mergeCell ref="A392:G392"/>
-    <mergeCell ref="A395:G395"/>
-    <mergeCell ref="A394:G394"/>
-    <mergeCell ref="A348:G348"/>
-    <mergeCell ref="A375:G375"/>
-    <mergeCell ref="A371:G371"/>
+    <mergeCell ref="A298:G298"/>
+    <mergeCell ref="A318:G318"/>
+    <mergeCell ref="A297:G297"/>
+    <mergeCell ref="A266:G266"/>
+    <mergeCell ref="A319:G319"/>
+    <mergeCell ref="A292:G292"/>
+    <mergeCell ref="A291:G291"/>
+    <mergeCell ref="A267:G267"/>
+    <mergeCell ref="A276:G276"/>
+    <mergeCell ref="A288:G288"/>
+    <mergeCell ref="A265:G265"/>
+    <mergeCell ref="A220:G220"/>
+    <mergeCell ref="A225:G225"/>
+    <mergeCell ref="A264:G264"/>
+    <mergeCell ref="A255:G255"/>
+    <mergeCell ref="A236:G236"/>
+    <mergeCell ref="A295:G295"/>
+    <mergeCell ref="A302:G302"/>
+    <mergeCell ref="A307:G307"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="A72:G72"/>
@@ -56465,41 +56476,51 @@
     <mergeCell ref="A122:G122"/>
     <mergeCell ref="A123:G123"/>
     <mergeCell ref="A125:G125"/>
-    <mergeCell ref="A264:G264"/>
-    <mergeCell ref="A220:G220"/>
-    <mergeCell ref="A225:G225"/>
-    <mergeCell ref="A263:G263"/>
-    <mergeCell ref="A254:G254"/>
-    <mergeCell ref="A236:G236"/>
-    <mergeCell ref="A294:G294"/>
-    <mergeCell ref="A301:G301"/>
-    <mergeCell ref="A306:G306"/>
-    <mergeCell ref="A311:G311"/>
-    <mergeCell ref="A320:G320"/>
-    <mergeCell ref="A297:G297"/>
-    <mergeCell ref="A317:G317"/>
-    <mergeCell ref="A296:G296"/>
-    <mergeCell ref="A265:G265"/>
-    <mergeCell ref="A318:G318"/>
-    <mergeCell ref="A291:G291"/>
-    <mergeCell ref="A290:G290"/>
-    <mergeCell ref="A266:G266"/>
-    <mergeCell ref="A275:G275"/>
-    <mergeCell ref="A287:G287"/>
-    <mergeCell ref="A161:G161"/>
-    <mergeCell ref="A190:G190"/>
-    <mergeCell ref="A191:G191"/>
-    <mergeCell ref="A192:G192"/>
-    <mergeCell ref="A193:G193"/>
-    <mergeCell ref="A216:G216"/>
-    <mergeCell ref="A201:G201"/>
-    <mergeCell ref="A200:G200"/>
-    <mergeCell ref="A212:G212"/>
-    <mergeCell ref="A162:G162"/>
-    <mergeCell ref="A170:G170"/>
-    <mergeCell ref="A178:G178"/>
-    <mergeCell ref="A179:G179"/>
-    <mergeCell ref="A180:G180"/>
+    <mergeCell ref="A402:G402"/>
+    <mergeCell ref="A355:G355"/>
+    <mergeCell ref="A348:G348"/>
+    <mergeCell ref="A375:G375"/>
+    <mergeCell ref="A401:G401"/>
+    <mergeCell ref="A322:G322"/>
+    <mergeCell ref="A323:G323"/>
+    <mergeCell ref="A329:G329"/>
+    <mergeCell ref="A358:G358"/>
+    <mergeCell ref="A370:G370"/>
+    <mergeCell ref="A335:G335"/>
+    <mergeCell ref="A341:G341"/>
+    <mergeCell ref="A332:G332"/>
+    <mergeCell ref="A381:G381"/>
+    <mergeCell ref="A385:G385"/>
+    <mergeCell ref="A393:G393"/>
+    <mergeCell ref="A396:G396"/>
+    <mergeCell ref="A395:G395"/>
+    <mergeCell ref="A349:G349"/>
+    <mergeCell ref="A376:G376"/>
+    <mergeCell ref="A372:G372"/>
+    <mergeCell ref="A160:G160"/>
+    <mergeCell ref="A202:G202"/>
+    <mergeCell ref="A325:G325"/>
+    <mergeCell ref="A346:G346"/>
+    <mergeCell ref="A367:G367"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A98:G98"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A113:G113"/>
+    <mergeCell ref="A226:G226"/>
+    <mergeCell ref="A237:G237"/>
+    <mergeCell ref="A241:G241"/>
+    <mergeCell ref="A235:G235"/>
+    <mergeCell ref="A257:G257"/>
+    <mergeCell ref="A232:G232"/>
+    <mergeCell ref="A248:G248"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G43" r:id="rId1" xr:uid="{742AFF79-FB56-4C66-9522-07C11D0E7152}"/>
@@ -56571,236 +56592,236 @@
   <sheetData>
     <row r="1" spans="1:8" s="14" customFormat="1">
       <c r="A1" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="14" customFormat="1">
       <c r="A2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="14" customFormat="1">
       <c r="A3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F7" t="s">
         <v>235</v>
       </c>
       <c r="G7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F8" t="s">
         <v>235</v>
       </c>
       <c r="G8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F10" t="s">
         <v>235</v>
       </c>
       <c r="G10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
@@ -56808,21 +56829,21 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="17" customFormat="1">
       <c r="A13" s="17" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18" t="s">
@@ -56832,65 +56853,65 @@
         <v>15</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="14" customFormat="1">
       <c r="A14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B14"/>
       <c r="C14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G14"/>
       <c r="H14"/>
     </row>
     <row r="15" spans="1:8" s="15" customFormat="1">
       <c r="A15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B15"/>
       <c r="C15" t="s">
+        <v>363</v>
+      </c>
+      <c r="D15" t="s">
+        <v>360</v>
+      </c>
+      <c r="E15" t="s">
+        <v>364</v>
+      </c>
+      <c r="F15" t="s">
         <v>362</v>
-      </c>
-      <c r="D15" t="s">
-        <v>359</v>
-      </c>
-      <c r="E15" t="s">
-        <v>363</v>
-      </c>
-      <c r="F15" t="s">
-        <v>361</v>
       </c>
       <c r="G15"/>
       <c r="H15"/>
     </row>
     <row r="16" spans="1:8" s="18" customFormat="1">
       <c r="A16" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
@@ -56900,15 +56921,15 @@
     </row>
     <row r="17" spans="1:8" s="18" customFormat="1">
       <c r="A17" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D17" s="17"/>
       <c r="E17" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
@@ -56916,35 +56937,35 @@
     </row>
     <row r="19" spans="1:8" ht="15.95">
       <c r="C19" s="22" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.95">
       <c r="C20" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
         <v>371</v>
-      </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.95">
       <c r="C21" s="21" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.95">
@@ -56972,17 +56993,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>

--- a/.github/datafiles/Communications Calendar 2026.xlsx
+++ b/.github/datafiles/Communications Calendar 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jewishvoice-my.sharepoint.com/personal/creativemarketing_jewishvoice_org/Documents/CM Shared Folders/Calendars/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF1547F1-9751-4A8D-9FDF-3DEE0D8C6A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2172BEB6-06E3-4BB2-90FB-F0BAC30B6D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{32BB45BA-020D-466F-91C6-73191094497B}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{32BB45BA-020D-466F-91C6-73191094497B}"/>
   </bookViews>
   <sheets>
     <sheet name="Dated Communications" sheetId="2" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9604" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9609" uniqueCount="381">
   <si>
     <t>Description</t>
   </si>
@@ -687,12 +687,6 @@
     <t>US</t>
   </si>
   <si>
-    <t>Epilogue Announcement</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
     <t>May HUG Email (Judi Devotional)</t>
   </si>
   <si>
@@ -712,6 +706,12 @@
   </si>
   <si>
     <t>816161 Mid May AP Final Art Files</t>
+  </si>
+  <si>
+    <t>Epilogue Announcement</t>
+  </si>
+  <si>
+    <t>Canada</t>
   </si>
   <si>
     <t>Pentecost and Prophecy</t>
@@ -747,19 +747,22 @@
     <t>Spring Bank Holiday (UK)/Memorial Day (US) - 5/25/26</t>
   </si>
   <si>
-    <t>TBD: Why Stand with Israel? (Guest Brian Sanders)</t>
+    <t>Should I Stand with Israel?</t>
   </si>
   <si>
     <t>5/25/26</t>
   </si>
   <si>
-    <t>TBD</t>
+    <t>Why Stand With Israel? (DVD), Why Stand With Israel? (Study Guide), Miracle of Israel DVD</t>
   </si>
   <si>
     <t>The Scoop (LYJN Month Announcement)</t>
   </si>
   <si>
     <t>GO Prayer Briefing Zoom Invite (2 of 3)</t>
+  </si>
+  <si>
+    <t>Malawi Recruitment Email</t>
   </si>
   <si>
     <t>TM Capaign (lapsed) #1 (End) - 5/30/26</t>
@@ -1224,6 +1227,12 @@
     <t>April 7-8</t>
   </si>
   <si>
+    <t>May 18-19</t>
+  </si>
+  <si>
+    <t>*Updated 5/12/26</t>
+  </si>
+  <si>
     <t>August 21-22</t>
   </si>
   <si>
@@ -1238,7 +1247,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="165" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1340,8 +1349,13 @@
       <name val="Lato"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Lato"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1402,6 +1416,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1440,7 +1460,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
@@ -1614,6 +1634,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1976,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD25C92C-1A37-4466-8D09-37A65C4BD4ED}">
-  <dimension ref="A1:XEY403"/>
+  <dimension ref="A1:XEY404"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="48.42578125" style="1" customWidth="1"/>
@@ -2023,43 +2047,43 @@
       </c>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1" ht="19.5" hidden="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
       <c r="H2" s="35"/>
       <c r="I2" s="35"/>
       <c r="J2" s="35"/>
     </row>
     <row r="3" spans="1:10" s="5" customFormat="1" ht="19.5" hidden="1">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
       <c r="H3" s="33"/>
       <c r="I3" s="33"/>
       <c r="J3" s="33"/>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
       <c r="H4" s="36"/>
       <c r="I4" s="36"/>
       <c r="J4" s="36"/>
@@ -2291,15 +2315,15 @@
       <c r="J15" s="37"/>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A16" s="78" t="s">
+      <c r="A16" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
+      <c r="B16" s="80"/>
+      <c r="C16" s="80"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
       <c r="H16" s="36"/>
       <c r="I16" s="36"/>
       <c r="J16" s="36"/>
@@ -2477,15 +2501,15 @@
       <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A25" s="77" t="s">
+      <c r="A25" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="77"/>
-      <c r="C25" s="77"/>
-      <c r="D25" s="77"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="79"/>
       <c r="H25" s="38"/>
       <c r="I25" s="38"/>
       <c r="J25" s="38"/>
@@ -2613,29 +2637,29 @@
       <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:10" s="5" customFormat="1" ht="19.5" hidden="1">
-      <c r="A33" s="79" t="s">
+      <c r="A33" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="79"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
       <c r="H33" s="34"/>
       <c r="I33" s="34"/>
       <c r="J33" s="34"/>
     </row>
     <row r="34" spans="1:10" s="5" customFormat="1" ht="19.5" hidden="1">
-      <c r="A34" s="75" t="s">
+      <c r="A34" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="75"/>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
       <c r="H34" s="33"/>
       <c r="I34" s="33"/>
       <c r="J34" s="33"/>
@@ -2663,15 +2687,15 @@
       <c r="J35" s="37"/>
     </row>
     <row r="36" spans="1:10" hidden="1">
-      <c r="A36" s="78" t="s">
+      <c r="A36" s="80" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="78"/>
-      <c r="C36" s="78"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="78"/>
+      <c r="B36" s="80"/>
+      <c r="C36" s="80"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="80"/>
       <c r="H36" s="36"/>
       <c r="I36" s="36"/>
       <c r="J36" s="36"/>
@@ -2695,15 +2719,15 @@
       <c r="F37" s="6"/>
     </row>
     <row r="38" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A38" s="76" t="s">
+      <c r="A38" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="76"/>
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
+      <c r="B38" s="78"/>
+      <c r="C38" s="78"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="78"/>
+      <c r="G38" s="78"/>
       <c r="H38" s="39"/>
       <c r="I38" s="39"/>
       <c r="J38" s="39"/>
@@ -2886,29 +2910,29 @@
       <c r="J47" s="37"/>
     </row>
     <row r="48" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A48" s="78" t="s">
+      <c r="A48" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="78"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="78"/>
-      <c r="E48" s="78"/>
-      <c r="F48" s="78"/>
-      <c r="G48" s="78"/>
+      <c r="B48" s="80"/>
+      <c r="C48" s="80"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="80"/>
+      <c r="F48" s="80"/>
+      <c r="G48" s="80"/>
       <c r="H48" s="36"/>
       <c r="I48" s="36"/>
       <c r="J48" s="36"/>
     </row>
     <row r="49" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A49" s="78" t="s">
+      <c r="A49" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="78"/>
-      <c r="C49" s="78"/>
-      <c r="D49" s="78"/>
-      <c r="E49" s="78"/>
-      <c r="F49" s="78"/>
-      <c r="G49" s="78"/>
+      <c r="B49" s="80"/>
+      <c r="C49" s="80"/>
+      <c r="D49" s="80"/>
+      <c r="E49" s="80"/>
+      <c r="F49" s="80"/>
+      <c r="G49" s="80"/>
       <c r="H49" s="36"/>
       <c r="I49" s="36"/>
       <c r="J49" s="36"/>
@@ -2932,15 +2956,15 @@
       <c r="F50" s="6"/>
     </row>
     <row r="51" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A51" s="76" t="s">
+      <c r="A51" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="76"/>
-      <c r="C51" s="76"/>
-      <c r="D51" s="76"/>
-      <c r="E51" s="76"/>
-      <c r="F51" s="76"/>
-      <c r="G51" s="76"/>
+      <c r="B51" s="78"/>
+      <c r="C51" s="78"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="78"/>
+      <c r="F51" s="78"/>
+      <c r="G51" s="78"/>
       <c r="H51" s="39"/>
       <c r="I51" s="39"/>
       <c r="J51" s="39"/>
@@ -2981,15 +3005,15 @@
       <c r="F53" s="6"/>
     </row>
     <row r="54" spans="1:10" s="1" customFormat="1" hidden="1">
-      <c r="A54" s="77" t="s">
+      <c r="A54" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="77"/>
-      <c r="C54" s="77"/>
-      <c r="D54" s="77"/>
-      <c r="E54" s="77"/>
-      <c r="F54" s="77"/>
-      <c r="G54" s="77"/>
+      <c r="B54" s="79"/>
+      <c r="C54" s="79"/>
+      <c r="D54" s="79"/>
+      <c r="E54" s="79"/>
+      <c r="F54" s="79"/>
+      <c r="G54" s="79"/>
       <c r="H54" s="38"/>
       <c r="I54" s="38"/>
       <c r="J54" s="38"/>
@@ -3347,29 +3371,29 @@
       <c r="F71" s="6"/>
     </row>
     <row r="72" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A72" s="79" t="s">
+      <c r="A72" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="B72" s="79"/>
-      <c r="C72" s="79"/>
-      <c r="D72" s="79"/>
-      <c r="E72" s="79"/>
-      <c r="F72" s="79"/>
-      <c r="G72" s="79"/>
+      <c r="B72" s="81"/>
+      <c r="C72" s="81"/>
+      <c r="D72" s="81"/>
+      <c r="E72" s="81"/>
+      <c r="F72" s="81"/>
+      <c r="G72" s="81"/>
       <c r="H72" s="34"/>
       <c r="I72" s="34"/>
       <c r="J72" s="34"/>
     </row>
     <row r="73" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A73" s="75" t="s">
+      <c r="A73" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="B73" s="75"/>
-      <c r="C73" s="75"/>
-      <c r="D73" s="75"/>
-      <c r="E73" s="75"/>
-      <c r="F73" s="75"/>
-      <c r="G73" s="75"/>
+      <c r="B73" s="77"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="77"/>
+      <c r="E73" s="77"/>
+      <c r="F73" s="77"/>
+      <c r="G73" s="77"/>
       <c r="H73" s="33"/>
       <c r="I73" s="33"/>
       <c r="J73" s="33"/>
@@ -3551,15 +3575,15 @@
       <c r="J80" s="37"/>
     </row>
     <row r="81" spans="1:10" s="1" customFormat="1">
-      <c r="A81" s="77" t="s">
+      <c r="A81" s="79" t="s">
         <v>101</v>
       </c>
-      <c r="B81" s="77"/>
-      <c r="C81" s="77"/>
-      <c r="D81" s="77"/>
-      <c r="E81" s="77"/>
-      <c r="F81" s="77"/>
-      <c r="G81" s="77"/>
+      <c r="B81" s="79"/>
+      <c r="C81" s="79"/>
+      <c r="D81" s="79"/>
+      <c r="E81" s="79"/>
+      <c r="F81" s="79"/>
+      <c r="G81" s="79"/>
       <c r="H81" s="38"/>
       <c r="I81" s="38"/>
       <c r="J81" s="38"/>
@@ -3627,15 +3651,15 @@
       <c r="J84" s="37"/>
     </row>
     <row r="85" spans="1:10" s="1" customFormat="1">
-      <c r="A85" s="76" t="s">
+      <c r="A85" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="B85" s="76"/>
-      <c r="C85" s="76"/>
-      <c r="D85" s="76"/>
-      <c r="E85" s="76"/>
-      <c r="F85" s="76"/>
-      <c r="G85" s="76"/>
+      <c r="B85" s="78"/>
+      <c r="C85" s="78"/>
+      <c r="D85" s="78"/>
+      <c r="E85" s="78"/>
+      <c r="F85" s="78"/>
+      <c r="G85" s="78"/>
       <c r="H85" s="39"/>
       <c r="I85" s="39"/>
       <c r="J85" s="39"/>
@@ -3830,15 +3854,15 @@
       </c>
     </row>
     <row r="95" spans="1:10" s="1" customFormat="1">
-      <c r="A95" s="78" t="s">
+      <c r="A95" s="80" t="s">
         <v>116</v>
       </c>
-      <c r="B95" s="78"/>
-      <c r="C95" s="78"/>
-      <c r="D95" s="78"/>
-      <c r="E95" s="78"/>
-      <c r="F95" s="78"/>
-      <c r="G95" s="78"/>
+      <c r="B95" s="80"/>
+      <c r="C95" s="80"/>
+      <c r="D95" s="80"/>
+      <c r="E95" s="80"/>
+      <c r="F95" s="80"/>
+      <c r="G95" s="80"/>
       <c r="H95" s="36"/>
       <c r="I95" s="36"/>
       <c r="J95" s="36"/>
@@ -3886,15 +3910,15 @@
       <c r="F97" s="6"/>
     </row>
     <row r="98" spans="1:10" s="1" customFormat="1">
-      <c r="A98" s="77" t="s">
+      <c r="A98" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="B98" s="77"/>
-      <c r="C98" s="77"/>
-      <c r="D98" s="77"/>
-      <c r="E98" s="77"/>
-      <c r="F98" s="77"/>
-      <c r="G98" s="77"/>
+      <c r="B98" s="79"/>
+      <c r="C98" s="79"/>
+      <c r="D98" s="79"/>
+      <c r="E98" s="79"/>
+      <c r="F98" s="79"/>
+      <c r="G98" s="79"/>
       <c r="H98" s="38"/>
       <c r="I98" s="38"/>
       <c r="J98" s="38"/>
@@ -4092,15 +4116,15 @@
       <c r="J107" s="54"/>
     </row>
     <row r="108" spans="1:10" s="7" customFormat="1">
-      <c r="A108" s="78" t="s">
+      <c r="A108" s="80" t="s">
         <v>127</v>
       </c>
-      <c r="B108" s="78"/>
-      <c r="C108" s="78"/>
-      <c r="D108" s="78"/>
-      <c r="E108" s="78"/>
-      <c r="F108" s="78"/>
-      <c r="G108" s="78"/>
+      <c r="B108" s="80"/>
+      <c r="C108" s="80"/>
+      <c r="D108" s="80"/>
+      <c r="E108" s="80"/>
+      <c r="F108" s="80"/>
+      <c r="G108" s="80"/>
       <c r="H108" s="36"/>
       <c r="I108" s="36"/>
       <c r="J108" s="36"/>
@@ -4170,29 +4194,29 @@
       <c r="F111" s="6"/>
     </row>
     <row r="112" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A112" s="79" t="s">
+      <c r="A112" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="B112" s="79"/>
-      <c r="C112" s="79"/>
-      <c r="D112" s="79"/>
-      <c r="E112" s="79"/>
-      <c r="F112" s="79"/>
-      <c r="G112" s="79"/>
+      <c r="B112" s="81"/>
+      <c r="C112" s="81"/>
+      <c r="D112" s="81"/>
+      <c r="E112" s="81"/>
+      <c r="F112" s="81"/>
+      <c r="G112" s="81"/>
       <c r="H112" s="34"/>
       <c r="I112" s="34"/>
       <c r="J112" s="34"/>
     </row>
     <row r="113" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A113" s="75" t="s">
+      <c r="A113" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="B113" s="75"/>
-      <c r="C113" s="75"/>
-      <c r="D113" s="75"/>
-      <c r="E113" s="75"/>
-      <c r="F113" s="75"/>
-      <c r="G113" s="75"/>
+      <c r="B113" s="77"/>
+      <c r="C113" s="77"/>
+      <c r="D113" s="77"/>
+      <c r="E113" s="77"/>
+      <c r="F113" s="77"/>
+      <c r="G113" s="77"/>
       <c r="H113" s="33"/>
       <c r="I113" s="33"/>
       <c r="J113" s="33"/>
@@ -4342,15 +4366,15 @@
       <c r="F119" s="6"/>
     </row>
     <row r="120" spans="1:10" s="1" customFormat="1">
-      <c r="A120" s="77" t="s">
+      <c r="A120" s="79" t="s">
         <v>145</v>
       </c>
-      <c r="B120" s="77"/>
-      <c r="C120" s="77"/>
-      <c r="D120" s="77"/>
-      <c r="E120" s="77"/>
-      <c r="F120" s="77"/>
-      <c r="G120" s="77"/>
+      <c r="B120" s="79"/>
+      <c r="C120" s="79"/>
+      <c r="D120" s="79"/>
+      <c r="E120" s="79"/>
+      <c r="F120" s="79"/>
+      <c r="G120" s="79"/>
       <c r="H120" s="38"/>
       <c r="I120" s="38"/>
       <c r="J120" s="38"/>
@@ -4380,29 +4404,29 @@
       <c r="J121" s="37"/>
     </row>
     <row r="122" spans="1:10" s="1" customFormat="1">
-      <c r="A122" s="78" t="s">
+      <c r="A122" s="80" t="s">
         <v>146</v>
       </c>
-      <c r="B122" s="78"/>
-      <c r="C122" s="78"/>
-      <c r="D122" s="78"/>
-      <c r="E122" s="78"/>
-      <c r="F122" s="78"/>
-      <c r="G122" s="78"/>
+      <c r="B122" s="80"/>
+      <c r="C122" s="80"/>
+      <c r="D122" s="80"/>
+      <c r="E122" s="80"/>
+      <c r="F122" s="80"/>
+      <c r="G122" s="80"/>
       <c r="H122" s="36"/>
       <c r="I122" s="36"/>
       <c r="J122" s="36"/>
     </row>
     <row r="123" spans="1:10" s="1" customFormat="1">
-      <c r="A123" s="77" t="s">
+      <c r="A123" s="79" t="s">
         <v>147</v>
       </c>
-      <c r="B123" s="77"/>
-      <c r="C123" s="77"/>
-      <c r="D123" s="77"/>
-      <c r="E123" s="77"/>
-      <c r="F123" s="77"/>
-      <c r="G123" s="77"/>
+      <c r="B123" s="79"/>
+      <c r="C123" s="79"/>
+      <c r="D123" s="79"/>
+      <c r="E123" s="79"/>
+      <c r="F123" s="79"/>
+      <c r="G123" s="79"/>
       <c r="H123" s="38"/>
       <c r="I123" s="38"/>
       <c r="J123" s="38"/>
@@ -4428,29 +4452,29 @@
       <c r="J124" s="56"/>
     </row>
     <row r="125" spans="1:10" s="1" customFormat="1">
-      <c r="A125" s="78" t="s">
+      <c r="A125" s="80" t="s">
         <v>150</v>
       </c>
-      <c r="B125" s="78"/>
-      <c r="C125" s="78"/>
-      <c r="D125" s="78"/>
-      <c r="E125" s="78"/>
-      <c r="F125" s="78"/>
-      <c r="G125" s="78"/>
+      <c r="B125" s="80"/>
+      <c r="C125" s="80"/>
+      <c r="D125" s="80"/>
+      <c r="E125" s="80"/>
+      <c r="F125" s="80"/>
+      <c r="G125" s="80"/>
       <c r="H125" s="36"/>
       <c r="I125" s="36"/>
       <c r="J125" s="36"/>
     </row>
     <row r="126" spans="1:10" s="1" customFormat="1">
-      <c r="A126" s="78" t="s">
+      <c r="A126" s="80" t="s">
         <v>151</v>
       </c>
-      <c r="B126" s="78"/>
-      <c r="C126" s="78"/>
-      <c r="D126" s="78"/>
-      <c r="E126" s="78"/>
-      <c r="F126" s="78"/>
-      <c r="G126" s="78"/>
+      <c r="B126" s="80"/>
+      <c r="C126" s="80"/>
+      <c r="D126" s="80"/>
+      <c r="E126" s="80"/>
+      <c r="F126" s="80"/>
+      <c r="G126" s="80"/>
       <c r="H126" s="36"/>
       <c r="I126" s="36"/>
       <c r="J126" s="36"/>
@@ -4516,15 +4540,15 @@
       <c r="J129" s="37"/>
     </row>
     <row r="130" spans="1:10" s="1" customFormat="1">
-      <c r="A130" s="76" t="s">
+      <c r="A130" s="78" t="s">
         <v>155</v>
       </c>
-      <c r="B130" s="76"/>
-      <c r="C130" s="76"/>
-      <c r="D130" s="76"/>
-      <c r="E130" s="76"/>
-      <c r="F130" s="76"/>
-      <c r="G130" s="76"/>
+      <c r="B130" s="78"/>
+      <c r="C130" s="78"/>
+      <c r="D130" s="78"/>
+      <c r="E130" s="78"/>
+      <c r="F130" s="78"/>
+      <c r="G130" s="78"/>
       <c r="H130" s="39"/>
       <c r="I130" s="39"/>
       <c r="J130" s="39"/>
@@ -4626,29 +4650,29 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="1" customFormat="1">
-      <c r="A136" s="76" t="s">
+      <c r="A136" s="78" t="s">
         <v>157</v>
       </c>
-      <c r="B136" s="76"/>
-      <c r="C136" s="76"/>
-      <c r="D136" s="76"/>
-      <c r="E136" s="76"/>
-      <c r="F136" s="76"/>
-      <c r="G136" s="76"/>
+      <c r="B136" s="78"/>
+      <c r="C136" s="78"/>
+      <c r="D136" s="78"/>
+      <c r="E136" s="78"/>
+      <c r="F136" s="78"/>
+      <c r="G136" s="78"/>
       <c r="H136" s="39"/>
       <c r="I136" s="39"/>
       <c r="J136" s="39"/>
     </row>
     <row r="137" spans="1:10" s="1" customFormat="1">
-      <c r="A137" s="77" t="s">
+      <c r="A137" s="79" t="s">
         <v>158</v>
       </c>
-      <c r="B137" s="77"/>
-      <c r="C137" s="77"/>
-      <c r="D137" s="77"/>
-      <c r="E137" s="77"/>
-      <c r="F137" s="77"/>
-      <c r="G137" s="77"/>
+      <c r="B137" s="79"/>
+      <c r="C137" s="79"/>
+      <c r="D137" s="79"/>
+      <c r="E137" s="79"/>
+      <c r="F137" s="79"/>
+      <c r="G137" s="79"/>
       <c r="H137" s="38"/>
       <c r="I137" s="38"/>
       <c r="J137" s="38"/>
@@ -4748,15 +4772,15 @@
       <c r="J141" s="23"/>
     </row>
     <row r="142" spans="1:10" s="1" customFormat="1">
-      <c r="A142" s="77" t="s">
+      <c r="A142" s="79" t="s">
         <v>163</v>
       </c>
-      <c r="B142" s="77"/>
-      <c r="C142" s="77"/>
-      <c r="D142" s="77"/>
-      <c r="E142" s="77"/>
-      <c r="F142" s="77"/>
-      <c r="G142" s="77"/>
+      <c r="B142" s="79"/>
+      <c r="C142" s="79"/>
+      <c r="D142" s="79"/>
+      <c r="E142" s="79"/>
+      <c r="F142" s="79"/>
+      <c r="G142" s="79"/>
       <c r="H142" s="38"/>
       <c r="I142" s="38"/>
       <c r="J142" s="38"/>
@@ -4825,29 +4849,29 @@
       </c>
     </row>
     <row r="146" spans="1:16379" s="1" customFormat="1">
-      <c r="A146" s="77" t="s">
+      <c r="A146" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="B146" s="77"/>
-      <c r="C146" s="77"/>
-      <c r="D146" s="77"/>
-      <c r="E146" s="77"/>
-      <c r="F146" s="77"/>
-      <c r="G146" s="77"/>
+      <c r="B146" s="79"/>
+      <c r="C146" s="79"/>
+      <c r="D146" s="79"/>
+      <c r="E146" s="79"/>
+      <c r="F146" s="79"/>
+      <c r="G146" s="79"/>
       <c r="H146" s="38"/>
       <c r="I146" s="38"/>
       <c r="J146" s="38"/>
     </row>
     <row r="147" spans="1:16379" s="1" customFormat="1">
-      <c r="A147" s="77" t="s">
+      <c r="A147" s="79" t="s">
         <v>169</v>
       </c>
-      <c r="B147" s="77"/>
-      <c r="C147" s="77"/>
-      <c r="D147" s="77"/>
-      <c r="E147" s="77"/>
-      <c r="F147" s="77"/>
-      <c r="G147" s="77"/>
+      <c r="B147" s="79"/>
+      <c r="C147" s="79"/>
+      <c r="D147" s="79"/>
+      <c r="E147" s="79"/>
+      <c r="F147" s="79"/>
+      <c r="G147" s="79"/>
       <c r="H147" s="38"/>
       <c r="I147" s="38"/>
       <c r="J147" s="38"/>
@@ -52106,57 +52130,57 @@
       <c r="J158" s="61"/>
     </row>
     <row r="159" spans="1:16379" s="1" customFormat="1" ht="19.5">
-      <c r="A159" s="79" t="s">
+      <c r="A159" s="81" t="s">
         <v>179</v>
       </c>
-      <c r="B159" s="79"/>
-      <c r="C159" s="79"/>
-      <c r="D159" s="79"/>
-      <c r="E159" s="79"/>
-      <c r="F159" s="79"/>
-      <c r="G159" s="79"/>
+      <c r="B159" s="81"/>
+      <c r="C159" s="81"/>
+      <c r="D159" s="81"/>
+      <c r="E159" s="81"/>
+      <c r="F159" s="81"/>
+      <c r="G159" s="81"/>
       <c r="H159" s="34"/>
       <c r="I159" s="34"/>
       <c r="J159" s="34"/>
     </row>
     <row r="160" spans="1:16379" s="5" customFormat="1" ht="19.5">
-      <c r="A160" s="75" t="s">
+      <c r="A160" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="B160" s="75"/>
-      <c r="C160" s="75"/>
-      <c r="D160" s="75"/>
-      <c r="E160" s="75"/>
-      <c r="F160" s="75"/>
-      <c r="G160" s="75"/>
+      <c r="B160" s="77"/>
+      <c r="C160" s="77"/>
+      <c r="D160" s="77"/>
+      <c r="E160" s="77"/>
+      <c r="F160" s="77"/>
+      <c r="G160" s="77"/>
       <c r="H160" s="33"/>
       <c r="I160" s="33"/>
       <c r="J160" s="33"/>
     </row>
     <row r="161" spans="1:10" s="1" customFormat="1">
-      <c r="A161" s="76" t="s">
+      <c r="A161" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="B161" s="76"/>
-      <c r="C161" s="76"/>
-      <c r="D161" s="76"/>
-      <c r="E161" s="76"/>
-      <c r="F161" s="76"/>
-      <c r="G161" s="76"/>
+      <c r="B161" s="78"/>
+      <c r="C161" s="78"/>
+      <c r="D161" s="78"/>
+      <c r="E161" s="78"/>
+      <c r="F161" s="78"/>
+      <c r="G161" s="78"/>
       <c r="H161" s="39"/>
       <c r="I161" s="39"/>
       <c r="J161" s="39"/>
     </row>
     <row r="162" spans="1:10" s="1" customFormat="1">
-      <c r="A162" s="78" t="s">
+      <c r="A162" s="80" t="s">
         <v>181</v>
       </c>
-      <c r="B162" s="78"/>
-      <c r="C162" s="78"/>
-      <c r="D162" s="78"/>
-      <c r="E162" s="78"/>
-      <c r="F162" s="78"/>
-      <c r="G162" s="78"/>
+      <c r="B162" s="80"/>
+      <c r="C162" s="80"/>
+      <c r="D162" s="80"/>
+      <c r="E162" s="80"/>
+      <c r="F162" s="80"/>
+      <c r="G162" s="80"/>
       <c r="H162" s="36"/>
       <c r="I162" s="36"/>
       <c r="J162" s="36"/>
@@ -52312,15 +52336,15 @@
       <c r="F169" s="6"/>
     </row>
     <row r="170" spans="1:10" s="1" customFormat="1">
-      <c r="A170" s="78" t="s">
+      <c r="A170" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="B170" s="78"/>
-      <c r="C170" s="78"/>
-      <c r="D170" s="78"/>
-      <c r="E170" s="78"/>
-      <c r="F170" s="78"/>
-      <c r="G170" s="78"/>
+      <c r="B170" s="80"/>
+      <c r="C170" s="80"/>
+      <c r="D170" s="80"/>
+      <c r="E170" s="80"/>
+      <c r="F170" s="80"/>
+      <c r="G170" s="80"/>
       <c r="H170" s="36"/>
       <c r="I170" s="36"/>
       <c r="J170" s="36"/>
@@ -52390,7 +52414,7 @@
         <v>197</v>
       </c>
       <c r="B174" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>25</v>
@@ -52399,133 +52423,133 @@
         <v>15</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="F174" s="6"/>
     </row>
     <row r="175" spans="1:10" s="1" customFormat="1">
       <c r="A175" s="1" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B175" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F175" s="6"/>
     </row>
     <row r="176" spans="1:10" s="1" customFormat="1">
-      <c r="A176" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B176" s="13">
-        <v>46155</v>
+      <c r="A176" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B176" s="11">
+        <v>46156</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F176" s="6"/>
     </row>
     <row r="177" spans="1:10" s="1" customFormat="1">
-      <c r="A177" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B177" s="11">
-        <v>46156</v>
-      </c>
-      <c r="C177" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E177" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F177" s="6"/>
+      <c r="A177" s="79" t="s">
+        <v>198</v>
+      </c>
+      <c r="B177" s="79"/>
+      <c r="C177" s="79"/>
+      <c r="D177" s="79"/>
+      <c r="E177" s="79"/>
+      <c r="F177" s="79"/>
+      <c r="G177" s="79"/>
+      <c r="H177" s="38"/>
+      <c r="I177" s="38"/>
+      <c r="J177" s="38"/>
     </row>
     <row r="178" spans="1:10" s="1" customFormat="1">
-      <c r="A178" s="77" t="s">
-        <v>200</v>
-      </c>
-      <c r="B178" s="77"/>
-      <c r="C178" s="77"/>
-      <c r="D178" s="77"/>
-      <c r="E178" s="77"/>
-      <c r="F178" s="77"/>
-      <c r="G178" s="77"/>
+      <c r="A178" s="79" t="s">
+        <v>199</v>
+      </c>
+      <c r="B178" s="79"/>
+      <c r="C178" s="79"/>
+      <c r="D178" s="79"/>
+      <c r="E178" s="79"/>
+      <c r="F178" s="79"/>
+      <c r="G178" s="79"/>
       <c r="H178" s="38"/>
       <c r="I178" s="38"/>
       <c r="J178" s="38"/>
     </row>
     <row r="179" spans="1:10" s="1" customFormat="1">
-      <c r="A179" s="77" t="s">
-        <v>201</v>
-      </c>
-      <c r="B179" s="77"/>
-      <c r="C179" s="77"/>
-      <c r="D179" s="77"/>
-      <c r="E179" s="77"/>
-      <c r="F179" s="77"/>
-      <c r="G179" s="77"/>
-      <c r="H179" s="38"/>
-      <c r="I179" s="38"/>
-      <c r="J179" s="38"/>
+      <c r="A179" s="80" t="s">
+        <v>200</v>
+      </c>
+      <c r="B179" s="80"/>
+      <c r="C179" s="80"/>
+      <c r="D179" s="80"/>
+      <c r="E179" s="80"/>
+      <c r="F179" s="80"/>
+      <c r="G179" s="80"/>
+      <c r="H179" s="36"/>
+      <c r="I179" s="36"/>
+      <c r="J179" s="36"/>
     </row>
     <row r="180" spans="1:10" s="1" customFormat="1">
-      <c r="A180" s="78" t="s">
+      <c r="A180" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="B180" s="24">
+        <v>46157</v>
+      </c>
+      <c r="C180" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D180" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E180" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F180" s="25">
+        <v>816161</v>
+      </c>
+      <c r="G180" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="B180" s="78"/>
-      <c r="C180" s="78"/>
-      <c r="D180" s="78"/>
-      <c r="E180" s="78"/>
-      <c r="F180" s="78"/>
-      <c r="G180" s="78"/>
-      <c r="H180" s="36"/>
-      <c r="I180" s="36"/>
-      <c r="J180" s="36"/>
+      <c r="H180" s="41"/>
+      <c r="I180" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="J180" s="41"/>
     </row>
     <row r="181" spans="1:10" s="1" customFormat="1">
-      <c r="A181" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="B181" s="24">
-        <v>46157</v>
-      </c>
-      <c r="C181" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D181" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E181" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F181" s="25">
-        <v>816161</v>
-      </c>
-      <c r="G181" s="23" t="s">
+      <c r="A181" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="H181" s="41"/>
-      <c r="I181" s="43" t="s">
+      <c r="B181" s="13">
+        <v>46160</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="J181" s="41"/>
+      <c r="F181" s="6"/>
     </row>
     <row r="182" spans="1:10" s="1" customFormat="1" ht="30.75">
       <c r="A182" s="1" t="s">
@@ -52689,62 +52713,62 @@
       <c r="F189" s="6"/>
     </row>
     <row r="190" spans="1:10" s="1" customFormat="1">
-      <c r="A190" s="76" t="s">
+      <c r="A190" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="B190" s="76"/>
-      <c r="C190" s="76"/>
-      <c r="D190" s="76"/>
-      <c r="E190" s="76"/>
-      <c r="F190" s="76"/>
-      <c r="G190" s="76"/>
+      <c r="B190" s="78"/>
+      <c r="C190" s="78"/>
+      <c r="D190" s="78"/>
+      <c r="E190" s="78"/>
+      <c r="F190" s="78"/>
+      <c r="G190" s="78"/>
       <c r="H190" s="39"/>
       <c r="I190" s="39"/>
       <c r="J190" s="39"/>
     </row>
     <row r="191" spans="1:10" s="1" customFormat="1">
-      <c r="A191" s="77" t="s">
+      <c r="A191" s="79" t="s">
         <v>214</v>
       </c>
-      <c r="B191" s="77"/>
-      <c r="C191" s="77"/>
-      <c r="D191" s="77"/>
-      <c r="E191" s="77"/>
-      <c r="F191" s="77"/>
-      <c r="G191" s="77"/>
+      <c r="B191" s="79"/>
+      <c r="C191" s="79"/>
+      <c r="D191" s="79"/>
+      <c r="E191" s="79"/>
+      <c r="F191" s="79"/>
+      <c r="G191" s="79"/>
       <c r="H191" s="38"/>
       <c r="I191" s="38"/>
       <c r="J191" s="38"/>
     </row>
     <row r="192" spans="1:10" s="1" customFormat="1">
-      <c r="A192" s="77" t="s">
+      <c r="A192" s="79" t="s">
         <v>215</v>
       </c>
-      <c r="B192" s="77"/>
-      <c r="C192" s="77"/>
-      <c r="D192" s="77"/>
-      <c r="E192" s="77"/>
-      <c r="F192" s="77"/>
-      <c r="G192" s="77"/>
+      <c r="B192" s="79"/>
+      <c r="C192" s="79"/>
+      <c r="D192" s="79"/>
+      <c r="E192" s="79"/>
+      <c r="F192" s="79"/>
+      <c r="G192" s="79"/>
       <c r="H192" s="38"/>
       <c r="I192" s="38"/>
       <c r="J192" s="38"/>
     </row>
     <row r="193" spans="1:10" s="1" customFormat="1">
-      <c r="A193" s="78" t="s">
+      <c r="A193" s="80" t="s">
         <v>216</v>
       </c>
-      <c r="B193" s="78"/>
-      <c r="C193" s="78"/>
-      <c r="D193" s="78"/>
-      <c r="E193" s="78"/>
-      <c r="F193" s="78"/>
-      <c r="G193" s="78"/>
+      <c r="B193" s="80"/>
+      <c r="C193" s="80"/>
+      <c r="D193" s="80"/>
+      <c r="E193" s="80"/>
+      <c r="F193" s="80"/>
+      <c r="G193" s="80"/>
       <c r="H193" s="36"/>
       <c r="I193" s="36"/>
       <c r="J193" s="36"/>
     </row>
-    <row r="194" spans="1:10" s="1" customFormat="1">
+    <row r="194" spans="1:10" s="1" customFormat="1" ht="27">
       <c r="A194" s="10" t="s">
         <v>217</v>
       </c>
@@ -52762,7 +52786,7 @@
       <c r="G194" s="70" t="s">
         <v>166</v>
       </c>
-      <c r="H194" s="69" t="s">
+      <c r="H194" s="75" t="s">
         <v>219</v>
       </c>
       <c r="I194" s="69"/>
@@ -52841,8 +52865,8 @@
       <c r="F198" s="6"/>
     </row>
     <row r="199" spans="1:10" s="1" customFormat="1">
-      <c r="A199" s="9" t="s">
-        <v>24</v>
+      <c r="A199" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="B199" s="13">
         <v>46170</v>
@@ -52853,78 +52877,71 @@
       <c r="D199" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E199" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="F199" s="6"/>
     </row>
-    <row r="200" spans="1:10" s="5" customFormat="1" ht="20.25">
-      <c r="A200" s="76" t="s">
-        <v>222</v>
-      </c>
-      <c r="B200" s="76"/>
-      <c r="C200" s="76"/>
-      <c r="D200" s="76"/>
-      <c r="E200" s="76"/>
-      <c r="F200" s="76"/>
-      <c r="G200" s="76"/>
-      <c r="H200" s="39"/>
-      <c r="I200" s="39"/>
-      <c r="J200" s="39"/>
+    <row r="200" spans="1:10" s="1" customFormat="1">
+      <c r="A200" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B200" s="13">
+        <v>46170</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E200" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F200" s="6"/>
     </row>
-    <row r="201" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A201" s="79" t="s">
+    <row r="201" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A201" s="78" t="s">
         <v>223</v>
       </c>
-      <c r="B201" s="79"/>
-      <c r="C201" s="79"/>
-      <c r="D201" s="79"/>
-      <c r="E201" s="79"/>
-      <c r="F201" s="79"/>
-      <c r="G201" s="79"/>
-      <c r="H201" s="34"/>
-      <c r="I201" s="34"/>
-      <c r="J201" s="34"/>
+      <c r="B201" s="78"/>
+      <c r="C201" s="78"/>
+      <c r="D201" s="78"/>
+      <c r="E201" s="78"/>
+      <c r="F201" s="78"/>
+      <c r="G201" s="78"/>
+      <c r="H201" s="39"/>
+      <c r="I201" s="39"/>
+      <c r="J201" s="39"/>
     </row>
-    <row r="202" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A202" s="75" t="s">
+    <row r="202" spans="1:10" s="1" customFormat="1" ht="19.5">
+      <c r="A202" s="81" t="s">
+        <v>224</v>
+      </c>
+      <c r="B202" s="81"/>
+      <c r="C202" s="81"/>
+      <c r="D202" s="81"/>
+      <c r="E202" s="81"/>
+      <c r="F202" s="81"/>
+      <c r="G202" s="81"/>
+      <c r="H202" s="34"/>
+      <c r="I202" s="34"/>
+      <c r="J202" s="34"/>
+    </row>
+    <row r="203" spans="1:10" s="5" customFormat="1" ht="19.5">
+      <c r="A203" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="B202" s="75"/>
-      <c r="C202" s="75"/>
-      <c r="D202" s="75"/>
-      <c r="E202" s="75"/>
-      <c r="F202" s="75"/>
-      <c r="G202" s="75"/>
-      <c r="H202" s="33"/>
-      <c r="I202" s="33"/>
-      <c r="J202" s="33"/>
-    </row>
-    <row r="203" spans="1:10" s="1" customFormat="1">
-      <c r="A203" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="B203" s="24">
-        <v>46174</v>
-      </c>
-      <c r="C203" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D203" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E203" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="F203" s="25"/>
-      <c r="G203" s="23"/>
-      <c r="H203" s="37"/>
-      <c r="I203" s="37"/>
-      <c r="J203" s="37"/>
+      <c r="B203" s="77"/>
+      <c r="C203" s="77"/>
+      <c r="D203" s="77"/>
+      <c r="E203" s="77"/>
+      <c r="F203" s="77"/>
+      <c r="G203" s="77"/>
+      <c r="H203" s="33"/>
+      <c r="I203" s="33"/>
+      <c r="J203" s="33"/>
     </row>
     <row r="204" spans="1:10" s="1" customFormat="1">
       <c r="A204" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B204" s="24">
         <v>46174</v>
@@ -52936,38 +52953,46 @@
         <v>19</v>
       </c>
       <c r="E204" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F204" s="25"/>
+        <v>226</v>
+      </c>
+      <c r="F204" s="25">
+        <v>816163</v>
+      </c>
       <c r="G204" s="23"/>
       <c r="H204" s="37"/>
       <c r="I204" s="37"/>
       <c r="J204" s="37"/>
     </row>
     <row r="205" spans="1:10" s="1" customFormat="1">
-      <c r="A205" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B205" s="13">
+      <c r="A205" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="B205" s="24">
         <v>46174</v>
       </c>
-      <c r="C205" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F205" s="6"/>
+      <c r="C205" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D205" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E205" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F205" s="25">
+        <v>816164</v>
+      </c>
+      <c r="G205" s="23"/>
+      <c r="H205" s="37"/>
+      <c r="I205" s="37"/>
+      <c r="J205" s="37"/>
     </row>
     <row r="206" spans="1:10" s="1" customFormat="1">
       <c r="A206" s="1" t="s">
-        <v>227</v>
+        <v>13</v>
       </c>
       <c r="B206" s="13">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>14</v>
@@ -52976,57 +53001,55 @@
         <v>15</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F206" s="6"/>
     </row>
     <row r="207" spans="1:10" s="1" customFormat="1">
-      <c r="A207" s="23" t="s">
+      <c r="A207" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B207" s="24">
+      <c r="B207" s="13">
         <v>46175</v>
       </c>
-      <c r="C207" s="25" t="s">
+      <c r="C207" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F207" s="6"/>
+    </row>
+    <row r="208" spans="1:10" s="1" customFormat="1">
+      <c r="A208" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="B208" s="24">
+        <v>46175</v>
+      </c>
+      <c r="C208" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D207" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E207" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F207" s="25"/>
-      <c r="G207" s="23"/>
-      <c r="H207" s="37"/>
-      <c r="I207" s="37"/>
-      <c r="J207" s="37"/>
+      <c r="D208" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E208" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F208" s="25">
+        <v>816233</v>
+      </c>
+      <c r="G208" s="23"/>
+      <c r="H208" s="37"/>
+      <c r="I208" s="37"/>
+      <c r="J208" s="37"/>
     </row>
-    <row r="208" spans="1:10" s="7" customFormat="1">
-      <c r="A208" s="9" t="s">
+    <row r="209" spans="1:10" s="7" customFormat="1">
+      <c r="A209" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="B208" s="13">
-        <v>46176</v>
-      </c>
-      <c r="C208" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E208" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F208" s="6"/>
-      <c r="G208" s="1"/>
-      <c r="H208" s="40"/>
-      <c r="I208" s="40"/>
-      <c r="J208" s="40"/>
-    </row>
-    <row r="209" spans="1:10" s="1" customFormat="1">
-      <c r="A209" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="B209" s="13">
         <v>46176</v>
@@ -53035,254 +53058,264 @@
         <v>14</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="E209" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F209" s="6"/>
+      <c r="G209" s="1"/>
+      <c r="H209" s="40"/>
+      <c r="I209" s="40"/>
+      <c r="J209" s="40"/>
     </row>
     <row r="210" spans="1:10" s="1" customFormat="1">
-      <c r="A210" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B210" s="11">
-        <v>46177</v>
+      <c r="A210" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B210" s="13">
+        <v>46176</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E210" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F210" s="6"/>
     </row>
     <row r="211" spans="1:10" s="1" customFormat="1">
-      <c r="A211" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B211" s="13">
-        <v>46181</v>
+      <c r="A211" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B211" s="11">
+        <v>46177</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E211" s="1" t="s">
-        <v>16</v>
+      <c r="E211" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F211" s="6"/>
     </row>
     <row r="212" spans="1:10" s="1" customFormat="1">
-      <c r="A212" s="76" t="s">
-        <v>229</v>
-      </c>
-      <c r="B212" s="76"/>
-      <c r="C212" s="76"/>
-      <c r="D212" s="76"/>
-      <c r="E212" s="76"/>
-      <c r="F212" s="76"/>
-      <c r="G212" s="76"/>
-      <c r="H212" s="39"/>
-      <c r="I212" s="39"/>
-      <c r="J212" s="39"/>
+      <c r="A212" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B212" s="13">
+        <v>46181</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F212" s="6"/>
     </row>
     <row r="213" spans="1:10" s="1" customFormat="1">
-      <c r="A213" s="23" t="s">
+      <c r="A213" s="78" t="s">
         <v>230</v>
       </c>
-      <c r="B213" s="24">
-        <v>46182</v>
-      </c>
-      <c r="C213" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D213" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E213" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F213" s="25"/>
-      <c r="G213" s="23"/>
-      <c r="H213" s="37"/>
-      <c r="I213" s="37"/>
-      <c r="J213" s="37"/>
+      <c r="B213" s="78"/>
+      <c r="C213" s="78"/>
+      <c r="D213" s="78"/>
+      <c r="E213" s="78"/>
+      <c r="F213" s="78"/>
+      <c r="G213" s="78"/>
+      <c r="H213" s="39"/>
+      <c r="I213" s="39"/>
+      <c r="J213" s="39"/>
     </row>
     <row r="214" spans="1:10" s="1" customFormat="1">
-      <c r="A214" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B214" s="13">
-        <v>46183</v>
-      </c>
-      <c r="C214" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F214" s="6"/>
+      <c r="A214" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="B214" s="24">
+        <v>46182</v>
+      </c>
+      <c r="C214" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D214" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E214" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F214" s="25">
+        <v>816232</v>
+      </c>
+      <c r="G214" s="23"/>
+      <c r="H214" s="37"/>
+      <c r="I214" s="37"/>
+      <c r="J214" s="37"/>
     </row>
     <row r="215" spans="1:10" s="1" customFormat="1">
-      <c r="A215" s="9" t="s">
-        <v>24</v>
+      <c r="A215" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B215" s="13">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E215" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F215" s="6"/>
     </row>
     <row r="216" spans="1:10" s="1" customFormat="1">
-      <c r="A216" s="78" t="s">
-        <v>231</v>
-      </c>
-      <c r="B216" s="78"/>
-      <c r="C216" s="78"/>
-      <c r="D216" s="78"/>
-      <c r="E216" s="78"/>
-      <c r="F216" s="78"/>
-      <c r="G216" s="78"/>
-      <c r="H216" s="36"/>
-      <c r="I216" s="36"/>
-      <c r="J216" s="36"/>
+      <c r="A216" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B216" s="13">
+        <v>46184</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E216" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F216" s="6"/>
     </row>
     <row r="217" spans="1:10" s="1" customFormat="1">
-      <c r="A217" s="23" t="s">
+      <c r="A217" s="80" t="s">
         <v>232</v>
       </c>
-      <c r="B217" s="24">
-        <v>46188</v>
-      </c>
-      <c r="C217" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D217" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E217" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="F217" s="26"/>
-      <c r="G217" s="26"/>
-      <c r="H217" s="41"/>
-      <c r="I217" s="41"/>
-      <c r="J217" s="41"/>
+      <c r="B217" s="80"/>
+      <c r="C217" s="80"/>
+      <c r="D217" s="80"/>
+      <c r="E217" s="80"/>
+      <c r="F217" s="80"/>
+      <c r="G217" s="80"/>
+      <c r="H217" s="36"/>
+      <c r="I217" s="36"/>
+      <c r="J217" s="36"/>
     </row>
     <row r="218" spans="1:10" s="1" customFormat="1">
-      <c r="A218" s="1" t="s">
+      <c r="A218" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="B218" s="24">
+        <v>46188</v>
+      </c>
+      <c r="C218" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D218" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E218" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="B218" s="13">
-        <v>46188</v>
-      </c>
-      <c r="C218" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F218" s="67"/>
-      <c r="G218" s="67"/>
-      <c r="H218" s="68"/>
-      <c r="I218" s="68"/>
-      <c r="J218" s="68"/>
+      <c r="F218" s="25">
+        <v>816166</v>
+      </c>
+      <c r="G218" s="26"/>
+      <c r="H218" s="41"/>
+      <c r="I218" s="41"/>
+      <c r="J218" s="41"/>
     </row>
     <row r="219" spans="1:10" s="1" customFormat="1">
       <c r="A219" s="1" t="s">
-        <v>13</v>
+        <v>235</v>
       </c>
       <c r="B219" s="13">
         <v>46188</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F219" s="6"/>
+        <v>236</v>
+      </c>
+      <c r="F219" s="67"/>
+      <c r="G219" s="67"/>
+      <c r="H219" s="68"/>
+      <c r="I219" s="68"/>
+      <c r="J219" s="68"/>
     </row>
     <row r="220" spans="1:10" s="1" customFormat="1">
-      <c r="A220" s="77" t="s">
-        <v>236</v>
-      </c>
-      <c r="B220" s="77"/>
-      <c r="C220" s="77"/>
-      <c r="D220" s="77"/>
-      <c r="E220" s="77"/>
-      <c r="F220" s="77"/>
-      <c r="G220" s="77"/>
-      <c r="H220" s="38"/>
-      <c r="I220" s="38"/>
-      <c r="J220" s="38"/>
+      <c r="A220" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B220" s="13">
+        <v>46188</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F220" s="6"/>
     </row>
     <row r="221" spans="1:10" s="1" customFormat="1">
-      <c r="A221" s="23" t="s">
+      <c r="A221" s="79" t="s">
         <v>237</v>
       </c>
-      <c r="B221" s="24">
-        <v>46189</v>
-      </c>
-      <c r="C221" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D221" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E221" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F221" s="25"/>
-      <c r="G221" s="23"/>
-      <c r="H221" s="37"/>
-      <c r="I221" s="37"/>
-      <c r="J221" s="37"/>
+      <c r="B221" s="79"/>
+      <c r="C221" s="79"/>
+      <c r="D221" s="79"/>
+      <c r="E221" s="79"/>
+      <c r="F221" s="79"/>
+      <c r="G221" s="79"/>
+      <c r="H221" s="38"/>
+      <c r="I221" s="38"/>
+      <c r="J221" s="38"/>
     </row>
     <row r="222" spans="1:10" s="1" customFormat="1">
-      <c r="A222" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B222" s="13">
-        <v>46190</v>
-      </c>
-      <c r="C222" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F222" s="6"/>
+      <c r="A222" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="B222" s="24">
+        <v>46189</v>
+      </c>
+      <c r="C222" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D222" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E222" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F222" s="25">
+        <v>816232</v>
+      </c>
+      <c r="G222" s="23"/>
+      <c r="H222" s="37"/>
+      <c r="I222" s="37"/>
+      <c r="J222" s="37"/>
     </row>
     <row r="223" spans="1:10" s="1" customFormat="1">
-      <c r="A223" s="9" t="s">
-        <v>28</v>
+      <c r="A223" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B223" s="13">
         <v>46190</v>
@@ -53291,22 +53324,22 @@
         <v>14</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E223" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F223" s="6"/>
     </row>
     <row r="224" spans="1:10" s="1" customFormat="1">
-      <c r="A224" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B224" s="11">
-        <v>46191</v>
+      <c r="A224" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B224" s="13">
+        <v>46190</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>15</v>
@@ -53317,244 +53350,246 @@
       <c r="F224" s="6"/>
     </row>
     <row r="225" spans="1:10" s="1" customFormat="1">
-      <c r="A225" s="78" t="s">
-        <v>238</v>
-      </c>
-      <c r="B225" s="78"/>
-      <c r="C225" s="78"/>
-      <c r="D225" s="78"/>
-      <c r="E225" s="78"/>
-      <c r="F225" s="78"/>
-      <c r="G225" s="78"/>
-      <c r="H225" s="36"/>
-      <c r="I225" s="36"/>
-      <c r="J225" s="36"/>
+      <c r="A225" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B225" s="11">
+        <v>46191</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E225" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F225" s="6"/>
     </row>
     <row r="226" spans="1:10" s="1" customFormat="1">
-      <c r="A226" s="78" t="s">
+      <c r="A226" s="80" t="s">
         <v>239</v>
       </c>
-      <c r="B226" s="78"/>
-      <c r="C226" s="78"/>
-      <c r="D226" s="78"/>
-      <c r="E226" s="78"/>
-      <c r="F226" s="78"/>
-      <c r="G226" s="78"/>
+      <c r="B226" s="80"/>
+      <c r="C226" s="80"/>
+      <c r="D226" s="80"/>
+      <c r="E226" s="80"/>
+      <c r="F226" s="80"/>
+      <c r="G226" s="80"/>
       <c r="H226" s="36"/>
       <c r="I226" s="36"/>
       <c r="J226" s="36"/>
     </row>
     <row r="227" spans="1:10" s="1" customFormat="1">
-      <c r="A227" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B227" s="13">
-        <v>46195</v>
-      </c>
-      <c r="C227" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E227" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F227" s="6"/>
+      <c r="A227" s="80" t="s">
+        <v>240</v>
+      </c>
+      <c r="B227" s="80"/>
+      <c r="C227" s="80"/>
+      <c r="D227" s="80"/>
+      <c r="E227" s="80"/>
+      <c r="F227" s="80"/>
+      <c r="G227" s="80"/>
+      <c r="H227" s="36"/>
+      <c r="I227" s="36"/>
+      <c r="J227" s="36"/>
     </row>
     <row r="228" spans="1:10" s="1" customFormat="1">
-      <c r="A228" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B228" s="24">
-        <v>46196</v>
-      </c>
-      <c r="C228" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D228" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E228" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F228" s="25"/>
-      <c r="G228" s="23"/>
-      <c r="H228" s="37"/>
-      <c r="I228" s="37"/>
-      <c r="J228" s="37"/>
+      <c r="A228" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B228" s="13">
+        <v>46195</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F228" s="6"/>
     </row>
     <row r="229" spans="1:10" s="1" customFormat="1">
-      <c r="A229" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B229" s="13">
-        <v>46197</v>
-      </c>
-      <c r="C229" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E229" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F229" s="6"/>
+      <c r="A229" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="B229" s="24">
+        <v>46196</v>
+      </c>
+      <c r="C229" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D229" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E229" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F229" s="25">
+        <v>816234</v>
+      </c>
+      <c r="G229" s="23"/>
+      <c r="H229" s="37"/>
+      <c r="I229" s="37"/>
+      <c r="J229" s="37"/>
     </row>
     <row r="230" spans="1:10" s="1" customFormat="1">
-      <c r="A230" s="9" t="s">
-        <v>24</v>
+      <c r="A230" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B230" s="13">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E230" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F230" s="6"/>
     </row>
     <row r="231" spans="1:10" s="1" customFormat="1">
-      <c r="A231" s="1" t="s">
-        <v>13</v>
+      <c r="A231" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="B231" s="13">
-        <v>46202</v>
+        <v>46198</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E231" s="1" t="s">
-        <v>16</v>
+      <c r="E231" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F231" s="6"/>
     </row>
-    <row r="232" spans="1:10" s="7" customFormat="1">
-      <c r="A232" s="76" t="s">
-        <v>241</v>
-      </c>
-      <c r="B232" s="76"/>
-      <c r="C232" s="76"/>
-      <c r="D232" s="76"/>
-      <c r="E232" s="76"/>
-      <c r="F232" s="76"/>
-      <c r="G232" s="76"/>
-      <c r="H232" s="39"/>
-      <c r="I232" s="39"/>
-      <c r="J232" s="39"/>
+    <row r="232" spans="1:10" s="1" customFormat="1">
+      <c r="A232" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B232" s="13">
+        <v>46202</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F232" s="6"/>
     </row>
-    <row r="233" spans="1:10" s="5" customFormat="1" ht="20.25">
-      <c r="A233" s="23" t="s">
+    <row r="233" spans="1:10" s="7" customFormat="1">
+      <c r="A233" s="78" t="s">
         <v>242</v>
       </c>
-      <c r="B233" s="24">
+      <c r="B233" s="78"/>
+      <c r="C233" s="78"/>
+      <c r="D233" s="78"/>
+      <c r="E233" s="78"/>
+      <c r="F233" s="78"/>
+      <c r="G233" s="78"/>
+      <c r="H233" s="39"/>
+      <c r="I233" s="39"/>
+      <c r="J233" s="39"/>
+    </row>
+    <row r="234" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A234" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="B234" s="24">
         <v>46203</v>
       </c>
-      <c r="C233" s="25" t="s">
+      <c r="C234" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D233" s="23" t="s">
+      <c r="D234" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="E233" s="23" t="s">
+      <c r="E234" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="F233" s="25"/>
-      <c r="G233" s="23"/>
-      <c r="H233" s="37"/>
-      <c r="I233" s="37"/>
-      <c r="J233" s="37"/>
+      <c r="F234" s="25"/>
+      <c r="G234" s="23"/>
+      <c r="H234" s="37"/>
+      <c r="I234" s="37"/>
+      <c r="J234" s="37"/>
     </row>
-    <row r="234" spans="1:10" s="1" customFormat="1">
-      <c r="A234" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B234" s="13">
+    <row r="235" spans="1:10" s="1" customFormat="1">
+      <c r="A235" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B235" s="13">
         <v>46203</v>
       </c>
-      <c r="C234" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E234" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F234" s="6"/>
+      <c r="C235" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F235" s="6"/>
     </row>
-    <row r="235" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A235" s="79" t="s">
-        <v>243</v>
-      </c>
-      <c r="B235" s="79"/>
-      <c r="C235" s="79"/>
-      <c r="D235" s="79"/>
-      <c r="E235" s="79"/>
-      <c r="F235" s="79"/>
-      <c r="G235" s="79"/>
-      <c r="H235" s="34"/>
-      <c r="I235" s="34"/>
-      <c r="J235" s="34"/>
+    <row r="236" spans="1:10" s="1" customFormat="1" ht="19.5">
+      <c r="A236" s="81" t="s">
+        <v>244</v>
+      </c>
+      <c r="B236" s="81"/>
+      <c r="C236" s="81"/>
+      <c r="D236" s="81"/>
+      <c r="E236" s="81"/>
+      <c r="F236" s="81"/>
+      <c r="G236" s="81"/>
+      <c r="H236" s="34"/>
+      <c r="I236" s="34"/>
+      <c r="J236" s="34"/>
     </row>
-    <row r="236" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A236" s="75" t="s">
+    <row r="237" spans="1:10" s="5" customFormat="1" ht="19.5">
+      <c r="A237" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="B236" s="75"/>
-      <c r="C236" s="75"/>
-      <c r="D236" s="75"/>
-      <c r="E236" s="75"/>
-      <c r="F236" s="75"/>
-      <c r="G236" s="75"/>
-      <c r="H236" s="33"/>
-      <c r="I236" s="33"/>
-      <c r="J236" s="33"/>
-    </row>
-    <row r="237" spans="1:10" s="1" customFormat="1">
-      <c r="A237" s="78" t="s">
-        <v>244</v>
-      </c>
-      <c r="B237" s="78"/>
-      <c r="C237" s="78"/>
-      <c r="D237" s="78"/>
-      <c r="E237" s="78"/>
-      <c r="F237" s="78"/>
-      <c r="G237" s="78"/>
-      <c r="H237" s="36"/>
-      <c r="I237" s="36"/>
-      <c r="J237" s="36"/>
+      <c r="B237" s="77"/>
+      <c r="C237" s="77"/>
+      <c r="D237" s="77"/>
+      <c r="E237" s="77"/>
+      <c r="F237" s="77"/>
+      <c r="G237" s="77"/>
+      <c r="H237" s="33"/>
+      <c r="I237" s="33"/>
+      <c r="J237" s="33"/>
     </row>
     <row r="238" spans="1:10" s="1" customFormat="1">
-      <c r="A238" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B238" s="13">
-        <v>46204</v>
-      </c>
-      <c r="C238" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D238" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E238" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F238" s="6"/>
+      <c r="A238" s="80" t="s">
+        <v>245</v>
+      </c>
+      <c r="B238" s="80"/>
+      <c r="C238" s="80"/>
+      <c r="D238" s="80"/>
+      <c r="E238" s="80"/>
+      <c r="F238" s="80"/>
+      <c r="G238" s="80"/>
+      <c r="H238" s="36"/>
+      <c r="I238" s="36"/>
+      <c r="J238" s="36"/>
     </row>
     <row r="239" spans="1:10" s="1" customFormat="1">
-      <c r="A239" s="9" t="s">
-        <v>28</v>
+      <c r="A239" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B239" s="13">
         <v>46204</v>
@@ -53563,22 +53598,22 @@
         <v>14</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E239" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F239" s="6"/>
     </row>
     <row r="240" spans="1:10" s="1" customFormat="1">
-      <c r="A240" s="10" t="s">
-        <v>24</v>
+      <c r="A240" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B240" s="13">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>15</v>
@@ -53589,166 +53624,166 @@
       <c r="F240" s="6"/>
     </row>
     <row r="241" spans="1:10" s="1" customFormat="1">
-      <c r="A241" s="78" t="s">
-        <v>245</v>
-      </c>
-      <c r="B241" s="78"/>
-      <c r="C241" s="78"/>
-      <c r="D241" s="78"/>
-      <c r="E241" s="78"/>
-      <c r="F241" s="78"/>
-      <c r="G241" s="78"/>
-      <c r="H241" s="36"/>
-      <c r="I241" s="36"/>
-      <c r="J241" s="36"/>
+      <c r="A241" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B241" s="13">
+        <v>46205</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E241" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F241" s="6"/>
     </row>
     <row r="242" spans="1:10" s="1" customFormat="1">
-      <c r="A242" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B242" s="13">
-        <v>46209</v>
-      </c>
-      <c r="C242" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E242" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F242" s="6"/>
+      <c r="A242" s="80" t="s">
+        <v>246</v>
+      </c>
+      <c r="B242" s="80"/>
+      <c r="C242" s="80"/>
+      <c r="D242" s="80"/>
+      <c r="E242" s="80"/>
+      <c r="F242" s="80"/>
+      <c r="G242" s="80"/>
+      <c r="H242" s="36"/>
+      <c r="I242" s="36"/>
+      <c r="J242" s="36"/>
     </row>
     <row r="243" spans="1:10" s="1" customFormat="1">
       <c r="A243" s="1" t="s">
-        <v>246</v>
+        <v>13</v>
       </c>
       <c r="B243" s="13">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F243" s="6"/>
     </row>
     <row r="244" spans="1:10" s="1" customFormat="1">
       <c r="A244" s="1" t="s">
-        <v>22</v>
+        <v>247</v>
       </c>
       <c r="B244" s="13">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F244" s="6"/>
     </row>
     <row r="245" spans="1:10" s="1" customFormat="1">
-      <c r="A245" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B245" s="11">
-        <v>46212</v>
+      <c r="A245" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B245" s="13">
+        <v>46211</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E245" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F245" s="6"/>
     </row>
     <row r="246" spans="1:10" s="1" customFormat="1">
-      <c r="A246" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B246" s="24">
-        <v>46213</v>
-      </c>
-      <c r="C246" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D246" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E246" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F246" s="25"/>
-      <c r="G246" s="23"/>
-      <c r="H246" s="37"/>
-      <c r="I246" s="37"/>
-      <c r="J246" s="37"/>
+      <c r="A246" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B246" s="11">
+        <v>46212</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E246" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F246" s="6"/>
     </row>
     <row r="247" spans="1:10" s="1" customFormat="1">
-      <c r="A247" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B247" s="13">
-        <v>46216</v>
-      </c>
-      <c r="C247" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D247" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E247" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F247" s="6"/>
+      <c r="A247" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="B247" s="24">
+        <v>46213</v>
+      </c>
+      <c r="C247" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D247" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E247" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F247" s="25"/>
+      <c r="G247" s="23"/>
+      <c r="H247" s="37"/>
+      <c r="I247" s="37"/>
+      <c r="J247" s="37"/>
     </row>
     <row r="248" spans="1:10" s="1" customFormat="1">
-      <c r="A248" s="77" t="s">
-        <v>248</v>
-      </c>
-      <c r="B248" s="77"/>
-      <c r="C248" s="77"/>
-      <c r="D248" s="77"/>
-      <c r="E248" s="77"/>
-      <c r="F248" s="77"/>
-      <c r="G248" s="77"/>
-      <c r="H248" s="38"/>
-      <c r="I248" s="38"/>
-      <c r="J248" s="38"/>
+      <c r="A248" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B248" s="13">
+        <v>46216</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F248" s="6"/>
     </row>
     <row r="249" spans="1:10" s="1" customFormat="1">
-      <c r="A249" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B249" s="13">
-        <v>46218</v>
-      </c>
-      <c r="C249" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E249" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F249" s="6"/>
+      <c r="A249" s="79" t="s">
+        <v>249</v>
+      </c>
+      <c r="B249" s="79"/>
+      <c r="C249" s="79"/>
+      <c r="D249" s="79"/>
+      <c r="E249" s="79"/>
+      <c r="F249" s="79"/>
+      <c r="G249" s="79"/>
+      <c r="H249" s="38"/>
+      <c r="I249" s="38"/>
+      <c r="J249" s="38"/>
     </row>
     <row r="250" spans="1:10" s="1" customFormat="1">
-      <c r="A250" s="9" t="s">
-        <v>28</v>
+      <c r="A250" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B250" s="13">
         <v>46218</v>
@@ -53757,22 +53792,22 @@
         <v>14</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E250" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F250" s="6"/>
     </row>
     <row r="251" spans="1:10" s="1" customFormat="1">
-      <c r="A251" s="10" t="s">
-        <v>24</v>
+      <c r="A251" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B251" s="13">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>15</v>
@@ -53783,57 +53818,57 @@
       <c r="F251" s="6"/>
     </row>
     <row r="252" spans="1:10" s="1" customFormat="1">
-      <c r="A252" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="B252" s="24">
-        <v>46223</v>
-      </c>
-      <c r="C252" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D252" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E252" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F252" s="25"/>
-      <c r="G252" s="23"/>
-      <c r="H252" s="37"/>
-      <c r="I252" s="37"/>
-      <c r="J252" s="37"/>
+      <c r="A252" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B252" s="13">
+        <v>46219</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E252" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F252" s="6"/>
     </row>
     <row r="253" spans="1:10" s="1" customFormat="1">
-      <c r="A253" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B253" s="13">
+      <c r="A253" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="B253" s="24">
         <v>46223</v>
       </c>
-      <c r="C253" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D253" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E253" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F253" s="6"/>
+      <c r="C253" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D253" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E253" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F253" s="25"/>
+      <c r="G253" s="23"/>
+      <c r="H253" s="37"/>
+      <c r="I253" s="37"/>
+      <c r="J253" s="37"/>
     </row>
     <row r="254" spans="1:10" s="1" customFormat="1">
       <c r="A254" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B254" s="13">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="C254" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>16</v>
@@ -53841,112 +53876,108 @@
       <c r="F254" s="6"/>
     </row>
     <row r="255" spans="1:10" s="1" customFormat="1">
-      <c r="A255" s="77" t="s">
-        <v>250</v>
-      </c>
-      <c r="B255" s="77"/>
-      <c r="C255" s="77"/>
-      <c r="D255" s="77"/>
-      <c r="E255" s="77"/>
-      <c r="F255" s="77"/>
-      <c r="G255" s="77"/>
-      <c r="H255" s="38"/>
-      <c r="I255" s="38"/>
-      <c r="J255" s="38"/>
+      <c r="A255" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B255" s="13">
+        <v>46225</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F255" s="6"/>
     </row>
     <row r="256" spans="1:10" s="1" customFormat="1">
-      <c r="A256" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B256" s="11">
-        <v>46226</v>
-      </c>
-      <c r="C256" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E256" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F256" s="6"/>
+      <c r="A256" s="79" t="s">
+        <v>251</v>
+      </c>
+      <c r="B256" s="79"/>
+      <c r="C256" s="79"/>
+      <c r="D256" s="79"/>
+      <c r="E256" s="79"/>
+      <c r="F256" s="79"/>
+      <c r="G256" s="79"/>
+      <c r="H256" s="38"/>
+      <c r="I256" s="38"/>
+      <c r="J256" s="38"/>
     </row>
     <row r="257" spans="1:10" s="1" customFormat="1">
-      <c r="A257" s="76" t="s">
-        <v>251</v>
-      </c>
-      <c r="B257" s="76"/>
-      <c r="C257" s="76"/>
-      <c r="D257" s="76"/>
-      <c r="E257" s="76"/>
-      <c r="F257" s="76"/>
-      <c r="G257" s="76"/>
-      <c r="H257" s="39"/>
-      <c r="I257" s="39"/>
-      <c r="J257" s="39"/>
+      <c r="A257" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B257" s="11">
+        <v>46226</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E257" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F257" s="6"/>
     </row>
     <row r="258" spans="1:10" s="1" customFormat="1">
-      <c r="A258" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B258" s="13">
-        <v>46230</v>
-      </c>
-      <c r="C258" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D258" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E258" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F258" s="6"/>
+      <c r="A258" s="78" t="s">
+        <v>252</v>
+      </c>
+      <c r="B258" s="78"/>
+      <c r="C258" s="78"/>
+      <c r="D258" s="78"/>
+      <c r="E258" s="78"/>
+      <c r="F258" s="78"/>
+      <c r="G258" s="78"/>
+      <c r="H258" s="39"/>
+      <c r="I258" s="39"/>
+      <c r="J258" s="39"/>
     </row>
     <row r="259" spans="1:10" s="1" customFormat="1">
       <c r="A259" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B259" s="13">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F259" s="6"/>
     </row>
-    <row r="260" spans="1:10" s="7" customFormat="1">
+    <row r="260" spans="1:10" s="1" customFormat="1">
       <c r="A260" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B260" s="13">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F260" s="6"/>
-      <c r="G260" s="1"/>
-      <c r="H260" s="40"/>
-      <c r="I260" s="40"/>
-      <c r="J260" s="40"/>
     </row>
     <row r="261" spans="1:10" s="7" customFormat="1">
-      <c r="A261" s="9" t="s">
-        <v>28</v>
+      <c r="A261" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B261" s="13">
         <v>46232</v>
@@ -53955,10 +53986,10 @@
         <v>14</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E261" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F261" s="6"/>
       <c r="G261" s="1"/>
@@ -53966,15 +53997,15 @@
       <c r="I261" s="40"/>
       <c r="J261" s="40"/>
     </row>
-    <row r="262" spans="1:10" s="5" customFormat="1" ht="20.25">
-      <c r="A262" s="10" t="s">
-        <v>24</v>
+    <row r="262" spans="1:10" s="7" customFormat="1">
+      <c r="A262" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B262" s="13">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>15</v>
@@ -53982,63 +54013,71 @@
       <c r="E262" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F262" s="65"/>
-      <c r="G262" s="7"/>
-      <c r="H262" s="42"/>
-      <c r="I262" s="42"/>
-      <c r="J262" s="42"/>
+      <c r="F262" s="6"/>
+      <c r="G262" s="1"/>
+      <c r="H262" s="40"/>
+      <c r="I262" s="40"/>
+      <c r="J262" s="40"/>
     </row>
-    <row r="263" spans="1:10" s="1" customFormat="1">
-      <c r="A263" s="9"/>
-      <c r="B263" s="13"/>
-      <c r="C263" s="8"/>
-      <c r="F263" s="6"/>
+    <row r="263" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A263" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B263" s="13">
+        <v>46233</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E263" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F263" s="65"/>
       <c r="G263" s="7"/>
       <c r="H263" s="42"/>
       <c r="I263" s="42"/>
       <c r="J263" s="42"/>
     </row>
-    <row r="264" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A264" s="79" t="s">
-        <v>252</v>
-      </c>
-      <c r="B264" s="79"/>
-      <c r="C264" s="79"/>
-      <c r="D264" s="79"/>
-      <c r="E264" s="79"/>
-      <c r="F264" s="79"/>
-      <c r="G264" s="79"/>
-      <c r="H264" s="34"/>
-      <c r="I264" s="34"/>
-      <c r="J264" s="34"/>
+    <row r="264" spans="1:10" s="1" customFormat="1">
+      <c r="A264" s="9"/>
+      <c r="B264" s="13"/>
+      <c r="C264" s="8"/>
+      <c r="F264" s="6"/>
+      <c r="G264" s="7"/>
+      <c r="H264" s="42"/>
+      <c r="I264" s="42"/>
+      <c r="J264" s="42"/>
     </row>
-    <row r="265" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A265" s="75" t="s">
+    <row r="265" spans="1:10" s="1" customFormat="1" ht="19.5">
+      <c r="A265" s="81" t="s">
+        <v>253</v>
+      </c>
+      <c r="B265" s="81"/>
+      <c r="C265" s="81"/>
+      <c r="D265" s="81"/>
+      <c r="E265" s="81"/>
+      <c r="F265" s="81"/>
+      <c r="G265" s="81"/>
+      <c r="H265" s="34"/>
+      <c r="I265" s="34"/>
+      <c r="J265" s="34"/>
+    </row>
+    <row r="266" spans="1:10" s="5" customFormat="1" ht="19.5">
+      <c r="A266" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="B265" s="75"/>
-      <c r="C265" s="75"/>
-      <c r="D265" s="75"/>
-      <c r="E265" s="75"/>
-      <c r="F265" s="75"/>
-      <c r="G265" s="75"/>
-      <c r="H265" s="33"/>
-      <c r="I265" s="33"/>
-      <c r="J265" s="33"/>
-    </row>
-    <row r="266" spans="1:10" s="1" customFormat="1">
-      <c r="A266" s="76" t="s">
-        <v>253</v>
-      </c>
-      <c r="B266" s="76"/>
-      <c r="C266" s="76"/>
-      <c r="D266" s="76"/>
-      <c r="E266" s="76"/>
-      <c r="F266" s="76"/>
-      <c r="G266" s="76"/>
-      <c r="H266" s="39"/>
-      <c r="I266" s="39"/>
-      <c r="J266" s="39"/>
+      <c r="B266" s="77"/>
+      <c r="C266" s="77"/>
+      <c r="D266" s="77"/>
+      <c r="E266" s="77"/>
+      <c r="F266" s="77"/>
+      <c r="G266" s="77"/>
+      <c r="H266" s="33"/>
+      <c r="I266" s="33"/>
+      <c r="J266" s="33"/>
     </row>
     <row r="267" spans="1:10" s="1" customFormat="1">
       <c r="A267" s="78" t="s">
@@ -54050,56 +54089,52 @@
       <c r="E267" s="78"/>
       <c r="F267" s="78"/>
       <c r="G267" s="78"/>
-      <c r="H267" s="36"/>
-      <c r="I267" s="36"/>
-      <c r="J267" s="36"/>
+      <c r="H267" s="39"/>
+      <c r="I267" s="39"/>
+      <c r="J267" s="39"/>
     </row>
     <row r="268" spans="1:10" s="1" customFormat="1">
-      <c r="A268" s="23" t="s">
+      <c r="A268" s="80" t="s">
         <v>255</v>
       </c>
-      <c r="B268" s="24">
-        <v>46235</v>
-      </c>
-      <c r="C268" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D268" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E268" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F268" s="26"/>
-      <c r="G268" s="26"/>
-      <c r="H268" s="41"/>
-      <c r="I268" s="41"/>
-      <c r="J268" s="41"/>
+      <c r="B268" s="80"/>
+      <c r="C268" s="80"/>
+      <c r="D268" s="80"/>
+      <c r="E268" s="80"/>
+      <c r="F268" s="80"/>
+      <c r="G268" s="80"/>
+      <c r="H268" s="36"/>
+      <c r="I268" s="36"/>
+      <c r="J268" s="36"/>
     </row>
     <row r="269" spans="1:10" s="1" customFormat="1">
-      <c r="A269" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B269" s="13">
-        <v>46237</v>
-      </c>
-      <c r="C269" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E269" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F269" s="6"/>
+      <c r="A269" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="B269" s="24">
+        <v>46235</v>
+      </c>
+      <c r="C269" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D269" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E269" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F269" s="26"/>
+      <c r="G269" s="26"/>
+      <c r="H269" s="41"/>
+      <c r="I269" s="41"/>
+      <c r="J269" s="41"/>
     </row>
     <row r="270" spans="1:10" s="1" customFormat="1">
       <c r="A270" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B270" s="13">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="C270" s="6" t="s">
         <v>14</v>
@@ -54107,20 +54142,20 @@
       <c r="D270" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E270" s="7" t="s">
-        <v>26</v>
+      <c r="E270" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F270" s="6"/>
     </row>
     <row r="271" spans="1:10" s="1" customFormat="1">
-      <c r="A271" s="9" t="s">
-        <v>24</v>
+      <c r="A271" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B271" s="13">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>15</v>
@@ -54131,29 +54166,29 @@
       <c r="F271" s="6"/>
     </row>
     <row r="272" spans="1:10" s="1" customFormat="1">
-      <c r="A272" s="1" t="s">
-        <v>13</v>
+      <c r="A272" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="B272" s="13">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E272" s="1" t="s">
-        <v>16</v>
+      <c r="E272" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F272" s="6"/>
     </row>
     <row r="273" spans="1:10" s="1" customFormat="1">
       <c r="A273" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B273" s="13">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="C273" s="6" t="s">
         <v>14</v>
@@ -54161,14 +54196,14 @@
       <c r="D273" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E273" s="7" t="s">
-        <v>26</v>
+      <c r="E273" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F273" s="6"/>
     </row>
     <row r="274" spans="1:10" s="1" customFormat="1">
-      <c r="A274" s="9" t="s">
-        <v>28</v>
+      <c r="A274" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B274" s="13">
         <v>46246</v>
@@ -54185,14 +54220,14 @@
       <c r="F274" s="6"/>
     </row>
     <row r="275" spans="1:10" s="1" customFormat="1">
-      <c r="A275" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B275" s="11">
-        <v>46247</v>
+      <c r="A275" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B275" s="13">
+        <v>46246</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>15</v>
@@ -54203,65 +54238,65 @@
       <c r="F275" s="6"/>
     </row>
     <row r="276" spans="1:10" s="1" customFormat="1">
-      <c r="A276" s="77" t="s">
-        <v>256</v>
-      </c>
-      <c r="B276" s="77"/>
-      <c r="C276" s="77"/>
-      <c r="D276" s="77"/>
-      <c r="E276" s="77"/>
-      <c r="F276" s="77"/>
-      <c r="G276" s="77"/>
-      <c r="H276" s="38"/>
-      <c r="I276" s="38"/>
-      <c r="J276" s="38"/>
+      <c r="A276" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B276" s="11">
+        <v>46247</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E276" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F276" s="6"/>
     </row>
     <row r="277" spans="1:10" s="1" customFormat="1">
-      <c r="A277" s="23" t="s">
+      <c r="A277" s="79" t="s">
         <v>257</v>
       </c>
-      <c r="B277" s="24">
-        <v>46249</v>
-      </c>
-      <c r="C277" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D277" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E277" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F277" s="26"/>
-      <c r="G277" s="26"/>
-      <c r="H277" s="41"/>
-      <c r="I277" s="41"/>
-      <c r="J277" s="41"/>
+      <c r="B277" s="79"/>
+      <c r="C277" s="79"/>
+      <c r="D277" s="79"/>
+      <c r="E277" s="79"/>
+      <c r="F277" s="79"/>
+      <c r="G277" s="79"/>
+      <c r="H277" s="38"/>
+      <c r="I277" s="38"/>
+      <c r="J277" s="38"/>
     </row>
     <row r="278" spans="1:10" s="1" customFormat="1">
-      <c r="A278" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B278" s="13">
-        <v>46251</v>
-      </c>
-      <c r="C278" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E278" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F278" s="6"/>
+      <c r="A278" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="B278" s="24">
+        <v>46249</v>
+      </c>
+      <c r="C278" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D278" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E278" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F278" s="26"/>
+      <c r="G278" s="26"/>
+      <c r="H278" s="41"/>
+      <c r="I278" s="41"/>
+      <c r="J278" s="41"/>
     </row>
     <row r="279" spans="1:10" s="1" customFormat="1">
       <c r="A279" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B279" s="13">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="C279" s="6" t="s">
         <v>14</v>
@@ -54269,20 +54304,20 @@
       <c r="D279" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E279" s="7" t="s">
-        <v>26</v>
+      <c r="E279" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F279" s="6"/>
     </row>
     <row r="280" spans="1:10" s="1" customFormat="1">
-      <c r="A280" s="9" t="s">
-        <v>24</v>
+      <c r="A280" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B280" s="13">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>15</v>
@@ -54293,62 +54328,62 @@
       <c r="F280" s="6"/>
     </row>
     <row r="281" spans="1:10" s="1" customFormat="1">
-      <c r="A281" s="1" t="s">
-        <v>13</v>
+      <c r="A281" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="B281" s="13">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E281" s="1" t="s">
-        <v>16</v>
+      <c r="E281" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F281" s="6"/>
     </row>
     <row r="282" spans="1:10" s="1" customFormat="1">
       <c r="A282" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B282" s="13">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F282" s="6"/>
     </row>
     <row r="283" spans="1:10" s="1" customFormat="1">
       <c r="A283" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B283" s="13">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E283" s="7" t="s">
-        <v>26</v>
+      <c r="E283" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F283" s="6"/>
     </row>
     <row r="284" spans="1:10" s="1" customFormat="1">
-      <c r="A284" s="9" t="s">
-        <v>28</v>
+      <c r="A284" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B284" s="13">
         <v>46260</v>
@@ -54365,26 +54400,22 @@
       <c r="F284" s="6"/>
     </row>
     <row r="285" spans="1:10" s="1" customFormat="1">
-      <c r="A285" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="B285" s="24">
-        <v>46261</v>
-      </c>
-      <c r="C285" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D285" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E285" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="F285" s="25"/>
-      <c r="G285" s="23"/>
-      <c r="H285" s="37"/>
-      <c r="I285" s="37"/>
-      <c r="J285" s="37"/>
+      <c r="A285" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B285" s="13">
+        <v>46260</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E285" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F285" s="6"/>
     </row>
     <row r="286" spans="1:10" s="1" customFormat="1">
       <c r="A286" s="23" t="s">
@@ -54400,7 +54431,7 @@
         <v>19</v>
       </c>
       <c r="E286" s="23" t="s">
-        <v>260</v>
+        <v>172</v>
       </c>
       <c r="F286" s="25"/>
       <c r="G286" s="23"/>
@@ -54409,126 +54440,130 @@
       <c r="J286" s="37"/>
     </row>
     <row r="287" spans="1:10" s="1" customFormat="1">
-      <c r="A287" s="10" t="s">
+      <c r="A287" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="B287" s="24">
+        <v>46261</v>
+      </c>
+      <c r="C287" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D287" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E287" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="F287" s="25"/>
+      <c r="G287" s="23"/>
+      <c r="H287" s="37"/>
+      <c r="I287" s="37"/>
+      <c r="J287" s="37"/>
+    </row>
+    <row r="288" spans="1:10" s="1" customFormat="1">
+      <c r="A288" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B287" s="11">
+      <c r="B288" s="11">
         <v>46261</v>
       </c>
-      <c r="C287" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D287" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E287" s="7" t="s">
+      <c r="C288" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E288" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F287" s="6"/>
+      <c r="F288" s="6"/>
     </row>
-    <row r="288" spans="1:10" s="7" customFormat="1">
-      <c r="A288" s="78" t="s">
-        <v>261</v>
-      </c>
-      <c r="B288" s="78"/>
-      <c r="C288" s="78"/>
-      <c r="D288" s="78"/>
-      <c r="E288" s="78"/>
-      <c r="F288" s="78"/>
-      <c r="G288" s="78"/>
-      <c r="H288" s="36"/>
-      <c r="I288" s="36"/>
-      <c r="J288" s="36"/>
+    <row r="289" spans="1:10" s="7" customFormat="1">
+      <c r="A289" s="80" t="s">
+        <v>262</v>
+      </c>
+      <c r="B289" s="80"/>
+      <c r="C289" s="80"/>
+      <c r="D289" s="80"/>
+      <c r="E289" s="80"/>
+      <c r="F289" s="80"/>
+      <c r="G289" s="80"/>
+      <c r="H289" s="36"/>
+      <c r="I289" s="36"/>
+      <c r="J289" s="36"/>
     </row>
-    <row r="289" spans="1:10" s="5" customFormat="1" ht="20.25">
-      <c r="A289" s="1" t="s">
+    <row r="290" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A290" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B289" s="13">
+      <c r="B290" s="13">
         <v>46265</v>
       </c>
-      <c r="C289" s="6" t="s">
+      <c r="C290" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D289" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E289" s="1" t="s">
+      <c r="D290" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E290" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F289" s="6"/>
-      <c r="G289" s="1"/>
-      <c r="H289" s="40"/>
-      <c r="I289" s="40"/>
-      <c r="J289" s="40"/>
+      <c r="F290" s="6"/>
+      <c r="G290" s="1"/>
+      <c r="H290" s="40"/>
+      <c r="I290" s="40"/>
+      <c r="J290" s="40"/>
     </row>
-    <row r="290" spans="1:10" s="1" customFormat="1">
-      <c r="A290" s="16"/>
-      <c r="B290" s="12"/>
-      <c r="C290" s="12"/>
-      <c r="D290" s="7"/>
-      <c r="E290" s="7"/>
-      <c r="F290" s="65"/>
-      <c r="G290" s="7"/>
-      <c r="H290" s="42"/>
-      <c r="I290" s="42"/>
-      <c r="J290" s="42"/>
+    <row r="291" spans="1:10" s="1" customFormat="1">
+      <c r="A291" s="16"/>
+      <c r="B291" s="12"/>
+      <c r="C291" s="12"/>
+      <c r="D291" s="7"/>
+      <c r="E291" s="7"/>
+      <c r="F291" s="65"/>
+      <c r="G291" s="7"/>
+      <c r="H291" s="42"/>
+      <c r="I291" s="42"/>
+      <c r="J291" s="42"/>
     </row>
-    <row r="291" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A291" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="B291" s="79"/>
-      <c r="C291" s="79"/>
-      <c r="D291" s="79"/>
-      <c r="E291" s="79"/>
-      <c r="F291" s="79"/>
-      <c r="G291" s="79"/>
-      <c r="H291" s="34"/>
-      <c r="I291" s="34"/>
-      <c r="J291" s="34"/>
+    <row r="292" spans="1:10" s="1" customFormat="1" ht="19.5">
+      <c r="A292" s="81" t="s">
+        <v>263</v>
+      </c>
+      <c r="B292" s="81"/>
+      <c r="C292" s="81"/>
+      <c r="D292" s="81"/>
+      <c r="E292" s="81"/>
+      <c r="F292" s="81"/>
+      <c r="G292" s="81"/>
+      <c r="H292" s="34"/>
+      <c r="I292" s="34"/>
+      <c r="J292" s="34"/>
     </row>
-    <row r="292" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A292" s="75" t="s">
+    <row r="293" spans="1:10" s="5" customFormat="1" ht="19.5">
+      <c r="A293" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="B292" s="75"/>
-      <c r="C292" s="75"/>
-      <c r="D292" s="75"/>
-      <c r="E292" s="75"/>
-      <c r="F292" s="75"/>
-      <c r="G292" s="75"/>
-      <c r="H292" s="33"/>
-      <c r="I292" s="33"/>
-      <c r="J292" s="33"/>
-    </row>
-    <row r="293" spans="1:10" s="1" customFormat="1">
-      <c r="A293" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B293" s="13">
-        <v>46267</v>
-      </c>
-      <c r="C293" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E293" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F293" s="6"/>
+      <c r="B293" s="77"/>
+      <c r="C293" s="77"/>
+      <c r="D293" s="77"/>
+      <c r="E293" s="77"/>
+      <c r="F293" s="77"/>
+      <c r="G293" s="77"/>
+      <c r="H293" s="33"/>
+      <c r="I293" s="33"/>
+      <c r="J293" s="33"/>
     </row>
     <row r="294" spans="1:10" s="1" customFormat="1">
-      <c r="A294" s="9" t="s">
-        <v>24</v>
+      <c r="A294" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B294" s="13">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>15</v>
@@ -54539,86 +54574,86 @@
       <c r="F294" s="6"/>
     </row>
     <row r="295" spans="1:10" s="1" customFormat="1">
-      <c r="A295" s="78" t="s">
-        <v>263</v>
-      </c>
-      <c r="B295" s="78"/>
-      <c r="C295" s="78"/>
-      <c r="D295" s="78"/>
-      <c r="E295" s="78"/>
-      <c r="F295" s="78"/>
-      <c r="G295" s="78"/>
-      <c r="H295" s="36"/>
-      <c r="I295" s="36"/>
-      <c r="J295" s="36"/>
+      <c r="A295" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B295" s="13">
+        <v>46268</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E295" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F295" s="6"/>
     </row>
     <row r="296" spans="1:10" s="1" customFormat="1">
-      <c r="A296" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B296" s="13">
-        <v>46272</v>
-      </c>
-      <c r="C296" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E296" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F296" s="6"/>
+      <c r="A296" s="80" t="s">
+        <v>264</v>
+      </c>
+      <c r="B296" s="80"/>
+      <c r="C296" s="80"/>
+      <c r="D296" s="80"/>
+      <c r="E296" s="80"/>
+      <c r="F296" s="80"/>
+      <c r="G296" s="80"/>
+      <c r="H296" s="36"/>
+      <c r="I296" s="36"/>
+      <c r="J296" s="36"/>
     </row>
     <row r="297" spans="1:10" s="1" customFormat="1">
-      <c r="A297" s="76" t="s">
-        <v>264</v>
-      </c>
-      <c r="B297" s="76"/>
-      <c r="C297" s="76"/>
-      <c r="D297" s="76"/>
-      <c r="E297" s="76"/>
-      <c r="F297" s="76"/>
-      <c r="G297" s="76"/>
-      <c r="H297" s="39"/>
-      <c r="I297" s="39"/>
-      <c r="J297" s="39"/>
+      <c r="A297" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B297" s="13">
+        <v>46272</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F297" s="6"/>
     </row>
     <row r="298" spans="1:10" s="1" customFormat="1">
-      <c r="A298" s="76" t="s">
+      <c r="A298" s="78" t="s">
         <v>265</v>
       </c>
-      <c r="B298" s="76"/>
-      <c r="C298" s="76"/>
-      <c r="D298" s="76"/>
-      <c r="E298" s="76"/>
-      <c r="F298" s="76"/>
-      <c r="G298" s="76"/>
+      <c r="B298" s="78"/>
+      <c r="C298" s="78"/>
+      <c r="D298" s="78"/>
+      <c r="E298" s="78"/>
+      <c r="F298" s="78"/>
+      <c r="G298" s="78"/>
       <c r="H298" s="39"/>
       <c r="I298" s="39"/>
       <c r="J298" s="39"/>
     </row>
     <row r="299" spans="1:10" s="1" customFormat="1">
-      <c r="A299" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B299" s="13">
-        <v>46274</v>
-      </c>
-      <c r="C299" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E299" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F299" s="6"/>
+      <c r="A299" s="78" t="s">
+        <v>266</v>
+      </c>
+      <c r="B299" s="78"/>
+      <c r="C299" s="78"/>
+      <c r="D299" s="78"/>
+      <c r="E299" s="78"/>
+      <c r="F299" s="78"/>
+      <c r="G299" s="78"/>
+      <c r="H299" s="39"/>
+      <c r="I299" s="39"/>
+      <c r="J299" s="39"/>
     </row>
     <row r="300" spans="1:10" s="1" customFormat="1">
-      <c r="A300" s="9" t="s">
-        <v>28</v>
+      <c r="A300" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B300" s="13">
         <v>46274</v>
@@ -54635,14 +54670,14 @@
       <c r="F300" s="6"/>
     </row>
     <row r="301" spans="1:10" s="1" customFormat="1">
-      <c r="A301" s="10" t="s">
-        <v>24</v>
+      <c r="A301" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B301" s="13">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>15</v>
@@ -54653,86 +54688,86 @@
       <c r="F301" s="6"/>
     </row>
     <row r="302" spans="1:10" s="1" customFormat="1">
-      <c r="A302" s="77" t="s">
-        <v>266</v>
-      </c>
-      <c r="B302" s="77"/>
-      <c r="C302" s="77"/>
-      <c r="D302" s="77"/>
-      <c r="E302" s="77"/>
-      <c r="F302" s="77"/>
-      <c r="G302" s="77"/>
-      <c r="H302" s="38"/>
-      <c r="I302" s="38"/>
-      <c r="J302" s="38"/>
+      <c r="A302" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B302" s="13">
+        <v>46275</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E302" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F302" s="6"/>
     </row>
     <row r="303" spans="1:10" s="1" customFormat="1">
-      <c r="A303" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B303" s="13">
-        <v>46279</v>
-      </c>
-      <c r="C303" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E303" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F303" s="6"/>
+      <c r="A303" s="79" t="s">
+        <v>267</v>
+      </c>
+      <c r="B303" s="79"/>
+      <c r="C303" s="79"/>
+      <c r="D303" s="79"/>
+      <c r="E303" s="79"/>
+      <c r="F303" s="79"/>
+      <c r="G303" s="79"/>
+      <c r="H303" s="38"/>
+      <c r="I303" s="38"/>
+      <c r="J303" s="38"/>
     </row>
     <row r="304" spans="1:10" s="1" customFormat="1">
-      <c r="A304" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="B304" s="24">
-        <v>46280</v>
-      </c>
-      <c r="C304" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D304" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E304" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F304" s="25"/>
-      <c r="G304" s="23"/>
-      <c r="H304" s="37"/>
-      <c r="I304" s="37"/>
-      <c r="J304" s="37"/>
+      <c r="A304" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B304" s="13">
+        <v>46279</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F304" s="6"/>
     </row>
     <row r="305" spans="1:10" s="1" customFormat="1">
-      <c r="A305" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B305" s="13">
-        <v>46281</v>
-      </c>
-      <c r="C305" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E305" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F305" s="6"/>
+      <c r="A305" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="B305" s="24">
+        <v>46280</v>
+      </c>
+      <c r="C305" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D305" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E305" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F305" s="25"/>
+      <c r="G305" s="23"/>
+      <c r="H305" s="37"/>
+      <c r="I305" s="37"/>
+      <c r="J305" s="37"/>
     </row>
     <row r="306" spans="1:10" s="1" customFormat="1">
-      <c r="A306" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B306" s="11">
-        <v>46282</v>
+      <c r="A306" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B306" s="13">
+        <v>46281</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>15</v>
@@ -54743,43 +54778,43 @@
       <c r="F306" s="6"/>
     </row>
     <row r="307" spans="1:10" s="1" customFormat="1">
-      <c r="A307" s="77" t="s">
-        <v>268</v>
-      </c>
-      <c r="B307" s="77"/>
-      <c r="C307" s="77"/>
-      <c r="D307" s="77"/>
-      <c r="E307" s="77"/>
-      <c r="F307" s="77"/>
-      <c r="G307" s="77"/>
-      <c r="H307" s="38"/>
-      <c r="I307" s="38"/>
-      <c r="J307" s="38"/>
+      <c r="A307" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B307" s="11">
+        <v>46282</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E307" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F307" s="6"/>
     </row>
     <row r="308" spans="1:10" s="1" customFormat="1">
-      <c r="A308" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B308" s="13">
-        <v>46286</v>
-      </c>
-      <c r="C308" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E308" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F308" s="6"/>
+      <c r="A308" s="79" t="s">
+        <v>269</v>
+      </c>
+      <c r="B308" s="79"/>
+      <c r="C308" s="79"/>
+      <c r="D308" s="79"/>
+      <c r="E308" s="79"/>
+      <c r="F308" s="79"/>
+      <c r="G308" s="79"/>
+      <c r="H308" s="38"/>
+      <c r="I308" s="38"/>
+      <c r="J308" s="38"/>
     </row>
     <row r="309" spans="1:10" s="1" customFormat="1">
       <c r="A309" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B309" s="13">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="C309" s="6" t="s">
         <v>14</v>
@@ -54787,14 +54822,14 @@
       <c r="D309" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E309" s="7" t="s">
-        <v>26</v>
+      <c r="E309" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F309" s="6"/>
     </row>
     <row r="310" spans="1:10" s="1" customFormat="1">
-      <c r="A310" s="9" t="s">
-        <v>28</v>
+      <c r="A310" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B310" s="13">
         <v>46288</v>
@@ -54811,14 +54846,14 @@
       <c r="F310" s="6"/>
     </row>
     <row r="311" spans="1:10" s="1" customFormat="1">
-      <c r="A311" s="10" t="s">
-        <v>24</v>
+      <c r="A311" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B311" s="13">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>15</v>
@@ -54829,78 +54864,74 @@
       <c r="F311" s="6"/>
     </row>
     <row r="312" spans="1:10" s="1" customFormat="1">
-      <c r="A312" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="B312" s="77"/>
-      <c r="C312" s="77"/>
-      <c r="D312" s="77"/>
-      <c r="E312" s="77"/>
-      <c r="F312" s="77"/>
-      <c r="G312" s="77"/>
-      <c r="H312" s="38"/>
-      <c r="I312" s="38"/>
-      <c r="J312" s="38"/>
+      <c r="A312" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B312" s="13">
+        <v>46289</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E312" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F312" s="6"/>
     </row>
     <row r="313" spans="1:10" s="1" customFormat="1">
-      <c r="A313" s="23" t="s">
+      <c r="A313" s="79" t="s">
         <v>270</v>
       </c>
-      <c r="B313" s="24">
+      <c r="B313" s="79"/>
+      <c r="C313" s="79"/>
+      <c r="D313" s="79"/>
+      <c r="E313" s="79"/>
+      <c r="F313" s="79"/>
+      <c r="G313" s="79"/>
+      <c r="H313" s="38"/>
+      <c r="I313" s="38"/>
+      <c r="J313" s="38"/>
+    </row>
+    <row r="314" spans="1:10" s="1" customFormat="1">
+      <c r="A314" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="B314" s="24">
         <v>46291</v>
       </c>
-      <c r="C313" s="25" t="s">
+      <c r="C314" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D313" s="23" t="s">
+      <c r="D314" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="E313" s="23" t="s">
+      <c r="E314" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="F313" s="26"/>
-      <c r="G313" s="26"/>
-      <c r="H313" s="41"/>
-      <c r="I313" s="41"/>
-      <c r="J313" s="41"/>
-    </row>
-    <row r="314" spans="1:10" s="7" customFormat="1">
-      <c r="A314" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B314" s="13">
-        <v>46293</v>
-      </c>
-      <c r="C314" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D314" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E314" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F314" s="6"/>
-      <c r="G314" s="1"/>
-      <c r="H314" s="40"/>
-      <c r="I314" s="40"/>
-      <c r="J314" s="40"/>
+      <c r="F314" s="26"/>
+      <c r="G314" s="26"/>
+      <c r="H314" s="41"/>
+      <c r="I314" s="41"/>
+      <c r="J314" s="41"/>
     </row>
     <row r="315" spans="1:10" s="7" customFormat="1">
       <c r="A315" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B315" s="13">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F315" s="6"/>
       <c r="G315" s="1"/>
@@ -54908,21 +54939,21 @@
       <c r="I315" s="40"/>
       <c r="J315" s="40"/>
     </row>
-    <row r="316" spans="1:10" s="5" customFormat="1" ht="20.25">
+    <row r="316" spans="1:10" s="7" customFormat="1">
       <c r="A316" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B316" s="13">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E316" s="7" t="s">
-        <v>26</v>
+      <c r="E316" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F316" s="6"/>
       <c r="G316" s="1"/>
@@ -54930,159 +54961,163 @@
       <c r="I316" s="40"/>
       <c r="J316" s="40"/>
     </row>
-    <row r="317" spans="1:10" s="1" customFormat="1">
-      <c r="A317" s="16"/>
-      <c r="B317" s="12"/>
-      <c r="C317" s="12"/>
-      <c r="D317" s="7"/>
-      <c r="E317" s="7"/>
-      <c r="F317" s="65"/>
-      <c r="G317" s="7"/>
-      <c r="H317" s="42"/>
-      <c r="I317" s="42"/>
-      <c r="J317" s="42"/>
+    <row r="317" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A317" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B317" s="13">
+        <v>46295</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E317" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F317" s="6"/>
+      <c r="G317" s="1"/>
+      <c r="H317" s="40"/>
+      <c r="I317" s="40"/>
+      <c r="J317" s="40"/>
     </row>
-    <row r="318" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A318" s="79" t="s">
-        <v>271</v>
-      </c>
-      <c r="B318" s="79"/>
-      <c r="C318" s="79"/>
-      <c r="D318" s="79"/>
-      <c r="E318" s="79"/>
-      <c r="F318" s="79"/>
-      <c r="G318" s="79"/>
-      <c r="H318" s="34"/>
-      <c r="I318" s="34"/>
-      <c r="J318" s="34"/>
+    <row r="318" spans="1:10" s="1" customFormat="1">
+      <c r="A318" s="16"/>
+      <c r="B318" s="12"/>
+      <c r="C318" s="12"/>
+      <c r="D318" s="7"/>
+      <c r="E318" s="7"/>
+      <c r="F318" s="65"/>
+      <c r="G318" s="7"/>
+      <c r="H318" s="42"/>
+      <c r="I318" s="42"/>
+      <c r="J318" s="42"/>
     </row>
-    <row r="319" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A319" s="75" t="s">
+    <row r="319" spans="1:10" s="1" customFormat="1" ht="19.5">
+      <c r="A319" s="81" t="s">
+        <v>272</v>
+      </c>
+      <c r="B319" s="81"/>
+      <c r="C319" s="81"/>
+      <c r="D319" s="81"/>
+      <c r="E319" s="81"/>
+      <c r="F319" s="81"/>
+      <c r="G319" s="81"/>
+      <c r="H319" s="34"/>
+      <c r="I319" s="34"/>
+      <c r="J319" s="34"/>
+    </row>
+    <row r="320" spans="1:10" s="5" customFormat="1" ht="19.5">
+      <c r="A320" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="B319" s="75"/>
-      <c r="C319" s="75"/>
-      <c r="D319" s="75"/>
-      <c r="E319" s="75"/>
-      <c r="F319" s="75"/>
-      <c r="G319" s="75"/>
-      <c r="H319" s="33"/>
-      <c r="I319" s="33"/>
-      <c r="J319" s="33"/>
-    </row>
-    <row r="320" spans="1:10" s="1" customFormat="1">
-      <c r="A320" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B320" s="11">
-        <v>46296</v>
-      </c>
-      <c r="C320" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E320" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F320" s="6"/>
+      <c r="B320" s="77"/>
+      <c r="C320" s="77"/>
+      <c r="D320" s="77"/>
+      <c r="E320" s="77"/>
+      <c r="F320" s="77"/>
+      <c r="G320" s="77"/>
+      <c r="H320" s="33"/>
+      <c r="I320" s="33"/>
+      <c r="J320" s="33"/>
     </row>
     <row r="321" spans="1:10" s="1" customFormat="1">
-      <c r="A321" s="77" t="s">
-        <v>272</v>
-      </c>
-      <c r="B321" s="77"/>
-      <c r="C321" s="77"/>
-      <c r="D321" s="77"/>
-      <c r="E321" s="77"/>
-      <c r="F321" s="77"/>
-      <c r="G321" s="77"/>
-      <c r="H321" s="38"/>
-      <c r="I321" s="38"/>
-      <c r="J321" s="38"/>
+      <c r="A321" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B321" s="11">
+        <v>46296</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E321" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F321" s="6"/>
     </row>
     <row r="322" spans="1:10" s="1" customFormat="1">
-      <c r="A322" s="77" t="s">
+      <c r="A322" s="79" t="s">
         <v>273</v>
       </c>
-      <c r="B322" s="77"/>
-      <c r="C322" s="77"/>
-      <c r="D322" s="77"/>
-      <c r="E322" s="77"/>
-      <c r="F322" s="77"/>
-      <c r="G322" s="77"/>
+      <c r="B322" s="79"/>
+      <c r="C322" s="79"/>
+      <c r="D322" s="79"/>
+      <c r="E322" s="79"/>
+      <c r="F322" s="79"/>
+      <c r="G322" s="79"/>
       <c r="H322" s="38"/>
       <c r="I322" s="38"/>
       <c r="J322" s="38"/>
     </row>
     <row r="323" spans="1:10" s="1" customFormat="1">
-      <c r="A323" s="77" t="s">
+      <c r="A323" s="79" t="s">
         <v>274</v>
       </c>
-      <c r="B323" s="77"/>
-      <c r="C323" s="77"/>
-      <c r="D323" s="77"/>
-      <c r="E323" s="77"/>
-      <c r="F323" s="77"/>
-      <c r="G323" s="77"/>
+      <c r="B323" s="79"/>
+      <c r="C323" s="79"/>
+      <c r="D323" s="79"/>
+      <c r="E323" s="79"/>
+      <c r="F323" s="79"/>
+      <c r="G323" s="79"/>
       <c r="H323" s="38"/>
       <c r="I323" s="38"/>
       <c r="J323" s="38"/>
     </row>
     <row r="324" spans="1:10" s="1" customFormat="1">
-      <c r="A324" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B324" s="13">
-        <v>46300</v>
-      </c>
-      <c r="C324" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D324" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E324" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F324" s="6"/>
+      <c r="A324" s="79" t="s">
+        <v>275</v>
+      </c>
+      <c r="B324" s="79"/>
+      <c r="C324" s="79"/>
+      <c r="D324" s="79"/>
+      <c r="E324" s="79"/>
+      <c r="F324" s="79"/>
+      <c r="G324" s="79"/>
+      <c r="H324" s="38"/>
+      <c r="I324" s="38"/>
+      <c r="J324" s="38"/>
     </row>
     <row r="325" spans="1:10" s="1" customFormat="1">
-      <c r="A325" s="76" t="s">
-        <v>275</v>
-      </c>
-      <c r="B325" s="76"/>
-      <c r="C325" s="76"/>
-      <c r="D325" s="76"/>
-      <c r="E325" s="76"/>
-      <c r="F325" s="76"/>
-      <c r="G325" s="76"/>
-      <c r="H325" s="39"/>
-      <c r="I325" s="39"/>
-      <c r="J325" s="39"/>
+      <c r="A325" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B325" s="13">
+        <v>46300</v>
+      </c>
+      <c r="C325" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E325" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F325" s="6"/>
     </row>
     <row r="326" spans="1:10" s="1" customFormat="1">
-      <c r="A326" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B326" s="13">
-        <v>46302</v>
-      </c>
-      <c r="C326" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D326" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E326" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F326" s="6"/>
+      <c r="A326" s="78" t="s">
+        <v>276</v>
+      </c>
+      <c r="B326" s="78"/>
+      <c r="C326" s="78"/>
+      <c r="D326" s="78"/>
+      <c r="E326" s="78"/>
+      <c r="F326" s="78"/>
+      <c r="G326" s="78"/>
+      <c r="H326" s="39"/>
+      <c r="I326" s="39"/>
+      <c r="J326" s="39"/>
     </row>
     <row r="327" spans="1:10" s="1" customFormat="1">
-      <c r="A327" s="9" t="s">
-        <v>28</v>
+      <c r="A327" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B327" s="13">
         <v>46302</v>
@@ -55099,14 +55134,14 @@
       <c r="F327" s="6"/>
     </row>
     <row r="328" spans="1:10" s="1" customFormat="1">
-      <c r="A328" s="10" t="s">
-        <v>24</v>
+      <c r="A328" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B328" s="13">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>15</v>
@@ -55117,100 +55152,100 @@
       <c r="F328" s="6"/>
     </row>
     <row r="329" spans="1:10" s="1" customFormat="1">
-      <c r="A329" s="78" t="s">
-        <v>276</v>
-      </c>
-      <c r="B329" s="78"/>
-      <c r="C329" s="78"/>
-      <c r="D329" s="78"/>
-      <c r="E329" s="78"/>
-      <c r="F329" s="78"/>
-      <c r="G329" s="78"/>
-      <c r="H329" s="36"/>
-      <c r="I329" s="36"/>
-      <c r="J329" s="36"/>
+      <c r="A329" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B329" s="13">
+        <v>46303</v>
+      </c>
+      <c r="C329" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E329" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F329" s="6"/>
     </row>
     <row r="330" spans="1:10" s="1" customFormat="1">
-      <c r="A330" s="23" t="s">
+      <c r="A330" s="80" t="s">
         <v>277</v>
       </c>
-      <c r="B330" s="24">
-        <v>46305</v>
-      </c>
-      <c r="C330" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D330" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E330" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F330" s="26"/>
-      <c r="G330" s="26"/>
-      <c r="H330" s="41"/>
-      <c r="I330" s="41"/>
-      <c r="J330" s="41"/>
+      <c r="B330" s="80"/>
+      <c r="C330" s="80"/>
+      <c r="D330" s="80"/>
+      <c r="E330" s="80"/>
+      <c r="F330" s="80"/>
+      <c r="G330" s="80"/>
+      <c r="H330" s="36"/>
+      <c r="I330" s="36"/>
+      <c r="J330" s="36"/>
     </row>
     <row r="331" spans="1:10" s="1" customFormat="1">
-      <c r="A331" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B331" s="13">
-        <v>46307</v>
-      </c>
-      <c r="C331" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E331" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F331" s="6"/>
+      <c r="A331" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="B331" s="24">
+        <v>46305</v>
+      </c>
+      <c r="C331" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D331" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E331" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F331" s="26"/>
+      <c r="G331" s="26"/>
+      <c r="H331" s="41"/>
+      <c r="I331" s="41"/>
+      <c r="J331" s="41"/>
     </row>
     <row r="332" spans="1:10" s="1" customFormat="1">
-      <c r="A332" s="76" t="s">
-        <v>278</v>
-      </c>
-      <c r="B332" s="76"/>
-      <c r="C332" s="76"/>
-      <c r="D332" s="76"/>
-      <c r="E332" s="76"/>
-      <c r="F332" s="76"/>
-      <c r="G332" s="76"/>
-      <c r="H332" s="39"/>
-      <c r="I332" s="39"/>
-      <c r="J332" s="39"/>
+      <c r="A332" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B332" s="13">
+        <v>46307</v>
+      </c>
+      <c r="C332" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E332" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F332" s="6"/>
     </row>
     <row r="333" spans="1:10" s="1" customFormat="1">
-      <c r="A333" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B333" s="13">
-        <v>46309</v>
-      </c>
-      <c r="C333" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E333" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F333" s="6"/>
+      <c r="A333" s="78" t="s">
+        <v>279</v>
+      </c>
+      <c r="B333" s="78"/>
+      <c r="C333" s="78"/>
+      <c r="D333" s="78"/>
+      <c r="E333" s="78"/>
+      <c r="F333" s="78"/>
+      <c r="G333" s="78"/>
+      <c r="H333" s="39"/>
+      <c r="I333" s="39"/>
+      <c r="J333" s="39"/>
     </row>
     <row r="334" spans="1:10" s="1" customFormat="1">
-      <c r="A334" s="9" t="s">
-        <v>24</v>
+      <c r="A334" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B334" s="13">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>15</v>
@@ -55221,80 +55256,80 @@
       <c r="F334" s="6"/>
     </row>
     <row r="335" spans="1:10" s="1" customFormat="1">
-      <c r="A335" s="76" t="s">
-        <v>279</v>
-      </c>
-      <c r="B335" s="76"/>
-      <c r="C335" s="76"/>
-      <c r="D335" s="76"/>
-      <c r="E335" s="76"/>
-      <c r="F335" s="76"/>
-      <c r="G335" s="76"/>
-      <c r="H335" s="39"/>
-      <c r="I335" s="39"/>
-      <c r="J335" s="39"/>
+      <c r="A335" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B335" s="13">
+        <v>46310</v>
+      </c>
+      <c r="C335" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E335" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F335" s="6"/>
     </row>
     <row r="336" spans="1:10" s="1" customFormat="1">
-      <c r="A336" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B336" s="13">
-        <v>46314</v>
-      </c>
-      <c r="C336" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D336" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E336" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F336" s="6"/>
+      <c r="A336" s="78" t="s">
+        <v>280</v>
+      </c>
+      <c r="B336" s="78"/>
+      <c r="C336" s="78"/>
+      <c r="D336" s="78"/>
+      <c r="E336" s="78"/>
+      <c r="F336" s="78"/>
+      <c r="G336" s="78"/>
+      <c r="H336" s="39"/>
+      <c r="I336" s="39"/>
+      <c r="J336" s="39"/>
     </row>
     <row r="337" spans="1:10" s="1" customFormat="1">
-      <c r="A337" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="B337" s="24">
-        <v>46315</v>
-      </c>
-      <c r="C337" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D337" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E337" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F337" s="25"/>
-      <c r="G337" s="23"/>
-      <c r="H337" s="37"/>
-      <c r="I337" s="37"/>
-      <c r="J337" s="37"/>
+      <c r="A337" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B337" s="13">
+        <v>46314</v>
+      </c>
+      <c r="C337" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E337" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F337" s="6"/>
     </row>
     <row r="338" spans="1:10" s="1" customFormat="1">
-      <c r="A338" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B338" s="13">
-        <v>46316</v>
-      </c>
-      <c r="C338" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E338" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F338" s="6"/>
+      <c r="A338" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="B338" s="24">
+        <v>46315</v>
+      </c>
+      <c r="C338" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D338" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E338" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F338" s="25"/>
+      <c r="G338" s="23"/>
+      <c r="H338" s="37"/>
+      <c r="I338" s="37"/>
+      <c r="J338" s="37"/>
     </row>
     <row r="339" spans="1:10" s="1" customFormat="1">
-      <c r="A339" s="9" t="s">
-        <v>28</v>
+      <c r="A339" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B339" s="13">
         <v>46316</v>
@@ -55311,14 +55346,14 @@
       <c r="F339" s="6"/>
     </row>
     <row r="340" spans="1:10" s="1" customFormat="1">
-      <c r="A340" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B340" s="11">
-        <v>46317</v>
+      <c r="A340" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B340" s="13">
+        <v>46316</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>15</v>
@@ -55329,56 +55364,52 @@
       <c r="F340" s="6"/>
     </row>
     <row r="341" spans="1:10" s="1" customFormat="1">
-      <c r="A341" s="76" t="s">
-        <v>281</v>
-      </c>
-      <c r="B341" s="76"/>
-      <c r="C341" s="76"/>
-      <c r="D341" s="76"/>
-      <c r="E341" s="76"/>
-      <c r="F341" s="76"/>
-      <c r="G341" s="76"/>
-      <c r="H341" s="39"/>
-      <c r="I341" s="39"/>
-      <c r="J341" s="39"/>
+      <c r="A341" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B341" s="11">
+        <v>46317</v>
+      </c>
+      <c r="C341" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E341" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F341" s="6"/>
     </row>
-    <row r="342" spans="1:10" s="7" customFormat="1">
-      <c r="A342" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B342" s="13">
-        <v>46321</v>
-      </c>
-      <c r="C342" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D342" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E342" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F342" s="6"/>
-      <c r="G342" s="1"/>
-      <c r="H342" s="40"/>
-      <c r="I342" s="40"/>
-      <c r="J342" s="40"/>
+    <row r="342" spans="1:10" s="1" customFormat="1">
+      <c r="A342" s="78" t="s">
+        <v>282</v>
+      </c>
+      <c r="B342" s="78"/>
+      <c r="C342" s="78"/>
+      <c r="D342" s="78"/>
+      <c r="E342" s="78"/>
+      <c r="F342" s="78"/>
+      <c r="G342" s="78"/>
+      <c r="H342" s="39"/>
+      <c r="I342" s="39"/>
+      <c r="J342" s="39"/>
     </row>
     <row r="343" spans="1:10" s="7" customFormat="1">
       <c r="A343" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B343" s="13">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F343" s="6"/>
       <c r="G343" s="1"/>
@@ -55388,19 +55419,19 @@
     </row>
     <row r="344" spans="1:10" s="7" customFormat="1">
       <c r="A344" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B344" s="13">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E344" s="7" t="s">
-        <v>26</v>
+      <c r="E344" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F344" s="6"/>
       <c r="G344" s="1"/>
@@ -55409,14 +55440,14 @@
       <c r="J344" s="40"/>
     </row>
     <row r="345" spans="1:10" s="7" customFormat="1">
-      <c r="A345" s="9" t="s">
-        <v>24</v>
+      <c r="A345" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B345" s="13">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D345" s="1" t="s">
         <v>15</v>
@@ -55424,106 +55455,110 @@
       <c r="E345" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F345" s="65"/>
+      <c r="F345" s="6"/>
+      <c r="G345" s="1"/>
+      <c r="H345" s="40"/>
+      <c r="I345" s="40"/>
+      <c r="J345" s="40"/>
     </row>
-    <row r="346" spans="1:10" s="5" customFormat="1" ht="20.25">
-      <c r="A346" s="76" t="s">
-        <v>282</v>
-      </c>
-      <c r="B346" s="76"/>
-      <c r="C346" s="76"/>
-      <c r="D346" s="76"/>
-      <c r="E346" s="76"/>
-      <c r="F346" s="76"/>
-      <c r="G346" s="76"/>
-      <c r="H346" s="39"/>
-      <c r="I346" s="39"/>
-      <c r="J346" s="39"/>
+    <row r="346" spans="1:10" s="7" customFormat="1">
+      <c r="A346" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B346" s="13">
+        <v>46324</v>
+      </c>
+      <c r="C346" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E346" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F346" s="65"/>
     </row>
-    <row r="347" spans="1:10" s="1" customFormat="1">
-      <c r="A347" s="9"/>
-      <c r="B347" s="13"/>
-      <c r="C347" s="8"/>
-      <c r="F347" s="6"/>
-      <c r="G347" s="7"/>
-      <c r="H347" s="42"/>
-      <c r="I347" s="42"/>
-      <c r="J347" s="42"/>
+    <row r="347" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A347" s="78" t="s">
+        <v>283</v>
+      </c>
+      <c r="B347" s="78"/>
+      <c r="C347" s="78"/>
+      <c r="D347" s="78"/>
+      <c r="E347" s="78"/>
+      <c r="F347" s="78"/>
+      <c r="G347" s="78"/>
+      <c r="H347" s="39"/>
+      <c r="I347" s="39"/>
+      <c r="J347" s="39"/>
     </row>
-    <row r="348" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A348" s="79" t="s">
-        <v>283</v>
-      </c>
-      <c r="B348" s="79"/>
-      <c r="C348" s="79"/>
-      <c r="D348" s="79"/>
-      <c r="E348" s="79"/>
-      <c r="F348" s="79"/>
-      <c r="G348" s="79"/>
-      <c r="H348" s="34"/>
-      <c r="I348" s="34"/>
-      <c r="J348" s="34"/>
+    <row r="348" spans="1:10" s="1" customFormat="1">
+      <c r="A348" s="9"/>
+      <c r="B348" s="13"/>
+      <c r="C348" s="8"/>
+      <c r="F348" s="6"/>
+      <c r="G348" s="7"/>
+      <c r="H348" s="42"/>
+      <c r="I348" s="42"/>
+      <c r="J348" s="42"/>
     </row>
-    <row r="349" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A349" s="75" t="s">
+    <row r="349" spans="1:10" s="1" customFormat="1" ht="19.5">
+      <c r="A349" s="81" t="s">
+        <v>284</v>
+      </c>
+      <c r="B349" s="81"/>
+      <c r="C349" s="81"/>
+      <c r="D349" s="81"/>
+      <c r="E349" s="81"/>
+      <c r="F349" s="81"/>
+      <c r="G349" s="81"/>
+      <c r="H349" s="34"/>
+      <c r="I349" s="34"/>
+      <c r="J349" s="34"/>
+    </row>
+    <row r="350" spans="1:10" s="5" customFormat="1" ht="19.5">
+      <c r="A350" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="B349" s="75"/>
-      <c r="C349" s="75"/>
-      <c r="D349" s="75"/>
-      <c r="E349" s="75"/>
-      <c r="F349" s="75"/>
-      <c r="G349" s="75"/>
-      <c r="H349" s="33"/>
-      <c r="I349" s="33"/>
-      <c r="J349" s="33"/>
-    </row>
-    <row r="350" spans="1:10" s="1" customFormat="1">
-      <c r="A350" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="B350" s="24">
-        <v>46327</v>
-      </c>
-      <c r="C350" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D350" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E350" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="F350" s="25"/>
-      <c r="G350" s="23"/>
-      <c r="H350" s="37"/>
-      <c r="I350" s="37"/>
-      <c r="J350" s="37"/>
+      <c r="B350" s="77"/>
+      <c r="C350" s="77"/>
+      <c r="D350" s="77"/>
+      <c r="E350" s="77"/>
+      <c r="F350" s="77"/>
+      <c r="G350" s="77"/>
+      <c r="H350" s="33"/>
+      <c r="I350" s="33"/>
+      <c r="J350" s="33"/>
     </row>
     <row r="351" spans="1:10" s="1" customFormat="1">
-      <c r="A351" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B351" s="13">
-        <v>46328</v>
-      </c>
-      <c r="C351" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E351" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F351" s="6"/>
+      <c r="A351" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="B351" s="24">
+        <v>46327</v>
+      </c>
+      <c r="C351" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D351" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E351" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="F351" s="25"/>
+      <c r="G351" s="23"/>
+      <c r="H351" s="37"/>
+      <c r="I351" s="37"/>
+      <c r="J351" s="37"/>
     </row>
     <row r="352" spans="1:10" s="1" customFormat="1">
       <c r="A352" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B352" s="13">
-        <v>46330</v>
+        <v>46328</v>
       </c>
       <c r="C352" s="6" t="s">
         <v>14</v>
@@ -55531,14 +55566,14 @@
       <c r="D352" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E352" s="7" t="s">
-        <v>26</v>
+      <c r="E352" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F352" s="6"/>
     </row>
     <row r="353" spans="1:10" s="1" customFormat="1">
-      <c r="A353" s="9" t="s">
-        <v>28</v>
+      <c r="A353" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B353" s="13">
         <v>46330</v>
@@ -55555,14 +55590,14 @@
       <c r="F353" s="6"/>
     </row>
     <row r="354" spans="1:10" s="1" customFormat="1">
-      <c r="A354" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B354" s="11">
-        <v>46331</v>
+      <c r="A354" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B354" s="13">
+        <v>46330</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>15</v>
@@ -55573,100 +55608,100 @@
       <c r="F354" s="6"/>
     </row>
     <row r="355" spans="1:10" s="1" customFormat="1">
-      <c r="A355" s="77" t="s">
-        <v>286</v>
-      </c>
-      <c r="B355" s="77"/>
-      <c r="C355" s="77"/>
-      <c r="D355" s="77"/>
-      <c r="E355" s="77"/>
-      <c r="F355" s="77"/>
-      <c r="G355" s="77"/>
-      <c r="H355" s="38"/>
-      <c r="I355" s="38"/>
-      <c r="J355" s="38"/>
+      <c r="A355" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B355" s="11">
+        <v>46331</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E355" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F355" s="6"/>
     </row>
     <row r="356" spans="1:10" s="1" customFormat="1">
-      <c r="A356" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B356" s="13">
-        <v>46335</v>
-      </c>
-      <c r="C356" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D356" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E356" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F356" s="6"/>
+      <c r="A356" s="79" t="s">
+        <v>287</v>
+      </c>
+      <c r="B356" s="79"/>
+      <c r="C356" s="79"/>
+      <c r="D356" s="79"/>
+      <c r="E356" s="79"/>
+      <c r="F356" s="79"/>
+      <c r="G356" s="79"/>
+      <c r="H356" s="38"/>
+      <c r="I356" s="38"/>
+      <c r="J356" s="38"/>
     </row>
     <row r="357" spans="1:10" s="1" customFormat="1">
-      <c r="A357" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="B357" s="24">
-        <v>46336</v>
-      </c>
-      <c r="C357" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D357" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E357" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="F357" s="25"/>
-      <c r="G357" s="23"/>
-      <c r="H357" s="37"/>
-      <c r="I357" s="37"/>
-      <c r="J357" s="37"/>
+      <c r="A357" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B357" s="13">
+        <v>46335</v>
+      </c>
+      <c r="C357" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E357" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F357" s="6"/>
     </row>
     <row r="358" spans="1:10" s="1" customFormat="1">
-      <c r="A358" s="78" t="s">
+      <c r="A358" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="B358" s="24">
+        <v>46336</v>
+      </c>
+      <c r="C358" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D358" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E358" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="B358" s="78"/>
-      <c r="C358" s="78"/>
-      <c r="D358" s="78"/>
-      <c r="E358" s="78"/>
-      <c r="F358" s="78"/>
-      <c r="G358" s="78"/>
-      <c r="H358" s="36"/>
-      <c r="I358" s="36"/>
-      <c r="J358" s="36"/>
+      <c r="F358" s="25"/>
+      <c r="G358" s="23"/>
+      <c r="H358" s="37"/>
+      <c r="I358" s="37"/>
+      <c r="J358" s="37"/>
     </row>
     <row r="359" spans="1:10" s="1" customFormat="1">
-      <c r="A359" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B359" s="13">
-        <v>46337</v>
-      </c>
-      <c r="C359" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D359" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E359" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F359" s="6"/>
+      <c r="A359" s="80" t="s">
+        <v>290</v>
+      </c>
+      <c r="B359" s="80"/>
+      <c r="C359" s="80"/>
+      <c r="D359" s="80"/>
+      <c r="E359" s="80"/>
+      <c r="F359" s="80"/>
+      <c r="G359" s="80"/>
+      <c r="H359" s="36"/>
+      <c r="I359" s="36"/>
+      <c r="J359" s="36"/>
     </row>
     <row r="360" spans="1:10" s="1" customFormat="1">
-      <c r="A360" s="9" t="s">
-        <v>24</v>
+      <c r="A360" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B360" s="13">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>15</v>
@@ -55677,29 +55712,29 @@
       <c r="F360" s="6"/>
     </row>
     <row r="361" spans="1:10" s="1" customFormat="1">
-      <c r="A361" s="1" t="s">
-        <v>13</v>
+      <c r="A361" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="B361" s="13">
-        <v>46342</v>
+        <v>46338</v>
       </c>
       <c r="C361" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E361" s="1" t="s">
-        <v>16</v>
+      <c r="E361" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F361" s="6"/>
     </row>
     <row r="362" spans="1:10" s="1" customFormat="1">
       <c r="A362" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B362" s="13">
-        <v>46344</v>
+        <v>46342</v>
       </c>
       <c r="C362" s="6" t="s">
         <v>14</v>
@@ -55707,14 +55742,14 @@
       <c r="D362" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E362" s="7" t="s">
-        <v>26</v>
+      <c r="E362" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F362" s="6"/>
     </row>
     <row r="363" spans="1:10" s="1" customFormat="1">
-      <c r="A363" s="9" t="s">
-        <v>28</v>
+      <c r="A363" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B363" s="13">
         <v>46344</v>
@@ -55731,14 +55766,14 @@
       <c r="F363" s="6"/>
     </row>
     <row r="364" spans="1:10" s="1" customFormat="1">
-      <c r="A364" s="10" t="s">
-        <v>24</v>
+      <c r="A364" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B364" s="13">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D364" s="1" t="s">
         <v>15</v>
@@ -55749,246 +55784,246 @@
       <c r="F364" s="6"/>
     </row>
     <row r="365" spans="1:10" s="1" customFormat="1">
-      <c r="A365" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="B365" s="24">
-        <v>46346</v>
-      </c>
-      <c r="C365" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D365" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E365" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="F365" s="25"/>
-      <c r="G365" s="23"/>
-      <c r="H365" s="37"/>
-      <c r="I365" s="37"/>
-      <c r="J365" s="37"/>
+      <c r="A365" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B365" s="13">
+        <v>46345</v>
+      </c>
+      <c r="C365" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E365" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F365" s="6"/>
     </row>
     <row r="366" spans="1:10" s="1" customFormat="1">
-      <c r="A366" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B366" s="13">
-        <v>46349</v>
-      </c>
-      <c r="C366" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D366" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E366" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F366" s="6"/>
+      <c r="A366" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="B366" s="24">
+        <v>46346</v>
+      </c>
+      <c r="C366" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D366" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E366" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="F366" s="25"/>
+      <c r="G366" s="23"/>
+      <c r="H366" s="37"/>
+      <c r="I366" s="37"/>
+      <c r="J366" s="37"/>
     </row>
     <row r="367" spans="1:10" s="1" customFormat="1">
-      <c r="A367" s="76" t="s">
-        <v>292</v>
-      </c>
-      <c r="B367" s="76"/>
-      <c r="C367" s="76"/>
-      <c r="D367" s="76"/>
-      <c r="E367" s="76"/>
-      <c r="F367" s="76"/>
-      <c r="G367" s="76"/>
-      <c r="H367" s="39"/>
-      <c r="I367" s="39"/>
-      <c r="J367" s="39"/>
+      <c r="A367" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B367" s="13">
+        <v>46349</v>
+      </c>
+      <c r="C367" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E367" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F367" s="6"/>
     </row>
     <row r="368" spans="1:10" s="1" customFormat="1">
-      <c r="A368" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B368" s="13">
-        <v>46350</v>
-      </c>
-      <c r="C368" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D368" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E368" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F368" s="6"/>
+      <c r="A368" s="78" t="s">
+        <v>293</v>
+      </c>
+      <c r="B368" s="78"/>
+      <c r="C368" s="78"/>
+      <c r="D368" s="78"/>
+      <c r="E368" s="78"/>
+      <c r="F368" s="78"/>
+      <c r="G368" s="78"/>
+      <c r="H368" s="39"/>
+      <c r="I368" s="39"/>
+      <c r="J368" s="39"/>
     </row>
     <row r="369" spans="1:10" s="1" customFormat="1">
       <c r="A369" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B369" s="13">
-        <v>46351</v>
+        <v>46350</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D369" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E369" s="7" t="s">
-        <v>26</v>
+      <c r="E369" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F369" s="6"/>
     </row>
     <row r="370" spans="1:10" s="1" customFormat="1">
-      <c r="A370" s="78" t="s">
-        <v>293</v>
-      </c>
-      <c r="B370" s="78"/>
-      <c r="C370" s="78"/>
-      <c r="D370" s="78"/>
-      <c r="E370" s="78"/>
-      <c r="F370" s="78"/>
-      <c r="G370" s="78"/>
-      <c r="H370" s="36"/>
-      <c r="I370" s="36"/>
-      <c r="J370" s="36"/>
+      <c r="A370" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B370" s="13">
+        <v>46351</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E370" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F370" s="6"/>
     </row>
     <row r="371" spans="1:10" s="1" customFormat="1">
-      <c r="A371" s="9" t="s">
+      <c r="A371" s="80" t="s">
+        <v>294</v>
+      </c>
+      <c r="B371" s="80"/>
+      <c r="C371" s="80"/>
+      <c r="D371" s="80"/>
+      <c r="E371" s="80"/>
+      <c r="F371" s="80"/>
+      <c r="G371" s="80"/>
+      <c r="H371" s="36"/>
+      <c r="I371" s="36"/>
+      <c r="J371" s="36"/>
+    </row>
+    <row r="372" spans="1:10" s="1" customFormat="1">
+      <c r="A372" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B371" s="11">
+      <c r="B372" s="11">
         <v>46352</v>
       </c>
-      <c r="C371" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D371" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E371" s="7" t="s">
+      <c r="C372" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E372" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F371" s="6"/>
+      <c r="F372" s="6"/>
     </row>
-    <row r="372" spans="1:10" s="7" customFormat="1">
-      <c r="A372" s="76" t="s">
-        <v>294</v>
-      </c>
-      <c r="B372" s="76"/>
-      <c r="C372" s="76"/>
-      <c r="D372" s="76"/>
-      <c r="E372" s="76"/>
-      <c r="F372" s="76"/>
-      <c r="G372" s="76"/>
-      <c r="H372" s="39"/>
-      <c r="I372" s="39"/>
-      <c r="J372" s="39"/>
+    <row r="373" spans="1:10" s="7" customFormat="1">
+      <c r="A373" s="78" t="s">
+        <v>295</v>
+      </c>
+      <c r="B373" s="78"/>
+      <c r="C373" s="78"/>
+      <c r="D373" s="78"/>
+      <c r="E373" s="78"/>
+      <c r="F373" s="78"/>
+      <c r="G373" s="78"/>
+      <c r="H373" s="39"/>
+      <c r="I373" s="39"/>
+      <c r="J373" s="39"/>
     </row>
-    <row r="373" spans="1:10" s="5" customFormat="1" ht="20.25">
-      <c r="A373" s="1" t="s">
+    <row r="374" spans="1:10" s="5" customFormat="1" ht="20.25">
+      <c r="A374" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B373" s="13">
+      <c r="B374" s="13">
         <v>46356</v>
       </c>
-      <c r="C373" s="6" t="s">
+      <c r="C374" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D373" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E373" s="1" t="s">
+      <c r="D374" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E374" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F373" s="6"/>
-      <c r="G373" s="1"/>
-      <c r="H373" s="40"/>
-      <c r="I373" s="40"/>
-      <c r="J373" s="40"/>
+      <c r="F374" s="6"/>
+      <c r="G374" s="1"/>
+      <c r="H374" s="40"/>
+      <c r="I374" s="40"/>
+      <c r="J374" s="40"/>
     </row>
-    <row r="374" spans="1:10" s="1" customFormat="1">
-      <c r="A374" s="7"/>
-      <c r="B374" s="7"/>
-      <c r="C374" s="7"/>
-      <c r="D374" s="7"/>
-      <c r="E374" s="7"/>
-      <c r="F374" s="65"/>
-      <c r="G374" s="7"/>
-      <c r="H374" s="42"/>
-      <c r="I374" s="42"/>
-      <c r="J374" s="42"/>
+    <row r="375" spans="1:10" s="1" customFormat="1">
+      <c r="A375" s="7"/>
+      <c r="B375" s="7"/>
+      <c r="C375" s="7"/>
+      <c r="D375" s="7"/>
+      <c r="E375" s="7"/>
+      <c r="F375" s="65"/>
+      <c r="G375" s="7"/>
+      <c r="H375" s="42"/>
+      <c r="I375" s="42"/>
+      <c r="J375" s="42"/>
     </row>
-    <row r="375" spans="1:10" s="1" customFormat="1" ht="19.5">
-      <c r="A375" s="79" t="s">
-        <v>295</v>
-      </c>
-      <c r="B375" s="79"/>
-      <c r="C375" s="79"/>
-      <c r="D375" s="79"/>
-      <c r="E375" s="79"/>
-      <c r="F375" s="79"/>
-      <c r="G375" s="79"/>
-      <c r="H375" s="34"/>
-      <c r="I375" s="34"/>
-      <c r="J375" s="34"/>
+    <row r="376" spans="1:10" s="1" customFormat="1" ht="19.5">
+      <c r="A376" s="81" t="s">
+        <v>296</v>
+      </c>
+      <c r="B376" s="81"/>
+      <c r="C376" s="81"/>
+      <c r="D376" s="81"/>
+      <c r="E376" s="81"/>
+      <c r="F376" s="81"/>
+      <c r="G376" s="81"/>
+      <c r="H376" s="34"/>
+      <c r="I376" s="34"/>
+      <c r="J376" s="34"/>
     </row>
-    <row r="376" spans="1:10" s="5" customFormat="1" ht="19.5">
-      <c r="A376" s="75" t="s">
+    <row r="377" spans="1:10" s="5" customFormat="1" ht="19.5">
+      <c r="A377" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="B376" s="75"/>
-      <c r="C376" s="75"/>
-      <c r="D376" s="75"/>
-      <c r="E376" s="75"/>
-      <c r="F376" s="75"/>
-      <c r="G376" s="75"/>
-      <c r="H376" s="33"/>
-      <c r="I376" s="33"/>
-      <c r="J376" s="33"/>
-    </row>
-    <row r="377" spans="1:10" s="1" customFormat="1">
-      <c r="A377" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="B377" s="24">
-        <v>46357</v>
-      </c>
-      <c r="C377" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D377" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E377" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="F377" s="25"/>
-      <c r="G377" s="23"/>
-      <c r="H377" s="37"/>
-      <c r="I377" s="37"/>
-      <c r="J377" s="37"/>
+      <c r="B377" s="77"/>
+      <c r="C377" s="77"/>
+      <c r="D377" s="77"/>
+      <c r="E377" s="77"/>
+      <c r="F377" s="77"/>
+      <c r="G377" s="77"/>
+      <c r="H377" s="33"/>
+      <c r="I377" s="33"/>
+      <c r="J377" s="33"/>
     </row>
     <row r="378" spans="1:10" s="1" customFormat="1">
-      <c r="A378" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B378" s="13">
-        <v>46358</v>
-      </c>
-      <c r="C378" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D378" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E378" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F378" s="6"/>
+      <c r="A378" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="B378" s="24">
+        <v>46357</v>
+      </c>
+      <c r="C378" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D378" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E378" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="F378" s="25"/>
+      <c r="G378" s="23"/>
+      <c r="H378" s="37"/>
+      <c r="I378" s="37"/>
+      <c r="J378" s="37"/>
     </row>
     <row r="379" spans="1:10" s="1" customFormat="1">
-      <c r="A379" s="9" t="s">
-        <v>28</v>
+      <c r="A379" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B379" s="13">
         <v>46358</v>
@@ -56005,14 +56040,14 @@
       <c r="F379" s="6"/>
     </row>
     <row r="380" spans="1:10" s="1" customFormat="1">
-      <c r="A380" s="10" t="s">
-        <v>24</v>
+      <c r="A380" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B380" s="13">
-        <v>46359</v>
+        <v>46358</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D380" s="1" t="s">
         <v>15</v>
@@ -56023,43 +56058,43 @@
       <c r="F380" s="6"/>
     </row>
     <row r="381" spans="1:10" s="1" customFormat="1">
-      <c r="A381" s="77" t="s">
-        <v>298</v>
-      </c>
-      <c r="B381" s="77"/>
-      <c r="C381" s="77"/>
-      <c r="D381" s="77"/>
-      <c r="E381" s="77"/>
-      <c r="F381" s="77"/>
-      <c r="G381" s="77"/>
-      <c r="H381" s="38"/>
-      <c r="I381" s="38"/>
-      <c r="J381" s="38"/>
+      <c r="A381" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B381" s="13">
+        <v>46359</v>
+      </c>
+      <c r="C381" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E381" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F381" s="6"/>
     </row>
     <row r="382" spans="1:10" s="1" customFormat="1">
-      <c r="A382" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B382" s="13">
-        <v>46363</v>
-      </c>
-      <c r="C382" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D382" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E382" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F382" s="6"/>
+      <c r="A382" s="79" t="s">
+        <v>299</v>
+      </c>
+      <c r="B382" s="79"/>
+      <c r="C382" s="79"/>
+      <c r="D382" s="79"/>
+      <c r="E382" s="79"/>
+      <c r="F382" s="79"/>
+      <c r="G382" s="79"/>
+      <c r="H382" s="38"/>
+      <c r="I382" s="38"/>
+      <c r="J382" s="38"/>
     </row>
     <row r="383" spans="1:10" s="1" customFormat="1">
       <c r="A383" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B383" s="13">
-        <v>46365</v>
+        <v>46363</v>
       </c>
       <c r="C383" s="6" t="s">
         <v>14</v>
@@ -56067,20 +56102,20 @@
       <c r="D383" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E383" s="7" t="s">
-        <v>26</v>
+      <c r="E383" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F383" s="6"/>
     </row>
     <row r="384" spans="1:10" s="1" customFormat="1">
-      <c r="A384" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B384" s="11">
-        <v>46366</v>
+      <c r="A384" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B384" s="13">
+        <v>46365</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>15</v>
@@ -56091,80 +56126,80 @@
       <c r="F384" s="6"/>
     </row>
     <row r="385" spans="1:10" s="1" customFormat="1">
-      <c r="A385" s="77" t="s">
-        <v>299</v>
-      </c>
-      <c r="B385" s="77"/>
-      <c r="C385" s="77"/>
-      <c r="D385" s="77"/>
-      <c r="E385" s="77"/>
-      <c r="F385" s="77"/>
-      <c r="G385" s="77"/>
-      <c r="H385" s="38"/>
-      <c r="I385" s="38"/>
-      <c r="J385" s="38"/>
+      <c r="A385" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B385" s="11">
+        <v>46366</v>
+      </c>
+      <c r="C385" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E385" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F385" s="6"/>
     </row>
     <row r="386" spans="1:10" s="1" customFormat="1">
-      <c r="A386" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B386" s="13">
-        <v>46370</v>
-      </c>
-      <c r="C386" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D386" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E386" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F386" s="6"/>
+      <c r="A386" s="79" t="s">
+        <v>300</v>
+      </c>
+      <c r="B386" s="79"/>
+      <c r="C386" s="79"/>
+      <c r="D386" s="79"/>
+      <c r="E386" s="79"/>
+      <c r="F386" s="79"/>
+      <c r="G386" s="79"/>
+      <c r="H386" s="38"/>
+      <c r="I386" s="38"/>
+      <c r="J386" s="38"/>
     </row>
     <row r="387" spans="1:10" s="1" customFormat="1">
-      <c r="A387" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="B387" s="24">
-        <v>46371</v>
-      </c>
-      <c r="C387" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D387" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E387" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="F387" s="25"/>
-      <c r="G387" s="23"/>
-      <c r="H387" s="37"/>
-      <c r="I387" s="37"/>
-      <c r="J387" s="37"/>
+      <c r="A387" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B387" s="13">
+        <v>46370</v>
+      </c>
+      <c r="C387" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E387" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F387" s="6"/>
     </row>
     <row r="388" spans="1:10" s="1" customFormat="1">
-      <c r="A388" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B388" s="13">
-        <v>46372</v>
-      </c>
-      <c r="C388" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D388" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E388" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F388" s="6"/>
+      <c r="A388" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="B388" s="24">
+        <v>46371</v>
+      </c>
+      <c r="C388" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D388" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E388" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="F388" s="25"/>
+      <c r="G388" s="23"/>
+      <c r="H388" s="37"/>
+      <c r="I388" s="37"/>
+      <c r="J388" s="37"/>
     </row>
     <row r="389" spans="1:10" s="1" customFormat="1">
-      <c r="A389" s="9" t="s">
-        <v>28</v>
+      <c r="A389" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B389" s="13">
         <v>46372</v>
@@ -56181,14 +56216,14 @@
       <c r="F389" s="6"/>
     </row>
     <row r="390" spans="1:10" s="1" customFormat="1">
-      <c r="A390" s="10" t="s">
-        <v>24</v>
+      <c r="A390" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B390" s="13">
-        <v>46373</v>
+        <v>46372</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>15</v>
@@ -56199,29 +56234,29 @@
       <c r="F390" s="6"/>
     </row>
     <row r="391" spans="1:10" s="1" customFormat="1">
-      <c r="A391" s="1" t="s">
-        <v>13</v>
+      <c r="A391" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="B391" s="13">
-        <v>46377</v>
+        <v>46373</v>
       </c>
       <c r="C391" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D391" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E391" s="1" t="s">
-        <v>16</v>
+      <c r="E391" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F391" s="6"/>
     </row>
     <row r="392" spans="1:10" s="1" customFormat="1">
       <c r="A392" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B392" s="13">
-        <v>46379</v>
+        <v>46377</v>
       </c>
       <c r="C392" s="6" t="s">
         <v>14</v>
@@ -56229,128 +56264,128 @@
       <c r="D392" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E392" s="7" t="s">
-        <v>26</v>
+      <c r="E392" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F392" s="6"/>
     </row>
     <row r="393" spans="1:10" s="1" customFormat="1">
-      <c r="A393" s="77" t="s">
-        <v>302</v>
-      </c>
-      <c r="B393" s="77"/>
-      <c r="C393" s="77"/>
-      <c r="D393" s="77"/>
-      <c r="E393" s="77"/>
-      <c r="F393" s="77"/>
-      <c r="G393" s="77"/>
-      <c r="H393" s="38"/>
-      <c r="I393" s="38"/>
-      <c r="J393" s="38"/>
+      <c r="A393" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B393" s="13">
+        <v>46379</v>
+      </c>
+      <c r="C393" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E393" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F393" s="6"/>
     </row>
     <row r="394" spans="1:10" s="1" customFormat="1">
-      <c r="A394" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B394" s="13">
-        <v>46380</v>
-      </c>
-      <c r="C394" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D394" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E394" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F394" s="6"/>
+      <c r="A394" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="B394" s="79"/>
+      <c r="C394" s="79"/>
+      <c r="D394" s="79"/>
+      <c r="E394" s="79"/>
+      <c r="F394" s="79"/>
+      <c r="G394" s="79"/>
+      <c r="H394" s="38"/>
+      <c r="I394" s="38"/>
+      <c r="J394" s="38"/>
     </row>
     <row r="395" spans="1:10" s="1" customFormat="1">
-      <c r="A395" s="77" t="s">
-        <v>303</v>
-      </c>
-      <c r="B395" s="77"/>
-      <c r="C395" s="77"/>
-      <c r="D395" s="77"/>
-      <c r="E395" s="77"/>
-      <c r="F395" s="77"/>
-      <c r="G395" s="77"/>
-      <c r="H395" s="38"/>
-      <c r="I395" s="38"/>
-      <c r="J395" s="38"/>
+      <c r="A395" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B395" s="13">
+        <v>46380</v>
+      </c>
+      <c r="C395" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E395" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F395" s="6"/>
     </row>
     <row r="396" spans="1:10" s="1" customFormat="1">
-      <c r="A396" s="78" t="s">
+      <c r="A396" s="79" t="s">
         <v>304</v>
       </c>
-      <c r="B396" s="78"/>
-      <c r="C396" s="78"/>
-      <c r="D396" s="78"/>
-      <c r="E396" s="78"/>
-      <c r="F396" s="78"/>
-      <c r="G396" s="78"/>
-      <c r="H396" s="36"/>
-      <c r="I396" s="36"/>
-      <c r="J396" s="36"/>
+      <c r="B396" s="79"/>
+      <c r="C396" s="79"/>
+      <c r="D396" s="79"/>
+      <c r="E396" s="79"/>
+      <c r="F396" s="79"/>
+      <c r="G396" s="79"/>
+      <c r="H396" s="38"/>
+      <c r="I396" s="38"/>
+      <c r="J396" s="38"/>
     </row>
     <row r="397" spans="1:10" s="1" customFormat="1">
-      <c r="A397" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B397" s="13">
-        <v>46384</v>
-      </c>
-      <c r="C397" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D397" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E397" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F397" s="6"/>
+      <c r="A397" s="80" t="s">
+        <v>305</v>
+      </c>
+      <c r="B397" s="80"/>
+      <c r="C397" s="80"/>
+      <c r="D397" s="80"/>
+      <c r="E397" s="80"/>
+      <c r="F397" s="80"/>
+      <c r="G397" s="80"/>
+      <c r="H397" s="36"/>
+      <c r="I397" s="36"/>
+      <c r="J397" s="36"/>
     </row>
     <row r="398" spans="1:10" s="1" customFormat="1">
       <c r="A398" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B398" s="13">
-        <v>46385</v>
+        <v>46384</v>
       </c>
       <c r="C398" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D398" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F398" s="6"/>
     </row>
     <row r="399" spans="1:10" s="1" customFormat="1">
       <c r="A399" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B399" s="13">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E399" s="7" t="s">
-        <v>26</v>
+      <c r="E399" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F399" s="6"/>
     </row>
     <row r="400" spans="1:10" s="1" customFormat="1">
-      <c r="A400" s="9" t="s">
-        <v>28</v>
+      <c r="A400" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B400" s="13">
         <v>46386</v>
@@ -56366,55 +56401,73 @@
       </c>
       <c r="F400" s="6"/>
     </row>
-    <row r="401" spans="1:10" s="7" customFormat="1">
-      <c r="A401" s="78" t="s">
-        <v>305</v>
-      </c>
-      <c r="B401" s="78"/>
-      <c r="C401" s="78"/>
-      <c r="D401" s="78"/>
-      <c r="E401" s="78"/>
-      <c r="F401" s="78"/>
-      <c r="G401" s="78"/>
-      <c r="H401" s="36"/>
-      <c r="I401" s="36"/>
-      <c r="J401" s="36"/>
+    <row r="401" spans="1:10" s="1" customFormat="1">
+      <c r="A401" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B401" s="13">
+        <v>46386</v>
+      </c>
+      <c r="C401" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E401" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F401" s="6"/>
     </row>
-    <row r="402" spans="1:10">
-      <c r="A402" s="76" t="s">
+    <row r="402" spans="1:10" s="7" customFormat="1">
+      <c r="A402" s="80" t="s">
         <v>306</v>
       </c>
-      <c r="B402" s="76"/>
-      <c r="C402" s="76"/>
-      <c r="D402" s="76"/>
-      <c r="E402" s="76"/>
-      <c r="F402" s="76"/>
-      <c r="G402" s="76"/>
-      <c r="H402" s="39"/>
-      <c r="I402" s="39"/>
-      <c r="J402" s="39"/>
+      <c r="B402" s="80"/>
+      <c r="C402" s="80"/>
+      <c r="D402" s="80"/>
+      <c r="E402" s="80"/>
+      <c r="F402" s="80"/>
+      <c r="G402" s="80"/>
+      <c r="H402" s="36"/>
+      <c r="I402" s="36"/>
+      <c r="J402" s="36"/>
     </row>
     <row r="403" spans="1:10">
-      <c r="A403" s="10" t="s">
+      <c r="A403" s="78" t="s">
+        <v>307</v>
+      </c>
+      <c r="B403" s="78"/>
+      <c r="C403" s="78"/>
+      <c r="D403" s="78"/>
+      <c r="E403" s="78"/>
+      <c r="F403" s="78"/>
+      <c r="G403" s="78"/>
+      <c r="H403" s="39"/>
+      <c r="I403" s="39"/>
+      <c r="J403" s="39"/>
+    </row>
+    <row r="404" spans="1:10">
+      <c r="A404" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B403" s="11">
+      <c r="B404" s="11">
         <v>46387</v>
       </c>
-      <c r="C403" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D403" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E403" s="7" t="s">
+      <c r="C404" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E404" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F403" s="65"/>
-      <c r="G403" s="7"/>
-      <c r="H403" s="42"/>
-      <c r="I403" s="42"/>
-      <c r="J403" s="42"/>
+      <c r="F404" s="65"/>
+      <c r="G404" s="7"/>
+      <c r="H404" s="42"/>
+      <c r="I404" s="42"/>
+      <c r="J404" s="42"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{CD25C92C-1A37-4466-8D09-37A65C4BD4ED}"/>
@@ -56424,36 +56477,36 @@
     <mergeCell ref="A191:G191"/>
     <mergeCell ref="A192:G192"/>
     <mergeCell ref="A193:G193"/>
-    <mergeCell ref="A216:G216"/>
+    <mergeCell ref="A217:G217"/>
+    <mergeCell ref="A202:G202"/>
     <mergeCell ref="A201:G201"/>
-    <mergeCell ref="A200:G200"/>
-    <mergeCell ref="A212:G212"/>
+    <mergeCell ref="A213:G213"/>
     <mergeCell ref="A162:G162"/>
     <mergeCell ref="A170:G170"/>
+    <mergeCell ref="A177:G177"/>
     <mergeCell ref="A178:G178"/>
     <mergeCell ref="A179:G179"/>
-    <mergeCell ref="A180:G180"/>
-    <mergeCell ref="A312:G312"/>
-    <mergeCell ref="A321:G321"/>
+    <mergeCell ref="A313:G313"/>
+    <mergeCell ref="A322:G322"/>
+    <mergeCell ref="A299:G299"/>
+    <mergeCell ref="A319:G319"/>
     <mergeCell ref="A298:G298"/>
-    <mergeCell ref="A318:G318"/>
-    <mergeCell ref="A297:G297"/>
+    <mergeCell ref="A267:G267"/>
+    <mergeCell ref="A320:G320"/>
+    <mergeCell ref="A293:G293"/>
+    <mergeCell ref="A292:G292"/>
+    <mergeCell ref="A268:G268"/>
+    <mergeCell ref="A277:G277"/>
+    <mergeCell ref="A289:G289"/>
     <mergeCell ref="A266:G266"/>
-    <mergeCell ref="A319:G319"/>
-    <mergeCell ref="A292:G292"/>
-    <mergeCell ref="A291:G291"/>
-    <mergeCell ref="A267:G267"/>
-    <mergeCell ref="A276:G276"/>
-    <mergeCell ref="A288:G288"/>
+    <mergeCell ref="A221:G221"/>
+    <mergeCell ref="A226:G226"/>
     <mergeCell ref="A265:G265"/>
-    <mergeCell ref="A220:G220"/>
-    <mergeCell ref="A225:G225"/>
-    <mergeCell ref="A264:G264"/>
-    <mergeCell ref="A255:G255"/>
-    <mergeCell ref="A236:G236"/>
-    <mergeCell ref="A295:G295"/>
-    <mergeCell ref="A302:G302"/>
-    <mergeCell ref="A307:G307"/>
+    <mergeCell ref="A256:G256"/>
+    <mergeCell ref="A237:G237"/>
+    <mergeCell ref="A296:G296"/>
+    <mergeCell ref="A303:G303"/>
+    <mergeCell ref="A308:G308"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="A72:G72"/>
@@ -56476,32 +56529,32 @@
     <mergeCell ref="A122:G122"/>
     <mergeCell ref="A123:G123"/>
     <mergeCell ref="A125:G125"/>
-    <mergeCell ref="A402:G402"/>
-    <mergeCell ref="A355:G355"/>
-    <mergeCell ref="A348:G348"/>
-    <mergeCell ref="A375:G375"/>
-    <mergeCell ref="A401:G401"/>
-    <mergeCell ref="A322:G322"/>
-    <mergeCell ref="A323:G323"/>
-    <mergeCell ref="A329:G329"/>
-    <mergeCell ref="A358:G358"/>
-    <mergeCell ref="A370:G370"/>
-    <mergeCell ref="A335:G335"/>
-    <mergeCell ref="A341:G341"/>
-    <mergeCell ref="A332:G332"/>
-    <mergeCell ref="A381:G381"/>
-    <mergeCell ref="A385:G385"/>
-    <mergeCell ref="A393:G393"/>
-    <mergeCell ref="A396:G396"/>
-    <mergeCell ref="A395:G395"/>
+    <mergeCell ref="A403:G403"/>
+    <mergeCell ref="A356:G356"/>
     <mergeCell ref="A349:G349"/>
     <mergeCell ref="A376:G376"/>
-    <mergeCell ref="A372:G372"/>
+    <mergeCell ref="A402:G402"/>
+    <mergeCell ref="A323:G323"/>
+    <mergeCell ref="A324:G324"/>
+    <mergeCell ref="A330:G330"/>
+    <mergeCell ref="A359:G359"/>
+    <mergeCell ref="A371:G371"/>
+    <mergeCell ref="A336:G336"/>
+    <mergeCell ref="A342:G342"/>
+    <mergeCell ref="A333:G333"/>
+    <mergeCell ref="A382:G382"/>
+    <mergeCell ref="A386:G386"/>
+    <mergeCell ref="A394:G394"/>
+    <mergeCell ref="A397:G397"/>
+    <mergeCell ref="A396:G396"/>
+    <mergeCell ref="A350:G350"/>
+    <mergeCell ref="A377:G377"/>
+    <mergeCell ref="A373:G373"/>
     <mergeCell ref="A160:G160"/>
-    <mergeCell ref="A202:G202"/>
-    <mergeCell ref="A325:G325"/>
-    <mergeCell ref="A346:G346"/>
-    <mergeCell ref="A367:G367"/>
+    <mergeCell ref="A203:G203"/>
+    <mergeCell ref="A326:G326"/>
+    <mergeCell ref="A347:G347"/>
+    <mergeCell ref="A368:G368"/>
     <mergeCell ref="A81:G81"/>
     <mergeCell ref="A95:G95"/>
     <mergeCell ref="A98:G98"/>
@@ -56514,13 +56567,13 @@
     <mergeCell ref="A49:G49"/>
     <mergeCell ref="A54:G54"/>
     <mergeCell ref="A113:G113"/>
-    <mergeCell ref="A226:G226"/>
-    <mergeCell ref="A237:G237"/>
-    <mergeCell ref="A241:G241"/>
-    <mergeCell ref="A235:G235"/>
-    <mergeCell ref="A257:G257"/>
-    <mergeCell ref="A232:G232"/>
-    <mergeCell ref="A248:G248"/>
+    <mergeCell ref="A227:G227"/>
+    <mergeCell ref="A238:G238"/>
+    <mergeCell ref="A242:G242"/>
+    <mergeCell ref="A236:G236"/>
+    <mergeCell ref="A258:G258"/>
+    <mergeCell ref="A233:G233"/>
+    <mergeCell ref="A249:G249"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G43" r:id="rId1" xr:uid="{742AFF79-FB56-4C66-9522-07C11D0E7152}"/>
@@ -56566,7 +56619,7 @@
     <hyperlink ref="H135" r:id="rId41" xr:uid="{87AB4455-9796-4948-AB71-0CEE64BDE185}"/>
     <hyperlink ref="G145" r:id="rId42" xr:uid="{9D255DDD-C496-4727-B4B4-CD25CFF108D5}"/>
     <hyperlink ref="G155" r:id="rId43" xr:uid="{CA84913D-41F5-40BF-8C06-6E3A565D6C77}"/>
-    <hyperlink ref="I181" r:id="rId44" xr:uid="{FFD348D1-FC85-40EF-B959-892A2FDAC5D2}"/>
+    <hyperlink ref="I180" r:id="rId44" xr:uid="{FFD348D1-FC85-40EF-B959-892A2FDAC5D2}"/>
     <hyperlink ref="I165" r:id="rId45" xr:uid="{5212898E-0486-4AE9-B388-1BFCFA1D05A8}"/>
     <hyperlink ref="G163" r:id="rId46" xr:uid="{6E1ED79B-1B90-4B7D-9B59-99E101DDECAA}"/>
     <hyperlink ref="G171" r:id="rId47" xr:uid="{FC5E99C3-DBF9-4B05-87A0-5900EBEF0FD2}"/>
@@ -56592,236 +56645,236 @@
   <sheetData>
     <row r="1" spans="1:8" s="14" customFormat="1">
       <c r="A1" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="14" customFormat="1">
       <c r="A2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="14" customFormat="1">
       <c r="A3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
@@ -56829,21 +56882,21 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="17" customFormat="1">
       <c r="A13" s="17" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18" t="s">
@@ -56853,65 +56906,65 @@
         <v>15</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="14" customFormat="1">
       <c r="A14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B14"/>
       <c r="C14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G14"/>
       <c r="H14"/>
     </row>
     <row r="15" spans="1:8" s="15" customFormat="1">
       <c r="A15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B15"/>
       <c r="C15" t="s">
+        <v>364</v>
+      </c>
+      <c r="D15" t="s">
+        <v>361</v>
+      </c>
+      <c r="E15" t="s">
+        <v>365</v>
+      </c>
+      <c r="F15" t="s">
         <v>363</v>
-      </c>
-      <c r="D15" t="s">
-        <v>360</v>
-      </c>
-      <c r="E15" t="s">
-        <v>364</v>
-      </c>
-      <c r="F15" t="s">
-        <v>362</v>
       </c>
       <c r="G15"/>
       <c r="H15"/>
     </row>
     <row r="16" spans="1:8" s="18" customFormat="1">
       <c r="A16" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
@@ -56921,15 +56974,15 @@
     </row>
     <row r="17" spans="1:8" s="18" customFormat="1">
       <c r="A17" s="17" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D17" s="17"/>
       <c r="E17" s="17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
@@ -56937,35 +56990,35 @@
     </row>
     <row r="19" spans="1:8" ht="15.95">
       <c r="C19" s="22" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.95">
       <c r="C20" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
         <v>372</v>
-      </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.95">
       <c r="C21" s="21" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.95">
@@ -56985,25 +57038,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E45CCE-D0CC-4272-9CD7-78C74A148970}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>376</v>
+    <row r="2" spans="1:2">
+      <c r="A2" s="76" t="s">
+        <v>377</v>
+      </c>
+      <c r="B2" s="76" t="s">
+        <v>378</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>377</v>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>
